--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC13" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Denmark_Su" displayName="AveragesTable_Denmark_Su" ref="A1:EC13" headerRowCount="1">
   <autoFilter ref="A1:EC13"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0.38</v>
@@ -1469,139 +1469,139 @@
         <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AI2" t="n">
-        <v>83</v>
+        <v>81.25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AN2" t="n">
-        <v>42.43</v>
+        <v>47</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.29</v>
+        <v>10.62</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.43</v>
+        <v>7.38</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>48.14</v>
+        <v>47.25</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.43</v>
+        <v>12.88</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.57</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.86</v>
+        <v>4.75</v>
       </c>
       <c r="BD2" t="n">
-        <v>19.86</v>
+        <v>18.12</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.13</v>
+        <v>3.06</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.33</v>
+        <v>9.31</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.13</v>
+        <v>3.06</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM2" t="n">
         <v>1</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="BR2" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS2" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT2" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU2" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV2" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BY2" t="n">
         <v>1.84</v>
@@ -1616,34 +1616,34 @@
         <v>3.95</v>
       </c>
       <c r="CC2" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.96</v>
+        <v>2.83</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CH2" t="n">
         <v>1.51</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.64</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM2" t="n">
         <v>2.41</v>
@@ -1655,10 +1655,10 @@
         <v>1.2</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="CR2" t="n">
         <v>1.35</v>
@@ -1673,10 +1673,10 @@
         <v>1.54</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CX2" t="n">
         <v>1.54</v>
@@ -1694,85 +1694,85 @@
         <v>1.22</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="DH2" t="n">
-        <v>100.8</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.4</v>
+        <v>5.31</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM2" t="n">
-        <v>55.6</v>
+        <v>57.06</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.14</v>
+        <v>10.19</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.93</v>
+        <v>10.62</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.93</v>
+        <v>6</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.2</v>
+        <v>53.38</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.73</v>
+        <v>16.69</v>
       </c>
       <c r="DY2" t="n">
-        <v>11.06</v>
+        <v>11.12</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.67</v>
+        <v>5.56</v>
       </c>
       <c r="EA2" t="n">
-        <v>18</v>
+        <v>17.25</v>
       </c>
       <c r="EB2" t="n">
         <v>1.85</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="G10" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="H10" t="n">
-        <v>99.70999999999999</v>
+        <v>99.75</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="K10" t="n">
         <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="M10" t="n">
-        <v>39.43</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="O10" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="P10" t="n">
-        <v>6.57</v>
+        <v>6.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.43</v>
+        <v>11.38</v>
       </c>
       <c r="R10" t="n">
-        <v>9.140000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="T10" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>51.57</v>
+        <v>52.5</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>12</v>
+        <v>11.38</v>
       </c>
       <c r="AA10" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>17.43</v>
+        <v>16.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AF10" t="n">
         <v>0.25</v>
@@ -4774,70 +4774,70 @@
         <v>0.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.4</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BO10" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="BP10" t="n">
         <v>5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT10" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU10" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW10" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BX10" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="CC10" t="n">
         <v>4.31</v>
@@ -4846,10 +4846,10 @@
         <v>4.63</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CG10" t="n">
         <v>3.33</v>
@@ -4861,13 +4861,13 @@
         <v>2.29</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CM10" t="n">
         <v>2.38</v>
@@ -4879,10 +4879,10 @@
         <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CR10" t="n">
         <v>1.34</v>
@@ -4897,106 +4897,106 @@
         <v>1.59</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY10" t="n">
         <v>1.93</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB10" t="n">
         <v>1.2</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.26000000000001</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.06</v>
+        <v>-0.12</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.4</v>
+        <v>4.44</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.53</v>
+        <v>41.5</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DP10" t="n">
-        <v>6.86</v>
+        <v>6.81</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.87</v>
+        <v>11.82</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.130000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.26</v>
+        <v>50.81</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.33</v>
+        <v>11.07</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.53</v>
+        <v>6.31</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.6</v>
+        <v>15.25</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="11">

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0.25</v>
@@ -1872,52 +1872,52 @@
         <v>1.38</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AI3" t="n">
-        <v>102.43</v>
+        <v>103.25</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AN3" t="n">
-        <v>56.71</v>
+        <v>55.38</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.57</v>
+        <v>9.25</v>
       </c>
       <c r="AR3" t="n">
-        <v>10</v>
+        <v>10.75</v>
       </c>
       <c r="AS3" t="n">
         <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>52.29</v>
+        <v>52.75</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA3" t="n">
-        <v>16.57</v>
+        <v>15.88</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.57</v>
+        <v>5.38</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.14</v>
+        <v>18.62</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.67</v>
+        <v>7.81</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>86.67</v>
+        <v>81.25</v>
       </c>
       <c r="BT3" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU3" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW3" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY3" t="n">
         <v>2.16</v>
@@ -2013,25 +2013,25 @@
         <v>2.26</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="CE3" t="n">
         <v>1.29</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="CH3" t="n">
         <v>1.53</v>
@@ -2043,139 +2043,139 @@
         <v>1.59</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO3" t="n">
         <v>1.18</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CR3" t="n">
         <v>1.35</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DB3" t="n">
         <v>1.21</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF3" t="n">
         <v>1</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="DH3" t="n">
-        <v>101.27</v>
+        <v>101.75</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="DM3" t="n">
-        <v>54.53</v>
+        <v>54</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.869999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.8</v>
+        <v>12.07</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.33</v>
+        <v>6.31</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>51</v>
+        <v>51.32</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX3" t="n">
-        <v>15</v>
+        <v>14.75</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.8</v>
+        <v>5.69</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0.12</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AI4" t="n">
-        <v>81.70999999999999</v>
+        <v>77.75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.29</v>
+        <v>-0.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN4" t="n">
-        <v>39.29</v>
+        <v>36.88</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.57</v>
+        <v>7.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.57</v>
+        <v>10.38</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>42.71</v>
+        <v>40.38</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.43</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BB4" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="BD4" t="n">
-        <v>16.43</v>
+        <v>15.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.53</v>
+        <v>3.62</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.53</v>
+        <v>10.56</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.53</v>
+        <v>3.62</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.4</v>
+        <v>5.44</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT4" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BU4" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BV4" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX4" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>4.19</v>
@@ -2416,70 +2416,70 @@
         <v>4.66</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.19</v>
+        <v>4.27</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.55</v>
+        <v>4.62</v>
       </c>
       <c r="CC4" t="n">
-        <v>5.55</v>
+        <v>5.7</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.21</v>
+        <v>6.41</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.51</v>
+        <v>3.57</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK4" t="n">
         <v>1.42</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CN4" t="n">
         <v>1.97</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CR4" t="n">
         <v>1.34</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="CT4" t="n">
         <v>3.35</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CW4" t="n">
         <v>1.62</v>
@@ -2491,94 +2491,94 @@
         <v>1.77</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DB4" t="n">
         <v>1.17</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DE4" t="n">
         <v>0.06</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="DH4" t="n">
-        <v>83.8</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.53</v>
+        <v>4.31</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.67</v>
+        <v>40.32</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.27</v>
+        <v>9.25</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.73</v>
+        <v>9.69</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44</v>
+        <v>42.75</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.8</v>
+        <v>10.37</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.13</v>
+        <v>6.88</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.4</v>
+        <v>16.88</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F5" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="G5" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="n">
-        <v>135.14</v>
+        <v>130.12</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="K5" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M5" t="n">
-        <v>60.57</v>
+        <v>58.25</v>
       </c>
       <c r="N5" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="O5" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="P5" t="n">
-        <v>11.71</v>
+        <v>12.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="R5" t="n">
-        <v>5.86</v>
+        <v>6.12</v>
       </c>
       <c r="S5" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="U5" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="V5" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>59</v>
+        <v>57.12</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.14</v>
+        <v>17.38</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.43</v>
+        <v>12.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.71</v>
+        <v>4.88</v>
       </c>
       <c r="AC5" t="n">
-        <v>22</v>
+        <v>21.12</v>
       </c>
       <c r="AD5" t="n">
         <v>1.86</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>1.38</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BN5" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.73</v>
+        <v>3.81</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.53</v>
+        <v>4.56</v>
       </c>
       <c r="BR5" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS5" t="n">
-        <v>93.33</v>
+        <v>87.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU5" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BV5" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BW5" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX5" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.34</v>
+        <v>4.29</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
       <c r="CC5" t="n">
         <v>1.67</v>
@@ -2834,28 +2834,28 @@
         <v>1.29</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CH5" t="n">
         <v>1.52</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN5" t="n">
         <v>1.84</v>
@@ -2864,22 +2864,22 @@
         <v>1.19</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV5" t="n">
         <v>2.09</v>
@@ -2888,100 +2888,100 @@
         <v>1.79</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB5" t="n">
         <v>1.22</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="DH5" t="n">
-        <v>132.2</v>
+        <v>129.87</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.8</v>
+        <v>4.88</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM5" t="n">
-        <v>59.33</v>
+        <v>58.25</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DO5" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.46</v>
+        <v>11.75</v>
       </c>
       <c r="DQ5" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.4</v>
+        <v>5.56</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>58.6</v>
+        <v>57.68</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX5" t="n">
-        <v>16.53</v>
+        <v>16.69</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.34</v>
+        <v>11.44</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.2</v>
+        <v>19.87</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>0.12</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.43</v>
+        <v>1.88</v>
       </c>
       <c r="AH6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>37.88</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BM6" t="n">
         <v>1</v>
       </c>
-      <c r="AI6" t="n">
-        <v>97.86</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>36.43</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>11.29</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>11.14</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>48.43</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.07</v>
-      </c>
       <c r="BN6" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.93</v>
+        <v>4.19</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.53</v>
+        <v>5.56</v>
       </c>
       <c r="BR6" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS6" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU6" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BV6" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BW6" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BX6" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY6" t="n">
         <v>1.54</v>
@@ -3222,25 +3222,25 @@
         <v>1.58</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.27</v>
+        <v>4.26</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.51</v>
+        <v>4.5</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="CE6" t="n">
         <v>1.24</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="CH6" t="n">
         <v>1.64</v>
@@ -3264,13 +3264,13 @@
         <v>2.03</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="CP6" t="n">
         <v>1.51</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
@@ -3285,7 +3285,7 @@
         <v>1.71</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CW6" t="n">
         <v>1.56</v>
@@ -3315,43 +3315,43 @@
         <v>0.06</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="DH6" t="n">
-        <v>104.47</v>
+        <v>104.25</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.8</v>
+        <v>4.94</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DM6" t="n">
-        <v>46.8</v>
+        <v>46.88</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DP6" t="n">
-        <v>11</v>
+        <v>11.07</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.8</v>
+        <v>12.57</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.33</v>
+        <v>7.31</v>
       </c>
       <c r="DS6" t="n">
         <v>0.06</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>52.33</v>
+        <v>52.75</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.67</v>
+        <v>14.25</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.27</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>6.4</v>
+        <v>6.12</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.87</v>
+        <v>20.82</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="EC6" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="7">
@@ -3394,61 +3394,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="F7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="G7" t="n">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="H7" t="n">
-        <v>98.56999999999999</v>
+        <v>106</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="K7" t="n">
-        <v>5.29</v>
+        <v>5.88</v>
       </c>
       <c r="L7" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="M7" t="n">
-        <v>54.43</v>
+        <v>61.25</v>
       </c>
       <c r="N7" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>9.289999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.43</v>
+        <v>9.25</v>
       </c>
       <c r="R7" t="n">
-        <v>6.29</v>
+        <v>5.88</v>
       </c>
       <c r="S7" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3460,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>56.57</v>
+        <v>59</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.86</v>
+        <v>14.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.29</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.57</v>
+        <v>6.38</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.57</v>
+        <v>16.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AF7" t="n">
         <v>0.12</v>
@@ -3565,70 +3565,70 @@
         <v>1.62</v>
       </c>
       <c r="BG7" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BI7" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.47</v>
+        <v>3.56</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.33</v>
+        <v>4.44</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT7" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BW7" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY7" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BZ7" t="n">
         <v>2.53</v>
       </c>
-      <c r="BZ7" t="n">
-        <v>2.69</v>
-      </c>
       <c r="CA7" t="n">
-        <v>3.62</v>
+        <v>3.73</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.81</v>
+        <v>3.92</v>
       </c>
       <c r="CC7" t="n">
         <v>2.53</v>
@@ -3640,16 +3640,16 @@
         <v>1.27</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.54</v>
@@ -3661,31 +3661,31 @@
         <v>1.96</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="CR7" t="n">
         <v>1.35</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="CT7" t="n">
         <v>3.34</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CV7" t="n">
         <v>2.58</v>
@@ -3694,100 +3694,100 @@
         <v>1.54</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB7" t="n">
         <v>1.19</v>
       </c>
       <c r="DC7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>111</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>51.88</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="EC7" t="n">
         <v>1.62</v>
-      </c>
-      <c r="DD7" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="DE7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DF7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>107.87</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>48.07</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>9.34</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>10.74</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>6.47</v>
-      </c>
-      <c r="DS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV7" t="n">
-        <v>56.67</v>
-      </c>
-      <c r="DW7" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DX7" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="DY7" t="n">
-        <v>7</v>
-      </c>
-      <c r="DZ7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="EA7" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="EB7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="EC7" t="n">
-        <v>1.66</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0.12</v>
@@ -3887,16 +3887,16 @@
         <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>76.29000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -3905,121 +3905,121 @@
         <v>2</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.14</v>
+        <v>4.38</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN8" t="n">
-        <v>33.14</v>
+        <v>35.75</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.71</v>
+        <v>12.25</v>
       </c>
       <c r="AR8" t="n">
-        <v>9.289999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.57</v>
+        <v>6.62</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>46.86</v>
+        <v>47.62</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.29</v>
+        <v>11.62</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.14</v>
+        <v>7.62</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.86</v>
+        <v>18.62</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.13</v>
+        <v>3.88</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.27</v>
+        <v>9.75</v>
       </c>
       <c r="BI8" t="n">
-        <v>4.13</v>
+        <v>3.88</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BN8" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.13</v>
+        <v>4.44</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.87</v>
+        <v>4.12</v>
       </c>
       <c r="BR8" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="BS8" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="BT8" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BU8" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BV8" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BW8" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BX8" t="n">
-        <v>93.33</v>
+        <v>87.5</v>
       </c>
       <c r="BY8" t="n">
         <v>2.49</v>
@@ -4028,25 +4028,25 @@
         <v>2.63</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CB8" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.36</v>
+        <v>4.2</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.56</v>
+        <v>4.38</v>
       </c>
       <c r="CE8" t="n">
         <v>1.28</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="CH8" t="n">
         <v>1.55</v>
@@ -4064,7 +4064,7 @@
         <v>1.79</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CN8" t="n">
         <v>1.98</v>
@@ -4073,10 +4073,10 @@
         <v>1.16</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="CR8" t="n">
         <v>1.33</v>
@@ -4100,97 +4100,97 @@
         <v>1.53</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.41</v>
       </c>
       <c r="DA8" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG8" t="n">
         <v>2</v>
       </c>
-      <c r="DB8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="DD8" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="DE8" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>1.8</v>
-      </c>
       <c r="DH8" t="n">
-        <v>92.47</v>
+        <v>93.56</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DK8" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DM8" t="n">
-        <v>41.53</v>
+        <v>42.32</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.46</v>
+        <v>12.25</v>
       </c>
       <c r="DQ8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DR8" t="n">
-        <v>6</v>
+        <v>6.06</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47.6</v>
+        <v>47.94</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.87</v>
+        <v>12</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.07</v>
+        <v>7.31</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.8</v>
+        <v>4.69</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.53</v>
+        <v>18.44</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="9">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -4212,82 +4212,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>91.43000000000001</v>
+        <v>91.12</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="K9" t="n">
-        <v>4.29</v>
+        <v>5.12</v>
       </c>
       <c r="L9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M9" t="n">
-        <v>41.71</v>
+        <v>42.88</v>
       </c>
       <c r="N9" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.29</v>
+        <v>2.12</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.289999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="R9" t="n">
-        <v>7.14</v>
+        <v>7.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="U9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.86</v>
+        <v>46</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.43</v>
+        <v>11.12</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.43</v>
+        <v>6.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>15.29</v>
+        <v>15.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
         <v>0.12</v>
@@ -4371,70 +4371,70 @@
         <v>2.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.67</v>
+        <v>9.19</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.93</v>
+        <v>4.25</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.67</v>
+        <v>4.88</v>
       </c>
       <c r="BR9" t="n">
-        <v>93.33</v>
+        <v>87.5</v>
       </c>
       <c r="BS9" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU9" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV9" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX9" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="CA9" t="n">
         <v>3.67</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CC9" t="n">
         <v>3.1</v>
@@ -4446,13 +4446,13 @@
         <v>1.31</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI9" t="n">
         <v>2.27</v>
@@ -4464,10 +4464,10 @@
         <v>1.47</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN9" t="n">
         <v>1.95</v>
@@ -4485,7 +4485,7 @@
         <v>1.35</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CT9" t="n">
         <v>3.32</v>
@@ -4524,76 +4524,76 @@
         <v>0.06</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="DG9" t="n">
         <v>2.94</v>
       </c>
       <c r="DH9" t="n">
-        <v>94.27</v>
+        <v>93.94</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.54</v>
+        <v>4.94</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM9" t="n">
-        <v>46.53</v>
+        <v>46.82</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.66</v>
+        <v>11.37</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.07</v>
+        <v>10</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.86</v>
+        <v>6.94</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.54</v>
+        <v>48.44</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>11</v>
+        <v>11.31</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.87</v>
+        <v>17.75</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="10">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="H11" t="n">
-        <v>83.43000000000001</v>
+        <v>83.25</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="K11" t="n">
-        <v>3.71</v>
+        <v>4.12</v>
       </c>
       <c r="L11" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="M11" t="n">
-        <v>44.43</v>
+        <v>44.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O11" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="P11" t="n">
-        <v>9.710000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.710000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>7.86</v>
+        <v>7.62</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="V11" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>45.86</v>
+        <v>45.25</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.43</v>
+        <v>13.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.140000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF11" t="n">
         <v>0.12</v>
@@ -5177,70 +5177,70 @@
         <v>1.62</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.869999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL11" t="n">
         <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.73</v>
+        <v>4.94</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.13</v>
+        <v>5.19</v>
       </c>
       <c r="BR11" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS11" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT11" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU11" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV11" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX11" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.31</v>
+        <v>3.49</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.42</v>
+        <v>3.61</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
       <c r="CC11" t="n">
         <v>3.74</v>
@@ -5252,13 +5252,13 @@
         <v>1.29</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CI11" t="n">
         <v>2.28</v>
@@ -5267,31 +5267,31 @@
         <v>1.59</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CO11" t="n">
         <v>1.19</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CR11" t="n">
         <v>1.34</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CT11" t="n">
         <v>3.34</v>
@@ -5303,7 +5303,7 @@
         <v>2.43</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CX11" t="n">
         <v>1.53</v>
@@ -5318,88 +5318,88 @@
         <v>2</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="DH11" t="n">
-        <v>90.40000000000001</v>
+        <v>89.88</v>
       </c>
       <c r="DI11" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.07</v>
+        <v>4.25</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.47</v>
+        <v>44.5</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.93</v>
+        <v>10.81</v>
       </c>
       <c r="DQ11" t="n">
-        <v>8.859999999999999</v>
+        <v>9</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.67</v>
+        <v>7.56</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>46.53</v>
+        <v>46.18</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.93</v>
+        <v>12.88</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.73</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.53</v>
+        <v>19.75</v>
       </c>
       <c r="EB11" t="n">
         <v>1.43</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>0.12</v>
@@ -5499,52 +5499,52 @@
         <v>1.25</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>91.70999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.57</v>
+        <v>3.75</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>39.71</v>
+        <v>41</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12.57</v>
+        <v>13.12</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.859999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.710000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="AT12" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>41</v>
+        <v>41.38</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.140000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.14</v>
+        <v>6.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BD12" t="n">
-        <v>20.57</v>
+        <v>21</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.8</v>
+        <v>3.06</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.6</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.8</v>
+        <v>3.06</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.2</v>
+        <v>4.12</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT12" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV12" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BX12" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY12" t="n">
         <v>3.21</v>
@@ -5640,16 +5640,16 @@
         <v>3.31</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="CB12" t="n">
         <v>4.12</v>
       </c>
       <c r="CC12" t="n">
-        <v>5.35</v>
+        <v>5.23</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="CE12" t="n">
         <v>1.3</v>
@@ -5658,7 +5658,7 @@
         <v>2.43</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CH12" t="n">
         <v>1.51</v>
@@ -5673,10 +5673,10 @@
         <v>1.41</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CN12" t="n">
         <v>2.05</v>
@@ -5712,13 +5712,13 @@
         <v>1.5</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.48</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DB12" t="n">
         <v>1.22</v>
@@ -5730,46 +5730,46 @@
         <v>2.71</v>
       </c>
       <c r="DE12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="DI12" t="n">
         <v>0.06</v>
       </c>
-      <c r="DF12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="DG12" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="DH12" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="DI12" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="DJ12" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.07</v>
+        <v>4.12</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DM12" t="n">
-        <v>43.33</v>
+        <v>43.75</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.86</v>
+        <v>13.12</v>
       </c>
       <c r="DQ12" t="n">
-        <v>8.6</v>
+        <v>8.57</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="DS12" t="n">
         <v>0.06</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.07</v>
+        <v>43.13</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.67</v>
+        <v>10.69</v>
       </c>
       <c r="DY12" t="n">
-        <v>7</v>
+        <v>7.12</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.67</v>
+        <v>3.56</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.13</v>
+        <v>21.31</v>
       </c>
       <c r="EB12" t="n">
         <v>1.25</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="13">
@@ -5812,28 +5812,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F13" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="G13" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="H13" t="n">
-        <v>91.14</v>
+        <v>92.25</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -5842,61 +5842,61 @@
         <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="M13" t="n">
-        <v>39.14</v>
+        <v>39</v>
       </c>
       <c r="N13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="P13" t="n">
-        <v>9.710000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.86</v>
+        <v>11.5</v>
       </c>
       <c r="R13" t="n">
-        <v>6.86</v>
+        <v>7</v>
       </c>
       <c r="S13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="T13" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="U13" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="V13" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>47.57</v>
+        <v>48.62</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>10.43</v>
+        <v>10.38</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.43</v>
+        <v>6.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -5983,70 +5983,70 @@
         <v>1.62</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.87</v>
+        <v>3.12</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.87</v>
+        <v>3.12</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.93</v>
+        <v>1.12</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.47</v>
+        <v>3.69</v>
       </c>
       <c r="BR13" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS13" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT13" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BU13" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BV13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BX13" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="CC13" t="n">
         <v>3.7</v>
@@ -6058,16 +6058,16 @@
         <v>1.29</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CH13" t="n">
         <v>1.53</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.59</v>
@@ -6079,7 +6079,7 @@
         <v>1.73</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CN13" t="n">
         <v>2.07</v>
@@ -6088,7 +6088,7 @@
         <v>1.19</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CQ13" t="n">
         <v>2.57</v>
@@ -6106,7 +6106,7 @@
         <v>1.56</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CW13" t="n">
         <v>1.61</v>
@@ -6115,97 +6115,97 @@
         <v>1.51</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.45</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DB13" t="n">
         <v>1.21</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD13" t="n">
         <v>2.68</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DH13" t="n">
-        <v>96.27</v>
+        <v>96.5</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.4</v>
+        <v>4.44</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.27</v>
+        <v>42.94</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.13</v>
+        <v>10.94</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.07</v>
+        <v>12.31</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.6</v>
+        <v>7.62</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.2</v>
+        <v>47.75</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.53</v>
+        <v>11.44</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.06</v>
+        <v>6.87</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.47</v>
+        <v>4.56</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.66</v>
+        <v>18.31</v>
       </c>
       <c r="EB13" t="n">
         <v>1.36</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -3926,7 +3926,7 @@
         <v>9</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.62</v>
+        <v>6.75</v>
       </c>
       <c r="AT8" t="n">
         <v>2.25</v>
@@ -3959,7 +3959,7 @@
         <v>4</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.62</v>
+        <v>18.75</v>
       </c>
       <c r="BE8" t="n">
         <v>1.27</v>
@@ -4100,13 +4100,13 @@
         <v>1.53</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.41</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DB8" t="n">
         <v>1.2</v>
@@ -4157,7 +4157,7 @@
         <v>9.619999999999999</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.06</v>
+        <v>6.12</v>
       </c>
       <c r="DS8" t="n">
         <v>0.25</v>
@@ -4184,7 +4184,7 @@
         <v>4.69</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.44</v>
+        <v>18.5</v>
       </c>
       <c r="EB8" t="n">
         <v>1.4</v>
@@ -5884,19 +5884,19 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>10.38</v>
+        <v>10.25</v>
       </c>
       <c r="AA13" t="n">
         <v>6.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.25</v>
+        <v>4.12</v>
       </c>
       <c r="AC13" t="n">
         <v>20</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -6190,13 +6190,13 @@
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.44</v>
+        <v>11.38</v>
       </c>
       <c r="DY13" t="n">
         <v>6.87</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="EA13" t="n">
         <v>18.31</v>

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="G11" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="H11" t="n">
-        <v>83.25</v>
+        <v>83</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="K11" t="n">
-        <v>4.12</v>
+        <v>3.89</v>
       </c>
       <c r="L11" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M11" t="n">
-        <v>44.5</v>
+        <v>44.11</v>
       </c>
       <c r="N11" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="O11" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="P11" t="n">
-        <v>9.619999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.880000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>7.62</v>
+        <v>8</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="T11" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>45.25</v>
+        <v>44.56</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.25</v>
+        <v>12.78</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.880000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.5</v>
+        <v>19.78</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF11" t="n">
         <v>0.12</v>
@@ -5177,70 +5177,70 @@
         <v>1.62</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="BH11" t="n">
         <v>10.12</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL11" t="n">
         <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.94</v>
+        <v>5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.19</v>
+        <v>5.12</v>
       </c>
       <c r="BR11" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS11" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU11" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BV11" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX11" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.49</v>
+        <v>3.34</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.61</v>
+        <v>3.47</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="CC11" t="n">
         <v>3.74</v>
@@ -5249,19 +5249,19 @@
         <v>3.91</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.59</v>
@@ -5270,13 +5270,13 @@
         <v>1.43</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CM11" t="n">
         <v>2.57</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CO11" t="n">
         <v>1.19</v>
@@ -5291,7 +5291,7 @@
         <v>1.34</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CT11" t="n">
         <v>3.34</v>
@@ -5318,88 +5318,88 @@
         <v>2</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="DH11" t="n">
-        <v>89.88</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="DI11" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.25</v>
+        <v>4.12</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.5</v>
+        <v>44.29</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.81</v>
+        <v>10.82</v>
       </c>
       <c r="DQ11" t="n">
         <v>9</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.56</v>
+        <v>7.76</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>46.18</v>
+        <v>45.76</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.88</v>
+        <v>12.65</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.630000000000001</v>
+        <v>8.41</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.75</v>
+        <v>19.88</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="12">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>0.25</v>
@@ -5911,43 +5911,43 @@
         <v>2</v>
       </c>
       <c r="AI13" t="n">
-        <v>100.75</v>
+        <v>104.56</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.88</v>
+        <v>4.33</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AN13" t="n">
-        <v>46.88</v>
+        <v>47.56</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.88</v>
+        <v>2.33</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.38</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.12</v>
+        <v>12.89</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.25</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>46.88</v>
+        <v>48.44</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>12.5</v>
+        <v>12.78</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.62</v>
+        <v>8</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.88</v>
+        <v>4.78</v>
       </c>
       <c r="BD13" t="n">
-        <v>16.62</v>
+        <v>17.33</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.5</v>
+        <v>8.59</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="BJ13" t="n">
         <v>1.12</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.38</v>
+        <v>3.53</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="BR13" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS13" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BU13" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BV13" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX13" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY13" t="n">
         <v>2.48</v>
@@ -6043,22 +6043,22 @@
         <v>2.65</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.85</v>
+        <v>3.77</v>
       </c>
       <c r="CE13" t="n">
         <v>1.29</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CG13" t="n">
         <v>3.3</v>
@@ -6067,7 +6067,7 @@
         <v>1.53</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.59</v>
@@ -6079,7 +6079,7 @@
         <v>1.73</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CN13" t="n">
         <v>2.07</v>
@@ -6088,16 +6088,16 @@
         <v>1.19</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CT13" t="n">
         <v>3.31</v>
@@ -6106,7 +6106,7 @@
         <v>1.56</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CW13" t="n">
         <v>1.61</v>
@@ -6115,7 +6115,7 @@
         <v>1.51</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.45</v>
@@ -6130,7 +6130,7 @@
         <v>1.69</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="DE13" t="n">
         <v>0.12</v>
@@ -6139,40 +6139,40 @@
         <v>0.88</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DH13" t="n">
-        <v>96.5</v>
+        <v>98.77</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.44</v>
+        <v>4.65</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM13" t="n">
-        <v>42.94</v>
+        <v>43.53</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.94</v>
+        <v>10.82</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.31</v>
+        <v>12.24</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.62</v>
+        <v>7.59</v>
       </c>
       <c r="DS13" t="n">
         <v>0.12</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.75</v>
+        <v>48.52</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.38</v>
+        <v>11.59</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.87</v>
+        <v>7.12</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.31</v>
+        <v>18.59</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="F2" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
       <c r="H2" t="n">
-        <v>116.38</v>
+        <v>111.11</v>
       </c>
       <c r="I2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="K2" t="n">
-        <v>6.5</v>
+        <v>6.67</v>
       </c>
       <c r="L2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M2" t="n">
-        <v>67.12</v>
+        <v>63.44</v>
       </c>
       <c r="N2" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="P2" t="n">
-        <v>10.38</v>
+        <v>10.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.62</v>
+        <v>11.22</v>
       </c>
       <c r="R2" t="n">
-        <v>4.62</v>
+        <v>5.11</v>
       </c>
       <c r="S2" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="T2" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="U2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>59.5</v>
+        <v>59.44</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.5</v>
+        <v>19.44</v>
       </c>
       <c r="AA2" t="n">
-        <v>14.12</v>
+        <v>13.33</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.38</v>
+        <v>6.11</v>
       </c>
       <c r="AC2" t="n">
-        <v>16.38</v>
+        <v>15.89</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="AE2" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AF2" t="n">
         <v>0.25</v>
@@ -1550,70 +1550,70 @@
         <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.31</v>
+        <v>9.59</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM2" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.25</v>
+        <v>5.47</v>
       </c>
       <c r="BR2" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS2" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT2" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU2" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV2" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BW2" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX2" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="CC2" t="n">
         <v>2.87</v>
@@ -1625,7 +1625,7 @@
         <v>1.29</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CG2" t="n">
         <v>3.27</v>
@@ -1634,22 +1634,22 @@
         <v>1.51</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.64</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO2" t="n">
         <v>1.2</v>
@@ -1658,7 +1658,7 @@
         <v>1.71</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CR2" t="n">
         <v>1.35</v>
@@ -1667,10 +1667,10 @@
         <v>2.56</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV2" t="n">
         <v>2.38</v>
@@ -1679,16 +1679,16 @@
         <v>1.63</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DA2" t="n">
         <v>1.9</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>1.91</v>
       </c>
       <c r="DB2" t="n">
         <v>1.22</v>
@@ -1697,82 +1697,82 @@
         <v>1.7</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="DH2" t="n">
-        <v>98.81999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="DI2" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.31</v>
+        <v>5.47</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DM2" t="n">
-        <v>57.06</v>
+        <v>55.7</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DO2" t="n">
         <v>2.82</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.19</v>
+        <v>10.41</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.62</v>
+        <v>10.94</v>
       </c>
       <c r="DR2" t="n">
-        <v>6</v>
+        <v>6.18</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>53.38</v>
+        <v>53.7</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.69</v>
+        <v>16.35</v>
       </c>
       <c r="DY2" t="n">
-        <v>11.12</v>
+        <v>10.88</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.56</v>
+        <v>5.47</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.25</v>
+        <v>16.94</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="3">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0.25</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AH5" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="AI5" t="n">
-        <v>129.62</v>
+        <v>124</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.75</v>
+        <v>4.89</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN5" t="n">
-        <v>58.25</v>
+        <v>55.11</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="BE5" t="n">
         <v>1.75</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>58.25</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>16</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>10.38</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>18.62</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.83</v>
-      </c>
       <c r="BF5" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.5</v>
+        <v>8.82</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BL5" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM5" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.81</v>
+        <v>3.88</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.56</v>
+        <v>4.82</v>
       </c>
       <c r="BR5" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS5" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU5" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV5" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BW5" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX5" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY5" t="n">
         <v>1.53</v>
@@ -2819,46 +2819,46 @@
         <v>1.53</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.29</v>
+        <v>4.24</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.58</v>
+        <v>4.53</v>
       </c>
       <c r="CC5" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="CD5" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="CE5" t="n">
         <v>1.29</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CH5" t="n">
         <v>1.52</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK5" t="n">
         <v>1.53</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CO5" t="n">
         <v>1.19</v>
@@ -2867,7 +2867,7 @@
         <v>1.65</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
@@ -2876,28 +2876,28 @@
         <v>2.52</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CU5" t="n">
         <v>1.57</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB5" t="n">
         <v>1.22</v>
@@ -2906,82 +2906,82 @@
         <v>1.71</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="DE5" t="n">
         <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="DH5" t="n">
-        <v>129.87</v>
+        <v>126.88</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.88</v>
+        <v>4.94</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="DM5" t="n">
-        <v>58.25</v>
+        <v>56.59</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DO5" t="n">
         <v>2.06</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.75</v>
+        <v>12</v>
       </c>
       <c r="DQ5" t="n">
-        <v>9.25</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.56</v>
+        <v>5.94</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>57.68</v>
+        <v>56.7</v>
       </c>
       <c r="DW5" t="n">
         <v>0.06</v>
       </c>
       <c r="DX5" t="n">
-        <v>16.69</v>
+        <v>16.29</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.44</v>
+        <v>11.18</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.25</v>
+        <v>5.12</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.87</v>
+        <v>19.82</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="F6" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="G6" t="n">
-        <v>4.62</v>
+        <v>4.22</v>
       </c>
       <c r="H6" t="n">
-        <v>110.25</v>
+        <v>109.89</v>
       </c>
       <c r="I6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="K6" t="n">
-        <v>6.62</v>
+        <v>6.56</v>
       </c>
       <c r="L6" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>55.88</v>
+        <v>55.89</v>
       </c>
       <c r="N6" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="P6" t="n">
-        <v>10.75</v>
+        <v>10.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.25</v>
+        <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>5.5</v>
+        <v>5.22</v>
       </c>
       <c r="S6" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="T6" t="n">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="U6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>55.75</v>
+        <v>56</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.88</v>
+        <v>16.67</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.25</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.62</v>
+        <v>7.78</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.88</v>
+        <v>19.22</v>
       </c>
       <c r="AD6" t="n">
         <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>2.38</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.75</v>
+        <v>9.59</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL6" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BM6" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN6" t="n">
         <v>2.06</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.19</v>
+        <v>4.24</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.56</v>
+        <v>5.35</v>
       </c>
       <c r="BR6" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS6" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU6" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BV6" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BW6" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BX6" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="CA6" t="n">
         <v>4.26</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="CC6" t="n">
         <v>2.17</v>
@@ -3237,7 +3237,7 @@
         <v>1.24</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CG6" t="n">
         <v>3.63</v>
@@ -3246,7 +3246,7 @@
         <v>1.64</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.55</v>
@@ -3255,7 +3255,7 @@
         <v>1.42</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CM6" t="n">
         <v>2.62</v>
@@ -3270,7 +3270,7 @@
         <v>1.51</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
@@ -3285,7 +3285,7 @@
         <v>1.71</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CW6" t="n">
         <v>1.56</v>
@@ -3294,13 +3294,13 @@
         <v>1.52</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.44</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DB6" t="n">
         <v>1.16</v>
@@ -3312,46 +3312,46 @@
         <v>2.28</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="DH6" t="n">
-        <v>104.25</v>
+        <v>104.41</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.94</v>
+        <v>5</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
       <c r="DM6" t="n">
-        <v>46.88</v>
+        <v>47.41</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="DO6" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.07</v>
+        <v>11.12</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.57</v>
+        <v>12.53</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.31</v>
+        <v>7.06</v>
       </c>
       <c r="DS6" t="n">
         <v>0.06</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>52.75</v>
+        <v>53.06</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.25</v>
+        <v>14.29</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.119999999999999</v>
+        <v>8</v>
       </c>
       <c r="DZ6" t="n">
-        <v>6.12</v>
+        <v>6.29</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.82</v>
+        <v>20.41</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0.38</v>
@@ -3484,52 +3484,52 @@
         <v>1.62</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AI7" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>42.5</v>
+        <v>40.56</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.380000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.88</v>
+        <v>11.89</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.62</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>56.75</v>
+        <v>55.11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA7" t="n">
-        <v>12</v>
+        <v>11.11</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.75</v>
+        <v>6.44</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.25</v>
+        <v>4.67</v>
       </c>
       <c r="BD7" t="n">
-        <v>19.12</v>
+        <v>19.22</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.12</v>
+        <v>3.29</v>
       </c>
       <c r="BH7" t="n">
-        <v>8</v>
+        <v>7.94</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.12</v>
+        <v>3.29</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.44</v>
+        <v>4.29</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT7" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU7" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BV7" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BW7" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BX7" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY7" t="n">
         <v>2.39</v>
@@ -3625,22 +3625,22 @@
         <v>2.53</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CG7" t="n">
         <v>3.5</v>
@@ -3649,22 +3649,22 @@
         <v>1.57</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.54</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL7" t="n">
         <v>1.96</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CO7" t="n">
         <v>1.16</v>
@@ -3673,13 +3673,13 @@
         <v>1.57</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CR7" t="n">
         <v>1.35</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CT7" t="n">
         <v>3.34</v>
@@ -3697,64 +3697,64 @@
         <v>1.58</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.32</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="DH7" t="n">
-        <v>111</v>
+        <v>109.71</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.13</v>
+        <v>4.88</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM7" t="n">
-        <v>51.88</v>
+        <v>50.3</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.32</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.57</v>
+        <v>10.65</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.25</v>
+        <v>6.47</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>57.88</v>
+        <v>56.94</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>13.25</v>
+        <v>12.71</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.44</v>
+        <v>7.23</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.82</v>
+        <v>5.47</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.81</v>
+        <v>17.94</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="G8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H8" t="n">
+        <v>107.56</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M8" t="n">
+        <v>50</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="P8" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="S8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
-        <v>106.62</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M8" t="n">
-        <v>48.88</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P8" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="R8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.25</v>
-      </c>
       <c r="T8" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="U8" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V8" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>48.25</v>
+        <v>49.11</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.38</v>
+        <v>12.11</v>
       </c>
       <c r="AA8" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.38</v>
+        <v>5.44</v>
       </c>
       <c r="AC8" t="n">
-        <v>18.25</v>
+        <v>18.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AF8" t="n">
         <v>0.38</v>
@@ -3968,67 +3968,67 @@
         <v>1.88</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.75</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BL8" t="n">
         <v>0.88</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="BO8" t="n">
         <v>1.94</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.44</v>
+        <v>4.53</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.12</v>
+        <v>4.06</v>
       </c>
       <c r="BR8" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS8" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT8" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BU8" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BV8" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BW8" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BX8" t="n">
-        <v>87.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="CB8" t="n">
         <v>3.97</v>
@@ -4043,10 +4043,10 @@
         <v>1.28</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="CH8" t="n">
         <v>1.55</v>
@@ -4058,16 +4058,16 @@
         <v>1.57</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CO8" t="n">
         <v>1.16</v>
@@ -4076,7 +4076,7 @@
         <v>1.62</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CR8" t="n">
         <v>1.33</v>
@@ -4100,13 +4100,13 @@
         <v>1.53</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.41</v>
       </c>
       <c r="DA8" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DB8" t="n">
         <v>1.2</v>
@@ -4118,79 +4118,79 @@
         <v>2.59</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DG8" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.56</v>
+        <v>94.83</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="DM8" t="n">
-        <v>42.32</v>
+        <v>43.29</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.25</v>
+        <v>12.12</v>
       </c>
       <c r="DQ8" t="n">
-        <v>9.619999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.12</v>
+        <v>6.06</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47.94</v>
+        <v>48.41</v>
       </c>
       <c r="DW8" t="n">
         <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>12</v>
+        <v>11.88</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.31</v>
+        <v>7.12</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.69</v>
+        <v>4.76</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.5</v>
+        <v>18.53</v>
       </c>
       <c r="EB8" t="n">
         <v>1.4</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,52 +4290,52 @@
         <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG9" t="n">
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="AI9" t="n">
-        <v>96.75</v>
+        <v>94.56</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.75</v>
+        <v>4.89</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN9" t="n">
-        <v>50.75</v>
+        <v>49.67</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.75</v>
+        <v>10.67</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.62</v>
+        <v>6.89</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>50.88</v>
+        <v>49.56</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.5</v>
+        <v>11.78</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="BD9" t="n">
-        <v>20.12</v>
+        <v>19.56</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.19</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN9" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.88</v>
+        <v>5.12</v>
       </c>
       <c r="BR9" t="n">
-        <v>87.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BT9" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU9" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV9" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX9" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY9" t="n">
         <v>2.74</v>
@@ -4431,28 +4431,28 @@
         <v>3</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CB9" t="n">
         <v>3.76</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="CE9" t="n">
         <v>1.31</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI9" t="n">
         <v>2.27</v>
@@ -4461,25 +4461,25 @@
         <v>1.59</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL9" t="n">
         <v>1.93</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO9" t="n">
         <v>1.2</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
@@ -4488,7 +4488,7 @@
         <v>2.57</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CU9" t="n">
         <v>1.54</v>
@@ -4524,13 +4524,13 @@
         <v>0.06</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="DH9" t="n">
-        <v>93.94</v>
+        <v>92.94</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
@@ -4539,28 +4539,28 @@
         <v>2.12</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.94</v>
+        <v>5</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM9" t="n">
-        <v>46.82</v>
+        <v>46.47</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="DO9" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.37</v>
+        <v>11.41</v>
       </c>
       <c r="DQ9" t="n">
         <v>10</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.94</v>
+        <v>7.06</v>
       </c>
       <c r="DS9" t="n">
         <v>0.06</v>
@@ -4572,25 +4572,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.44</v>
+        <v>47.88</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.31</v>
+        <v>11.47</v>
       </c>
       <c r="DY9" t="n">
-        <v>7</v>
+        <v>7.18</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.75</v>
+        <v>17.59</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="EC9" t="n">
         <v>2.12</v>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="G10" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="H10" t="n">
-        <v>99.75</v>
+        <v>101.89</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J10" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>5.44</v>
       </c>
       <c r="L10" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="M10" t="n">
-        <v>49</v>
+        <v>49.11</v>
       </c>
       <c r="N10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="O10" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="P10" t="n">
-        <v>6.5</v>
+        <v>6.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.38</v>
+        <v>11.44</v>
       </c>
       <c r="R10" t="n">
-        <v>8.880000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="T10" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>52.5</v>
+        <v>53.44</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>11.38</v>
+        <v>12.11</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.5</v>
+        <v>7.33</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.88</v>
+        <v>4.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>16.5</v>
+        <v>16.44</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="n">
         <v>0.25</v>
@@ -4774,70 +4774,70 @@
         <v>0.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.31</v>
+        <v>3.12</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.380000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.31</v>
+        <v>3.12</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="BO10" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BP10" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.38</v>
+        <v>4.65</v>
       </c>
       <c r="BR10" t="n">
-        <v>100</v>
+        <v>94.12</v>
       </c>
       <c r="BS10" t="n">
-        <v>93.75</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU10" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV10" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW10" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BX10" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="CC10" t="n">
         <v>4.31</v>
@@ -4846,13 +4846,13 @@
         <v>4.63</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="CH10" t="n">
         <v>1.54</v>
@@ -4870,7 +4870,7 @@
         <v>1.96</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CN10" t="n">
         <v>1.84</v>
@@ -4879,19 +4879,19 @@
         <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CR10" t="n">
         <v>1.34</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="CU10" t="n">
         <v>1.59</v>
@@ -4927,76 +4927,76 @@
         <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.68000000000001</v>
+        <v>95.17</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.44</v>
+        <v>4.71</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="DM10" t="n">
-        <v>41.5</v>
+        <v>42</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="DP10" t="n">
-        <v>6.81</v>
+        <v>7</v>
       </c>
       <c r="DQ10" t="n">
         <v>11.82</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.07</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.81</v>
+        <v>51.41</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.07</v>
+        <v>11.47</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.31</v>
+        <v>6.76</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.25</v>
+        <v>15.29</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="11">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>0.12</v>
@@ -5499,52 +5499,52 @@
         <v>1.25</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AI12" t="n">
-        <v>91.5</v>
+        <v>93.22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>41</v>
+        <v>40.67</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.75</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.75</v>
+        <v>8.67</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>41.38</v>
+        <v>41.67</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.380000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.5</v>
+        <v>6.56</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="BD12" t="n">
         <v>21</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BG12" t="n">
         <v>3.06</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.619999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="BI12" t="n">
         <v>3.06</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BO12" t="n">
         <v>1.88</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.12</v>
+        <v>4.24</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.5</v>
+        <v>5.35</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT12" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU12" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV12" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW12" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX12" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY12" t="n">
         <v>3.21</v>
@@ -5643,52 +5643,52 @@
         <v>4</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="CC12" t="n">
-        <v>5.23</v>
+        <v>5.12</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.75</v>
+        <v>5.57</v>
       </c>
       <c r="CE12" t="n">
         <v>1.3</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CK12" t="n">
         <v>1.41</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CO12" t="n">
         <v>1.2</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
@@ -5727,19 +5727,19 @@
         <v>1.7</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="DH12" t="n">
-        <v>90.75</v>
+        <v>91.7</v>
       </c>
       <c r="DI12" t="n">
         <v>0.06</v>
@@ -5748,25 +5748,25 @@
         <v>1.82</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.12</v>
+        <v>4.18</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM12" t="n">
-        <v>43.75</v>
+        <v>43.41</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.12</v>
+        <v>13.06</v>
       </c>
       <c r="DQ12" t="n">
-        <v>8.57</v>
+        <v>8.65</v>
       </c>
       <c r="DR12" t="n">
         <v>8</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.13</v>
+        <v>43.18</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.69</v>
+        <v>10.77</v>
       </c>
       <c r="DY12" t="n">
         <v>7.12</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.31</v>
+        <v>21.29</v>
       </c>
       <c r="EB12" t="n">
         <v>1.25</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="13">

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F3" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="H3" t="n">
-        <v>100.25</v>
+        <v>104.33</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="K3" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="M3" t="n">
-        <v>52.62</v>
+        <v>59.44</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
         <v>11</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.38</v>
+        <v>12.78</v>
       </c>
       <c r="R3" t="n">
-        <v>6.62</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="T3" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="U3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>49.88</v>
+        <v>51.44</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.62</v>
+        <v>14.22</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.62</v>
+        <v>8.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>6</v>
+        <v>5.78</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.38</v>
+        <v>19.56</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF3" t="n">
         <v>0.12</v>
@@ -1953,70 +1953,70 @@
         <v>1.62</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.81</v>
+        <v>8</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BV3" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW3" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX3" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.71</v>
+        <v>3.85</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.9</v>
+        <v>4.06</v>
       </c>
       <c r="CC3" t="n">
         <v>2.31</v>
@@ -2028,58 +2028,58 @@
         <v>1.29</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CK3" t="n">
         <v>1.48</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM3" t="n">
         <v>2.49</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO3" t="n">
         <v>1.18</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="CR3" t="n">
         <v>1.35</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="CT3" t="n">
         <v>3.3</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CX3" t="n">
         <v>1.57</v>
@@ -2094,55 +2094,55 @@
         <v>1.92</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF3" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="DH3" t="n">
-        <v>101.75</v>
+        <v>103.82</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.44</v>
+        <v>3.71</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DM3" t="n">
-        <v>54</v>
+        <v>57.53</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.12</v>
+        <v>10.18</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.07</v>
+        <v>11.82</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.31</v>
+        <v>6</v>
       </c>
       <c r="DS3" t="n">
         <v>0.12</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>51.32</v>
+        <v>52.06</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.75</v>
+        <v>15</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.06</v>
+        <v>9.41</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.69</v>
+        <v>5.59</v>
       </c>
       <c r="EA3" t="n">
-        <v>19</v>
+        <v>19.12</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0.12</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AI4" t="n">
-        <v>77.75</v>
+        <v>73.56</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN4" t="n">
-        <v>36.88</v>
+        <v>35.44</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.619999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.75</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.38</v>
+        <v>10.56</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>40.38</v>
+        <v>39.89</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.619999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.5</v>
+        <v>6.44</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
       <c r="BD4" t="n">
-        <v>15.5</v>
+        <v>15.22</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.56</v>
+        <v>10.59</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM4" t="n">
         <v>1.12</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.44</v>
+        <v>5.47</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT4" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BU4" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BV4" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY4" t="n">
         <v>4.19</v>
@@ -2416,37 +2416,37 @@
         <v>4.66</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.27</v>
+        <v>4.37</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.62</v>
+        <v>4.73</v>
       </c>
       <c r="CC4" t="n">
-        <v>5.7</v>
+        <v>6.13</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.41</v>
+        <v>6.81</v>
       </c>
       <c r="CE4" t="n">
         <v>1.26</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="CH4" t="n">
         <v>1.59</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL4" t="n">
         <v>1.84</v>
@@ -2455,34 +2455,34 @@
         <v>2.55</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CO4" t="n">
         <v>1.15</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CR4" t="n">
         <v>1.34</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CT4" t="n">
         <v>3.35</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CX4" t="n">
         <v>1.48</v>
@@ -2500,52 +2500,52 @@
         <v>1.17</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DE4" t="n">
         <v>0.06</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="DH4" t="n">
-        <v>81.68000000000001</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="DJ4" t="n">
         <v>1.12</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.31</v>
+        <v>4.24</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM4" t="n">
-        <v>40.32</v>
+        <v>39.35</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DO4" t="n">
         <v>1.94</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.5</v>
+        <v>9.41</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.25</v>
+        <v>9.35</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.69</v>
+        <v>9.83</v>
       </c>
       <c r="DS4" t="n">
         <v>0.06</v>
@@ -2557,25 +2557,25 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>42.75</v>
+        <v>42.35</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.37</v>
+        <v>10.41</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.88</v>
+        <v>6.82</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="EA4" t="n">
-        <v>16.88</v>
+        <v>16.65</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="EC4" t="n">
         <v>1.12</v>

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -2185,61 +2185,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F4" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="H4" t="n">
-        <v>85.62</v>
+        <v>86.33</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="K4" t="n">
-        <v>5.75</v>
+        <v>5.89</v>
       </c>
       <c r="L4" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>43.75</v>
+        <v>44.44</v>
       </c>
       <c r="N4" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="P4" t="n">
-        <v>9.380000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.75</v>
+        <v>10.22</v>
       </c>
       <c r="R4" t="n">
         <v>9</v>
       </c>
       <c r="S4" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="T4" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>45.12</v>
+        <v>45.44</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.12</v>
+        <v>11</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.25</v>
+        <v>7.22</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="AC4" t="n">
-        <v>18.25</v>
+        <v>18</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>0.78</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.59</v>
+        <v>10.72</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="BL4" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.76</v>
+        <v>4.78</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.47</v>
+        <v>5.61</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT4" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BU4" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BV4" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX4" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.19</v>
+        <v>4.11</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.66</v>
+        <v>4.62</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.73</v>
+        <v>4.71</v>
       </c>
       <c r="CC4" t="n">
         <v>6.13</v>
@@ -2434,16 +2434,16 @@
         <v>2.25</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK4" t="n">
         <v>1.43</v>
@@ -2452,13 +2452,13 @@
         <v>1.84</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CP4" t="n">
         <v>1.54</v>
@@ -2479,22 +2479,22 @@
         <v>1.68</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CX4" t="n">
         <v>1.48</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.53</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="DB4" t="n">
         <v>1.17</v>
@@ -2509,43 +2509,43 @@
         <v>0.06</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="DH4" t="n">
-        <v>79.23999999999999</v>
+        <v>79.94</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.24</v>
+        <v>4.39</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM4" t="n">
-        <v>39.35</v>
+        <v>39.94</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DO4" t="n">
         <v>1.94</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.41</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.35</v>
+        <v>9.16</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.83</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DS4" t="n">
         <v>0.06</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>42.35</v>
+        <v>42.66</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.41</v>
+        <v>10.39</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="EA4" t="n">
-        <v>16.65</v>
+        <v>16.61</v>
       </c>
       <c r="EB4" t="n">
         <v>1.19</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="5">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0.11</v>
@@ -3887,139 +3887,139 @@
         <v>1.56</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AI8" t="n">
-        <v>80.5</v>
+        <v>82.89</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.38</v>
+        <v>4.56</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN8" t="n">
-        <v>35.75</v>
+        <v>39</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.25</v>
+        <v>11.56</v>
       </c>
       <c r="AR8" t="n">
-        <v>9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.75</v>
+        <v>6.44</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>47.62</v>
+        <v>48.11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.62</v>
+        <v>11.67</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.62</v>
+        <v>7.44</v>
       </c>
       <c r="BC8" t="n">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.75</v>
+        <v>18.89</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.710000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BM8" t="n">
         <v>1</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.53</v>
+        <v>4.56</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.06</v>
+        <v>4.28</v>
       </c>
       <c r="BR8" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS8" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT8" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BU8" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BV8" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BW8" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BX8" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BY8" t="n">
         <v>2.41</v>
@@ -4028,16 +4028,16 @@
         <v>2.54</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.2</v>
+        <v>3.93</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.38</v>
+        <v>4.09</v>
       </c>
       <c r="CE8" t="n">
         <v>1.28</v>
@@ -4046,10 +4046,10 @@
         <v>2.34</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CI8" t="n">
         <v>2.32</v>
@@ -4058,16 +4058,16 @@
         <v>1.57</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL8" t="n">
         <v>1.8</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CO8" t="n">
         <v>1.16</v>
@@ -4091,7 +4091,7 @@
         <v>1.59</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CW8" t="n">
         <v>1.57</v>
@@ -4100,97 +4100,97 @@
         <v>1.53</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.41</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DC8" t="n">
         <v>1.64</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DH8" t="n">
-        <v>94.83</v>
+        <v>95.22</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="DK8" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM8" t="n">
-        <v>43.29</v>
+        <v>44.5</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.12</v>
+        <v>11.78</v>
       </c>
       <c r="DQ8" t="n">
-        <v>9.76</v>
+        <v>9.66</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.06</v>
+        <v>5.94</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.41</v>
+        <v>48.61</v>
       </c>
       <c r="DW8" t="n">
         <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.88</v>
+        <v>11.89</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.12</v>
+        <v>7.06</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.76</v>
+        <v>4.83</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.53</v>
+        <v>18.61</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="9">

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0.44</v>
@@ -1469,139 +1469,139 @@
         <v>1.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AI2" t="n">
-        <v>81.25</v>
+        <v>81.78</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AN2" t="n">
-        <v>47</v>
+        <v>46.56</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.62</v>
+        <v>11.33</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.38</v>
+        <v>7.78</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>47.25</v>
+        <v>47.56</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.88</v>
+        <v>12.78</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.119999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.75</v>
+        <v>4.78</v>
       </c>
       <c r="BD2" t="n">
-        <v>18.12</v>
+        <v>18.11</v>
       </c>
       <c r="BE2" t="n">
         <v>1.48</v>
       </c>
       <c r="BF2" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="BG2" t="n">
         <v>3</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.59</v>
+        <v>9.44</v>
       </c>
       <c r="BI2" t="n">
         <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="BP2" t="n">
         <v>4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.47</v>
+        <v>5.33</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS2" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT2" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU2" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX2" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY2" t="n">
         <v>1.9</v>
@@ -1610,25 +1610,25 @@
         <v>1.9</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF2" t="n">
         <v>2.47</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CH2" t="n">
         <v>1.51</v>
@@ -1637,19 +1637,19 @@
         <v>2.23</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CO2" t="n">
         <v>1.2</v>
@@ -1658,7 +1658,7 @@
         <v>1.71</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CR2" t="n">
         <v>1.35</v>
@@ -1679,13 +1679,13 @@
         <v>1.63</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA2" t="n">
         <v>1.9</v>
@@ -1694,85 +1694,85 @@
         <v>1.22</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="DH2" t="n">
-        <v>97.06</v>
+        <v>96.44</v>
       </c>
       <c r="DI2" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.47</v>
+        <v>5.39</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>55.7</v>
+        <v>55</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.41</v>
+        <v>10.56</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.94</v>
+        <v>11.27</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.18</v>
+        <v>6.44</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>53.7</v>
+        <v>53.5</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.35</v>
+        <v>16.11</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.88</v>
+        <v>10.66</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.47</v>
+        <v>5.44</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.94</v>
+        <v>17</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="H5" t="n">
-        <v>130.12</v>
+        <v>132.44</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="J5" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="L5" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>58.25</v>
+        <v>58.11</v>
       </c>
       <c r="N5" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="O5" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="P5" t="n">
-        <v>12.25</v>
+        <v>11.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.5</v>
+        <v>9.56</v>
       </c>
       <c r="R5" t="n">
-        <v>6.12</v>
+        <v>5.89</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>57.12</v>
+        <v>57.78</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.38</v>
+        <v>17.67</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.5</v>
+        <v>12.78</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.12</v>
+        <v>20.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>1.67</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.82</v>
+        <v>9</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.82</v>
+        <v>4.89</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS5" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT5" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU5" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV5" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW5" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX5" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.24</v>
+        <v>4.23</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.53</v>
+        <v>4.52</v>
       </c>
       <c r="CC5" t="n">
         <v>1.79</v>
@@ -2834,10 +2834,10 @@
         <v>1.29</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CH5" t="n">
         <v>1.52</v>
@@ -2852,7 +2852,7 @@
         <v>1.53</v>
       </c>
       <c r="CL5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CM5" t="n">
         <v>2.34</v>
@@ -2861,10 +2861,10 @@
         <v>1.83</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CQ5" t="n">
         <v>2.67</v>
@@ -2873,19 +2873,19 @@
         <v>1.36</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CU5" t="n">
         <v>1.57</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX5" t="n">
         <v>1.57</v>
@@ -2903,85 +2903,85 @@
         <v>1.22</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="DH5" t="n">
-        <v>126.88</v>
+        <v>128.22</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.94</v>
+        <v>5.11</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM5" t="n">
-        <v>56.59</v>
+        <v>56.61</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DP5" t="n">
-        <v>12</v>
+        <v>11.78</v>
       </c>
       <c r="DQ5" t="n">
-        <v>9.529999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.94</v>
+        <v>5.84</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.7</v>
+        <v>57.06</v>
       </c>
       <c r="DW5" t="n">
         <v>0.06</v>
       </c>
       <c r="DX5" t="n">
-        <v>16.29</v>
+        <v>16.5</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.18</v>
+        <v>11.39</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.82</v>
+        <v>19.73</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0.33</v>
@@ -3084,49 +3084,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="AI6" t="n">
-        <v>98.25</v>
+        <v>97.67</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.25</v>
+        <v>3.89</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>37.88</v>
+        <v>40.78</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AP6" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.38</v>
+        <v>11.67</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.88</v>
+        <v>11.44</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.119999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>49.75</v>
+        <v>51</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.62</v>
+        <v>12.44</v>
       </c>
       <c r="BB6" t="n">
-        <v>7</v>
+        <v>7.78</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.62</v>
+        <v>4.67</v>
       </c>
       <c r="BD6" t="n">
-        <v>21.75</v>
+        <v>21.78</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.71</v>
+        <v>3.83</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.59</v>
+        <v>9.67</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.71</v>
+        <v>3.83</v>
       </c>
       <c r="BJ6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BM6" t="n">
         <v>1.06</v>
       </c>
-      <c r="BK6" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0.9399999999999999</v>
-      </c>
       <c r="BN6" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.24</v>
+        <v>4.17</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS6" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT6" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU6" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BV6" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BW6" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BX6" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY6" t="n">
         <v>1.56</v>
@@ -3222,16 +3222,16 @@
         <v>1.61</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="CE6" t="n">
         <v>1.24</v>
@@ -3240,7 +3240,7 @@
         <v>2.17</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CH6" t="n">
         <v>1.64</v>
@@ -3252,16 +3252,16 @@
         <v>1.55</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL6" t="n">
         <v>1.8</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CO6" t="n">
         <v>1.14</v>
@@ -3270,22 +3270,22 @@
         <v>1.51</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CT6" t="n">
         <v>3.21</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CW6" t="n">
         <v>1.56</v>
@@ -3300,58 +3300,58 @@
         <v>2.44</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="DB6" t="n">
         <v>1.16</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="DH6" t="n">
-        <v>104.41</v>
+        <v>103.78</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="DK6" t="n">
-        <v>5</v>
+        <v>5.22</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="DM6" t="n">
-        <v>47.41</v>
+        <v>48.34</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.12</v>
+        <v>11.28</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.53</v>
+        <v>12.72</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.06</v>
+        <v>7</v>
       </c>
       <c r="DS6" t="n">
         <v>0.06</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>53.06</v>
+        <v>53.5</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.29</v>
+        <v>14.56</v>
       </c>
       <c r="DY6" t="n">
-        <v>8</v>
+        <v>8.34</v>
       </c>
       <c r="DZ6" t="n">
-        <v>6.29</v>
+        <v>6.22</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.41</v>
+        <v>20.5</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F7" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="G7" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>106</v>
+        <v>108.56</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="J7" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="K7" t="n">
-        <v>5.88</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>61.25</v>
+        <v>63.56</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="O7" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>9.25</v>
+        <v>9.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.25</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>59</v>
+        <v>59.44</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.5</v>
+        <v>14.78</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.119999999999999</v>
+        <v>8</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.38</v>
+        <v>6.78</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="AF7" t="n">
         <v>0.11</v>
@@ -3565,70 +3565,70 @@
         <v>1.67</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.29</v>
+        <v>3.39</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.94</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.29</v>
+        <v>3.39</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL7" t="n">
         <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.65</v>
+        <v>3.83</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT7" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BV7" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BW7" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BX7" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="CC7" t="n">
         <v>2.69</v>
@@ -3640,16 +3640,16 @@
         <v>1.26</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="CH7" t="n">
         <v>1.57</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.54</v>
@@ -3670,124 +3670,124 @@
         <v>1.16</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CR7" t="n">
         <v>1.35</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CT7" t="n">
         <v>3.34</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB7" t="n">
         <v>1.18</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DH7" t="n">
-        <v>109.71</v>
+        <v>110.78</v>
       </c>
       <c r="DI7" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="DM7" t="n">
-        <v>50.3</v>
+        <v>52.06</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.470000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.65</v>
+        <v>10.34</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.47</v>
+        <v>6.39</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>56.94</v>
+        <v>57.28</v>
       </c>
       <c r="DW7" t="n">
         <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.71</v>
+        <v>12.94</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.23</v>
+        <v>7.22</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.47</v>
+        <v>5.72</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.94</v>
+        <v>17.61</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="8">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
@@ -4212,82 +4212,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="H9" t="n">
-        <v>91.12</v>
+        <v>93.67</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="K9" t="n">
-        <v>5.12</v>
+        <v>4.89</v>
       </c>
       <c r="L9" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="M9" t="n">
-        <v>42.88</v>
+        <v>44.44</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="O9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="P9" t="n">
-        <v>9.619999999999999</v>
+        <v>10.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.25</v>
+        <v>9.67</v>
       </c>
       <c r="R9" t="n">
-        <v>7.25</v>
+        <v>6.89</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="U9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>46</v>
+        <v>46.44</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.12</v>
+        <v>11.56</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.25</v>
+        <v>6.78</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.88</v>
+        <v>4.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>15.38</v>
+        <v>15.11</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
         <v>0.11</v>
@@ -4371,70 +4371,70 @@
         <v>2.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.529999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="BR9" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS9" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BT9" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU9" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV9" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX9" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="CC9" t="n">
         <v>3.04</v>
@@ -4464,13 +4464,13 @@
         <v>1.48</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CM9" t="n">
         <v>2.5</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO9" t="n">
         <v>1.2</v>
@@ -4479,7 +4479,7 @@
         <v>1.69</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
@@ -4506,10 +4506,10 @@
         <v>1.86</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DB9" t="n">
         <v>1.22</v>
@@ -4518,49 +4518,49 @@
         <v>1.72</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="DE9" t="n">
         <v>0.06</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="DH9" t="n">
-        <v>92.94</v>
+        <v>94.12</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="DK9" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DM9" t="n">
-        <v>46.47</v>
+        <v>47.06</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.41</v>
+        <v>11.72</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10</v>
+        <v>10.17</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.06</v>
+        <v>6.89</v>
       </c>
       <c r="DS9" t="n">
         <v>0.06</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47.88</v>
+        <v>48</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.47</v>
+        <v>11.67</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.18</v>
+        <v>7.39</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.59</v>
+        <v>17.33</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,139 +4693,139 @@
         <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AH10" t="n">
         <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>87.62</v>
+        <v>85.33</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN10" t="n">
-        <v>34</v>
+        <v>33.89</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.12</v>
+        <v>7</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.25</v>
+        <v>12.11</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.25</v>
+        <v>7.33</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>49.12</v>
+        <v>47.78</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.75</v>
+        <v>10.89</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.12</v>
+        <v>6.44</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.62</v>
+        <v>4.44</v>
       </c>
       <c r="BD10" t="n">
-        <v>14</v>
+        <v>14.22</v>
       </c>
       <c r="BE10" t="n">
         <v>1.25</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.710000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.06</v>
+        <v>5.17</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.65</v>
+        <v>4.61</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS10" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT10" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU10" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BV10" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BW10" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BX10" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY10" t="n">
         <v>2.8</v>
@@ -4834,31 +4834,31 @@
         <v>2.89</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.99</v>
+        <v>4.03</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.31</v>
+        <v>4.27</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.63</v>
+        <v>4.62</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="CH10" t="n">
         <v>1.54</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.58</v>
@@ -4882,25 +4882,25 @@
         <v>1.62</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CR10" t="n">
         <v>1.34</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="CT10" t="n">
         <v>3.36</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CX10" t="n">
         <v>1.54</v>
@@ -4909,7 +4909,7 @@
         <v>1.93</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA10" t="n">
         <v>1.88</v>
@@ -4918,52 +4918,52 @@
         <v>1.2</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DH10" t="n">
-        <v>95.17</v>
+        <v>93.61</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.11</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.71</v>
+        <v>4.66</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="DM10" t="n">
-        <v>42</v>
+        <v>41.5</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DP10" t="n">
-        <v>7</v>
+        <v>6.94</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.82</v>
+        <v>11.77</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.289999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="DS10" t="n">
         <v>0.11</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>51.41</v>
+        <v>50.61</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.47</v>
+        <v>11.5</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.76</v>
+        <v>6.89</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.7</v>
+        <v>4.61</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.29</v>
+        <v>15.33</v>
       </c>
       <c r="EB10" t="n">
         <v>1.36</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>0.33</v>
@@ -5096,139 +5096,139 @@
         <v>1.33</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AI11" t="n">
-        <v>96.5</v>
+        <v>94.22</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>44.5</v>
+        <v>41.44</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AP11" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12</v>
+        <v>11.78</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.119999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.5</v>
+        <v>8.33</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>47.12</v>
+        <v>46</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.5</v>
+        <v>12.11</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.380000000000001</v>
+        <v>7.78</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.12</v>
+        <v>4.33</v>
       </c>
       <c r="BD11" t="n">
-        <v>20</v>
+        <v>19.56</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.12</v>
+        <v>10.22</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="BL11" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BP11" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.12</v>
+        <v>5.17</v>
       </c>
       <c r="BR11" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS11" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT11" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU11" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV11" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX11" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY11" t="n">
         <v>3.34</v>
@@ -5237,46 +5237,46 @@
         <v>3.47</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="CB11" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="CC11" t="n">
         <v>3.94</v>
       </c>
-      <c r="CC11" t="n">
-        <v>3.74</v>
-      </c>
       <c r="CD11" t="n">
-        <v>3.91</v>
+        <v>4.07</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="CH11" t="n">
         <v>1.52</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CO11" t="n">
         <v>1.19</v>
@@ -5285,13 +5285,13 @@
         <v>1.64</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CR11" t="n">
         <v>1.34</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CT11" t="n">
         <v>3.34</v>
@@ -5300,10 +5300,10 @@
         <v>1.59</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX11" t="n">
         <v>1.53</v>
@@ -5321,85 +5321,85 @@
         <v>1.21</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DD11" t="n">
         <v>2.63</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="DH11" t="n">
-        <v>89.34999999999999</v>
+        <v>88.61</v>
       </c>
       <c r="DI11" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.29</v>
+        <v>42.78</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.82</v>
+        <v>10.78</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9</v>
+        <v>8.94</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.76</v>
+        <v>8.16</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>45.76</v>
+        <v>45.28</v>
       </c>
       <c r="DW11" t="n">
         <v>0.11</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.65</v>
+        <v>12.44</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.41</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.23</v>
+        <v>4.33</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.88</v>
+        <v>19.67</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F13" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="H13" t="n">
-        <v>92.25</v>
+        <v>89.67</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="L13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M13" t="n">
-        <v>39</v>
+        <v>39.56</v>
       </c>
       <c r="N13" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>9.5</v>
+        <v>10.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.5</v>
+        <v>11.78</v>
       </c>
       <c r="R13" t="n">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="S13" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="U13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>48.62</v>
+        <v>47.56</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>10.25</v>
+        <v>10.22</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.12</v>
+        <v>6.22</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="AC13" t="n">
-        <v>20</v>
+        <v>19.22</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>1.56</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.18</v>
+        <v>3.33</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.59</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.18</v>
+        <v>3.33</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.71</v>
+        <v>3.94</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS13" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BU13" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BV13" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.88</v>
+        <v>11.11</v>
       </c>
       <c r="BX13" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.88</v>
+        <v>3.91</v>
       </c>
       <c r="CC13" t="n">
         <v>3.63</v>
@@ -6058,7 +6058,7 @@
         <v>1.29</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CG13" t="n">
         <v>3.3</v>
@@ -6079,7 +6079,7 @@
         <v>1.73</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CN13" t="n">
         <v>2.07</v>
@@ -6091,13 +6091,13 @@
         <v>1.64</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CT13" t="n">
         <v>3.31</v>
@@ -6106,7 +6106,7 @@
         <v>1.56</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CW13" t="n">
         <v>1.61</v>
@@ -6115,13 +6115,13 @@
         <v>1.51</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.45</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DB13" t="n">
         <v>1.21</v>
@@ -6130,82 +6130,82 @@
         <v>1.69</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="DH13" t="n">
-        <v>98.77</v>
+        <v>97.12</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.53</v>
+        <v>43.56</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.82</v>
+        <v>11.11</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.24</v>
+        <v>12.34</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.59</v>
+        <v>7.72</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.52</v>
+        <v>48</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.59</v>
+        <v>11.5</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.12</v>
+        <v>7.11</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.47</v>
+        <v>4.39</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.59</v>
+        <v>18.27</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>0.22</v>
@@ -1872,52 +1872,52 @@
         <v>1.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.12</v>
+        <v>1.56</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>103.25</v>
+        <v>102.78</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.88</v>
+        <v>2.44</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN3" t="n">
-        <v>55.38</v>
+        <v>55.11</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.25</v>
+        <v>9.56</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.75</v>
+        <v>11.44</v>
       </c>
       <c r="AS3" t="n">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>52.75</v>
+        <v>53.78</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="BA3" t="n">
-        <v>15.88</v>
+        <v>15.33</v>
       </c>
       <c r="BB3" t="n">
-        <v>10.5</v>
+        <v>10.33</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.38</v>
+        <v>5</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.62</v>
+        <v>19.11</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BH3" t="n">
-        <v>8</v>
+        <v>7.89</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT3" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV3" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX3" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY3" t="n">
         <v>2.06</v>
@@ -2013,43 +2013,43 @@
         <v>2.15</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="CE3" t="n">
         <v>1.29</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.61</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL3" t="n">
         <v>1.89</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CN3" t="n">
         <v>1.93</v>
@@ -2058,10 +2058,10 @@
         <v>1.18</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="CR3" t="n">
         <v>1.35</v>
@@ -2070,13 +2070,13 @@
         <v>2.48</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CW3" t="n">
         <v>1.62</v>
@@ -2094,88 +2094,88 @@
         <v>1.92</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="DG3" t="n">
         <v>2</v>
       </c>
       <c r="DH3" t="n">
-        <v>103.82</v>
+        <v>103.56</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.71</v>
+        <v>3.78</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="DM3" t="n">
-        <v>57.53</v>
+        <v>57.28</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.18</v>
+        <v>10.28</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.82</v>
+        <v>12.11</v>
       </c>
       <c r="DR3" t="n">
-        <v>6</v>
+        <v>5.94</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>52.06</v>
+        <v>52.61</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="DX3" t="n">
-        <v>15</v>
+        <v>14.77</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.41</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.59</v>
+        <v>5.39</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.12</v>
+        <v>19.33</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="4">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.88</v>
+        <v>1.22</v>
       </c>
       <c r="G12" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="H12" t="n">
-        <v>90</v>
+        <v>90.11</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="K12" t="n">
-        <v>4.5</v>
+        <v>4.11</v>
       </c>
       <c r="L12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M12" t="n">
-        <v>46.5</v>
+        <v>43.33</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>13.12</v>
+        <v>13.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.380000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="R12" t="n">
-        <v>7.25</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T12" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="U12" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="V12" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>44.88</v>
+        <v>44.11</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>12</v>
+        <v>11.44</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.75</v>
+        <v>7.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AC12" t="n">
-        <v>21.62</v>
+        <v>21.89</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
         <v>0.11</v>
@@ -5583,67 +5583,67 @@
         <v>3.06</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.59</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI12" t="n">
         <v>3.06</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.35</v>
+        <v>5.17</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT12" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU12" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV12" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW12" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX12" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.21</v>
+        <v>3.34</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.31</v>
+        <v>3.42</v>
       </c>
       <c r="CA12" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="CC12" t="n">
         <v>5.12</v>
@@ -5655,22 +5655,22 @@
         <v>1.3</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI12" t="n">
         <v>2.18</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL12" t="n">
         <v>1.82</v>
@@ -5679,16 +5679,16 @@
         <v>2.7</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO12" t="n">
         <v>1.2</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
@@ -5697,7 +5697,7 @@
         <v>2.57</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CU12" t="n">
         <v>1.54</v>
@@ -5727,82 +5727,82 @@
         <v>1.7</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="DE12" t="n">
         <v>0.11</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="DH12" t="n">
-        <v>91.7</v>
+        <v>91.66</v>
       </c>
       <c r="DI12" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM12" t="n">
-        <v>43.41</v>
+        <v>42</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.06</v>
+        <v>13.28</v>
       </c>
       <c r="DQ12" t="n">
-        <v>8.65</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DR12" t="n">
-        <v>8</v>
+        <v>8.44</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.18</v>
+        <v>42.89</v>
       </c>
       <c r="DW12" t="n">
         <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.77</v>
+        <v>10.56</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.12</v>
+        <v>7</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.29</v>
+        <v>21.44</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="13">

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -1400,10 +1400,10 @@
         <v>111.11</v>
       </c>
       <c r="I2" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="J2" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="K2" t="n">
         <v>6.67</v>
@@ -1415,7 +1415,7 @@
         <v>63.44</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="O2" t="n">
         <v>3.33</v>
@@ -1466,7 +1466,7 @@
         <v>2.11</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AF2" t="n">
         <v>0.22</v>
@@ -1712,10 +1712,10 @@
         <v>96.44</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="DK2" t="n">
         <v>5.39</v>
@@ -1727,7 +1727,7 @@
         <v>55</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="DO2" t="n">
         <v>2.78</v>
@@ -1772,7 +1772,7 @@
         <v>1.8</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="3">
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AH6" t="n">
         <v>1.78</v>
@@ -3096,7 +3096,7 @@
         <v>0.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AL6" t="n">
         <v>3.89</v>
@@ -3159,7 +3159,7 @@
         <v>1.41</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="BG6" t="n">
         <v>3.83</v>
@@ -3315,7 +3315,7 @@
         <v>0.16</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DG6" t="n">
         <v>3</v>
@@ -3327,7 +3327,7 @@
         <v>0.16</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="DK6" t="n">
         <v>5.22</v>
@@ -3384,7 +3384,7 @@
         <v>1.7</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="7">
@@ -5018,7 +5018,7 @@
         <v>0.33</v>
       </c>
       <c r="F11" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="G11" t="n">
         <v>2.33</v>
@@ -5030,7 +5030,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="K11" t="n">
         <v>3.89</v>
@@ -5093,7 +5093,7 @@
         <v>1.43</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AF11" t="n">
         <v>0.11</v>
@@ -5330,7 +5330,7 @@
         <v>0.22</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="DG11" t="n">
         <v>2.22</v>
@@ -5342,7 +5342,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="DK11" t="n">
         <v>4.11</v>
@@ -5399,7 +5399,7 @@
         <v>1.4</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="12">

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="G2" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="H2" t="n">
-        <v>111.11</v>
+        <v>116.4</v>
       </c>
       <c r="I2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="J2" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="K2" t="n">
-        <v>6.67</v>
+        <v>6.9</v>
       </c>
       <c r="L2" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="M2" t="n">
-        <v>63.44</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="O2" t="n">
-        <v>3.33</v>
+        <v>3.7</v>
       </c>
       <c r="P2" t="n">
-        <v>10.78</v>
+        <v>10.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.22</v>
+        <v>11.8</v>
       </c>
       <c r="R2" t="n">
-        <v>5.11</v>
+        <v>4.8</v>
       </c>
       <c r="S2" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="T2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>59.44</v>
+        <v>60</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.44</v>
+        <v>19.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>13.33</v>
+        <v>12.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.11</v>
+        <v>6.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>15.89</v>
+        <v>16.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF2" t="n">
         <v>0.22</v>
@@ -1553,67 +1553,67 @@
         <v>3</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.44</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI2" t="n">
         <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BP2" t="n">
-        <v>4</v>
+        <v>4.21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.33</v>
+        <v>5.16</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT2" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU2" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV2" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX2" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CA2" t="n">
         <v>3.75</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="CC2" t="n">
         <v>2.78</v>
@@ -1634,7 +1634,7 @@
         <v>1.51</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.63</v>
@@ -1643,7 +1643,7 @@
         <v>1.5</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM2" t="n">
         <v>2.41</v>
@@ -1655,10 +1655,10 @@
         <v>1.2</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CR2" t="n">
         <v>1.35</v>
@@ -1670,13 +1670,13 @@
         <v>3.3</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CX2" t="n">
         <v>1.54</v>
@@ -1685,10 +1685,10 @@
         <v>1.9</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DB2" t="n">
         <v>1.22</v>
@@ -1700,46 +1700,46 @@
         <v>2.74</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="DH2" t="n">
-        <v>96.44</v>
+        <v>100</v>
       </c>
       <c r="DI2" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.39</v>
+        <v>5.58</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="DM2" t="n">
-        <v>55</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.56</v>
+        <v>10.31</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.27</v>
+        <v>11.58</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.44</v>
+        <v>6.21</v>
       </c>
       <c r="DS2" t="n">
         <v>0.16</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>53.5</v>
+        <v>54.11</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.11</v>
+        <v>16.16</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.66</v>
+        <v>10.53</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.44</v>
+        <v>5.63</v>
       </c>
       <c r="EA2" t="n">
-        <v>17</v>
+        <v>17.47</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G3" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="H3" t="n">
-        <v>104.33</v>
+        <v>103.4</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>59.44</v>
+        <v>60.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.78</v>
+        <v>12.9</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="S3" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="U3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>51.44</v>
+        <v>51.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.22</v>
+        <v>13.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.44</v>
+        <v>8.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.78</v>
+        <v>5.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.56</v>
+        <v>19.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AF3" t="n">
         <v>0.11</v>
@@ -1953,70 +1953,70 @@
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.89</v>
+        <v>8.16</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.83</v>
+        <v>4.05</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="BR3" t="n">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU3" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV3" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX3" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="CC3" t="n">
         <v>2.24</v>
@@ -2028,19 +2028,19 @@
         <v>1.29</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="CH3" t="n">
         <v>1.53</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK3" t="n">
         <v>1.47</v>
@@ -2058,37 +2058,37 @@
         <v>1.18</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CR3" t="n">
         <v>1.35</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY3" t="n">
         <v>1.9</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DA3" t="n">
         <v>1.92</v>
@@ -2097,52 +2097,52 @@
         <v>1.21</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="DE3" t="n">
         <v>0.16</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="DG3" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DH3" t="n">
-        <v>103.56</v>
+        <v>103.11</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="DM3" t="n">
-        <v>57.28</v>
+        <v>57.84</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.28</v>
+        <v>10.37</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.11</v>
+        <v>12.21</v>
       </c>
       <c r="DR3" t="n">
-        <v>5.94</v>
+        <v>6.16</v>
       </c>
       <c r="DS3" t="n">
         <v>0.11</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>52.61</v>
+        <v>52.63</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.77</v>
+        <v>14.58</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.380000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.39</v>
+        <v>5.21</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.33</v>
+        <v>19.53</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0.11</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AH4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>45</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BK4" t="n">
         <v>0.89</v>
       </c>
-      <c r="AI4" t="n">
-        <v>73.56</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>35.44</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>10.56</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>39.89</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>15.22</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>10.72</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.78</v>
-      </c>
       <c r="BL4" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.78</v>
+        <v>5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.61</v>
+        <v>5.58</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BU4" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BV4" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX4" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY4" t="n">
         <v>4.11</v>
@@ -2416,55 +2416,55 @@
         <v>4.62</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.35</v>
+        <v>4.31</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.71</v>
+        <v>4.65</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.13</v>
+        <v>5.84</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.81</v>
+        <v>6.49</v>
       </c>
       <c r="CE4" t="n">
         <v>1.26</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK4" t="n">
         <v>1.43</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CM4" t="n">
         <v>2.57</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CO4" t="n">
         <v>1.16</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="CR4" t="n">
         <v>1.34</v>
@@ -2479,10 +2479,10 @@
         <v>1.68</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CX4" t="n">
         <v>1.48</v>
@@ -2500,85 +2500,85 @@
         <v>1.17</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="DH4" t="n">
-        <v>79.94</v>
+        <v>80</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.16</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DM4" t="n">
-        <v>39.94</v>
+        <v>44.73</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.380000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.16</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.779999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>42.66</v>
+        <v>42.26</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.39</v>
+        <v>10.26</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.83</v>
+        <v>6.58</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.56</v>
+        <v>3.69</v>
       </c>
       <c r="EA4" t="n">
-        <v>16.61</v>
+        <v>16.74</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0.22</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>124</v>
+        <v>120.2</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.89</v>
+        <v>5.1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AN5" t="n">
-        <v>55.11</v>
+        <v>53.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.78</v>
+        <v>12.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.56</v>
+        <v>10.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>56.33</v>
+        <v>55</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>15.33</v>
+        <v>15.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.33</v>
+        <v>5.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>18.67</v>
+        <v>19.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="BG5" t="n">
         <v>3.11</v>
       </c>
       <c r="BH5" t="n">
-        <v>9</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI5" t="n">
         <v>3.11</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="BM5" t="n">
         <v>0.89</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BP5" t="n">
         <v>4</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.89</v>
+        <v>5</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT5" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU5" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV5" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW5" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX5" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY5" t="n">
         <v>1.54</v>
@@ -2819,22 +2819,22 @@
         <v>1.54</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.23</v>
+        <v>4.2</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.52</v>
+        <v>4.48</v>
       </c>
       <c r="CC5" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="CD5" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="CE5" t="n">
         <v>1.29</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CG5" t="n">
         <v>3.28</v>
@@ -2843,10 +2843,10 @@
         <v>1.52</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK5" t="n">
         <v>1.53</v>
@@ -2855,19 +2855,19 @@
         <v>1.99</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CN5" t="n">
         <v>1.83</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP5" t="n">
         <v>1.66</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
@@ -2882,19 +2882,19 @@
         <v>1.57</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA5" t="n">
         <v>1.87</v>
@@ -2906,82 +2906,82 @@
         <v>1.7</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF5" t="n">
         <v>1.16</v>
       </c>
       <c r="DG5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="DH5" t="n">
-        <v>128.22</v>
+        <v>126</v>
       </c>
       <c r="DI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.11</v>
+        <v>5.21</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DM5" t="n">
-        <v>56.61</v>
+        <v>55.63</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.78</v>
+        <v>12</v>
       </c>
       <c r="DQ5" t="n">
-        <v>9.56</v>
+        <v>10</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.84</v>
+        <v>5.79</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>57.06</v>
+        <v>56.32</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX5" t="n">
-        <v>16.5</v>
+        <v>16.42</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.39</v>
+        <v>11.42</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.73</v>
+        <v>20.21</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F6" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="H6" t="n">
-        <v>109.89</v>
+        <v>109.9</v>
       </c>
       <c r="I6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J6" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="K6" t="n">
-        <v>6.56</v>
+        <v>6.3</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>55.89</v>
+        <v>54</v>
       </c>
       <c r="N6" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="P6" t="n">
-        <v>10.89</v>
+        <v>11.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="R6" t="n">
-        <v>5.22</v>
+        <v>5.6</v>
       </c>
       <c r="S6" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T6" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="U6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.890000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.78</v>
+        <v>7.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.22</v>
+        <v>18.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>2.44</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.67</v>
+        <v>9.74</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL6" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BN6" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="BO6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>94.73999999999999</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>89.47</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>63.16</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>47.37</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>36.84</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>36.84</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>63.16</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BZ6" t="n">
         <v>1.67</v>
       </c>
-      <c r="BP6" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>94.44</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>88.89</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>61.11</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>50</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>38.89</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>38.89</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>61.11</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1.61</v>
-      </c>
       <c r="CA6" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.48</v>
+        <v>4.45</v>
       </c>
       <c r="CC6" t="n">
         <v>2.12</v>
@@ -3237,40 +3237,40 @@
         <v>1.24</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.55</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CO6" t="n">
         <v>1.14</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
@@ -3291,16 +3291,16 @@
         <v>1.56</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY6" t="n">
         <v>1.77</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DB6" t="n">
         <v>1.16</v>
@@ -3309,82 +3309,82 @@
         <v>1.52</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="DE6" t="n">
         <v>0.16</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="DG6" t="n">
         <v>3</v>
       </c>
       <c r="DH6" t="n">
-        <v>103.78</v>
+        <v>104.11</v>
       </c>
       <c r="DI6" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.22</v>
+        <v>5.16</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DM6" t="n">
-        <v>48.34</v>
+        <v>47.74</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.28</v>
+        <v>11.58</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.72</v>
+        <v>13.05</v>
       </c>
       <c r="DR6" t="n">
-        <v>7</v>
+        <v>7.11</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>53.5</v>
+        <v>53.68</v>
       </c>
       <c r="DW6" t="n">
         <v>0.16</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.56</v>
+        <v>14.31</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.34</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>6.22</v>
+        <v>6.11</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F7" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="H7" t="n">
-        <v>108.56</v>
+        <v>110.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>63.56</v>
+        <v>61.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>9.44</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.779999999999999</v>
+        <v>9</v>
       </c>
       <c r="R7" t="n">
-        <v>5.78</v>
+        <v>6.2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>59.44</v>
+        <v>59.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.78</v>
+        <v>14.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.78</v>
+        <v>6.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AF7" t="n">
         <v>0.11</v>
@@ -3565,64 +3565,64 @@
         <v>1.67</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.109999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL7" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.83</v>
+        <v>3.89</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.28</v>
+        <v>4.16</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BU7" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV7" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BW7" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BX7" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="CA7" t="n">
         <v>3.78</v>
@@ -3643,13 +3643,13 @@
         <v>2.29</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.54</v>
@@ -3673,13 +3673,13 @@
         <v>1.56</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CR7" t="n">
         <v>1.35</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CT7" t="n">
         <v>3.34</v>
@@ -3700,7 +3700,7 @@
         <v>1.92</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="DA7" t="n">
         <v>1.88</v>
@@ -3712,22 +3712,22 @@
         <v>1.59</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="DH7" t="n">
-        <v>110.78</v>
+        <v>111.47</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ7" t="n">
         <v>2</v>
@@ -3736,58 +3736,58 @@
         <v>5</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.06</v>
+        <v>51.53</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.56</v>
+        <v>9.84</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.34</v>
+        <v>10.37</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.39</v>
+        <v>6.58</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>57.28</v>
+        <v>57.47</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.94</v>
+        <v>12.95</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.22</v>
+        <v>7.37</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.72</v>
+        <v>5.58</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.61</v>
+        <v>17.42</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0.11</v>
@@ -3887,139 +3887,139 @@
         <v>1.56</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AI8" t="n">
-        <v>82.89</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.56</v>
+        <v>4.2</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AN8" t="n">
-        <v>39</v>
+        <v>43.2</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.56</v>
+        <v>12</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.890000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.44</v>
+        <v>6.8</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>48.11</v>
+        <v>46.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.67</v>
+        <v>10.9</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.44</v>
+        <v>6.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.89</v>
+        <v>18.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="BH8" t="n">
         <v>9.890000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="BM8" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BO8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.56</v>
+        <v>4.74</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.28</v>
+        <v>4.16</v>
       </c>
       <c r="BR8" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BU8" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BV8" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BW8" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BX8" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BY8" t="n">
         <v>2.41</v>
@@ -4028,16 +4028,16 @@
         <v>2.54</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CB8" t="n">
         <v>3.99</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.93</v>
+        <v>4.07</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.09</v>
+        <v>4.17</v>
       </c>
       <c r="CE8" t="n">
         <v>1.28</v>
@@ -4046,13 +4046,13 @@
         <v>2.34</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.57</v>
@@ -4064,10 +4064,10 @@
         <v>1.8</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CN8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CO8" t="n">
         <v>1.16</v>
@@ -4076,121 +4076,121 @@
         <v>1.62</v>
       </c>
       <c r="CQ8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CS8" t="n">
         <v>2.45</v>
       </c>
-      <c r="CR8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="CS8" t="n">
-        <v>2.44</v>
-      </c>
       <c r="CT8" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="CU8" t="n">
         <v>1.59</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY8" t="n">
         <v>1.8</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC8" t="n">
         <v>1.64</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="DH8" t="n">
-        <v>95.22</v>
+        <v>93.53</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.06</v>
+        <v>4.84</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="DM8" t="n">
-        <v>44.5</v>
+        <v>46.42</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.78</v>
+        <v>12</v>
       </c>
       <c r="DQ8" t="n">
-        <v>9.66</v>
+        <v>9.52</v>
       </c>
       <c r="DR8" t="n">
-        <v>5.94</v>
+        <v>6.16</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.61</v>
+        <v>47.89</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.89</v>
+        <v>11.47</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.06</v>
+        <v>6.74</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.83</v>
+        <v>4.73</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.61</v>
+        <v>18.31</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,52 +4290,52 @@
         <v>1.67</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AI9" t="n">
-        <v>94.56</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.89</v>
+        <v>5.2</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN9" t="n">
-        <v>49.67</v>
+        <v>50.2</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AQ9" t="n">
         <v>13</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.67</v>
+        <v>10.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.89</v>
+        <v>6.9</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>49.56</v>
+        <v>49.3</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.78</v>
+        <v>11.8</v>
       </c>
       <c r="BB9" t="n">
         <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.56</v>
+        <v>19.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.390000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.33</v>
+        <v>4.53</v>
       </c>
       <c r="BQ9" t="n">
         <v>5</v>
       </c>
       <c r="BR9" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BS9" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BT9" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU9" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV9" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX9" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BY9" t="n">
         <v>2.81</v>
@@ -4431,37 +4431,37 @@
         <v>3.07</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CB9" t="n">
         <v>3.75</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="CE9" t="n">
         <v>1.31</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CH9" t="n">
         <v>1.5</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.59</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL9" t="n">
         <v>1.92</v>
@@ -4470,34 +4470,34 @@
         <v>2.5</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO9" t="n">
         <v>1.2</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX9" t="n">
         <v>1.52</v>
@@ -4509,91 +4509,91 @@
         <v>2.43</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB9" t="n">
         <v>1.22</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="DG9" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="DH9" t="n">
-        <v>94.12</v>
+        <v>94.69</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.89</v>
+        <v>5.05</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DM9" t="n">
-        <v>47.06</v>
+        <v>47.47</v>
       </c>
       <c r="DN9" t="n">
         <v>0.89</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.72</v>
+        <v>11.79</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.17</v>
+        <v>10.16</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.89</v>
+        <v>6.9</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48</v>
+        <v>47.95</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.67</v>
+        <v>11.69</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.39</v>
+        <v>7.42</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.33</v>
+        <v>17.42</v>
       </c>
       <c r="EB9" t="n">
         <v>1.38</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
@@ -4615,79 +4615,79 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="G10" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H10" t="n">
-        <v>101.89</v>
+        <v>98.7</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>5.44</v>
+        <v>5.3</v>
       </c>
       <c r="L10" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="M10" t="n">
-        <v>49.11</v>
+        <v>47.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>6.89</v>
+        <v>7.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.44</v>
+        <v>11.5</v>
       </c>
       <c r="R10" t="n">
-        <v>9.220000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="S10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>53.44</v>
+        <v>52.8</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.11</v>
+        <v>12</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.33</v>
+        <v>7.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.78</v>
+        <v>4.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>16.44</v>
+        <v>16.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -4774,70 +4774,70 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.779999999999999</v>
+        <v>10.05</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BO10" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.17</v>
+        <v>5.32</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.61</v>
+        <v>4.74</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU10" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV10" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW10" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BX10" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY10" t="n">
         <v>2.8</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="CC10" t="n">
         <v>4.27</v>
@@ -4855,10 +4855,10 @@
         <v>3.33</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.58</v>
@@ -4867,13 +4867,13 @@
         <v>1.53</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM10" t="n">
         <v>2.39</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CO10" t="n">
         <v>1.18</v>
@@ -4882,13 +4882,13 @@
         <v>1.62</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CR10" t="n">
         <v>1.34</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CT10" t="n">
         <v>3.36</v>
@@ -4903,16 +4903,16 @@
         <v>1.58</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DB10" t="n">
         <v>1.2</v>
@@ -4921,82 +4921,82 @@
         <v>1.64</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.61</v>
+        <v>92.37</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.66</v>
+        <v>4.63</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DM10" t="n">
-        <v>41.5</v>
+        <v>41.16</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="DP10" t="n">
-        <v>6.94</v>
+        <v>7.11</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.77</v>
+        <v>11.79</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.27</v>
+        <v>8.52</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.61</v>
+        <v>50.42</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.5</v>
+        <v>11.47</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.89</v>
+        <v>7.05</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.61</v>
+        <v>4.42</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.33</v>
+        <v>15.53</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0.33</v>
@@ -5096,139 +5096,139 @@
         <v>1.56</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>94.22</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>41.44</v>
+        <v>41.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11.78</v>
+        <v>11.7</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.109999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.33</v>
+        <v>8.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>46</v>
+        <v>45.3</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.11</v>
+        <v>12</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.78</v>
+        <v>7.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="BD11" t="n">
-        <v>19.56</v>
+        <v>19.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.22</v>
+        <v>10.05</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="BR11" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU11" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV11" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX11" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY11" t="n">
         <v>3.34</v>
@@ -5237,22 +5237,22 @@
         <v>3.47</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.07</v>
+        <v>4.12</v>
       </c>
       <c r="CE11" t="n">
         <v>1.29</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CG11" t="n">
         <v>3.37</v>
@@ -5261,19 +5261,19 @@
         <v>1.52</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CK11" t="n">
         <v>1.44</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CN11" t="n">
         <v>1.96</v>
@@ -5285,13 +5285,13 @@
         <v>1.64</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CR11" t="n">
         <v>1.34</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CT11" t="n">
         <v>3.34</v>
@@ -5300,10 +5300,10 @@
         <v>1.59</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CX11" t="n">
         <v>1.53</v>
@@ -5312,61 +5312,61 @@
         <v>1.81</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DA11" t="n">
         <v>2</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DC11" t="n">
         <v>1.66</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="DH11" t="n">
-        <v>88.61</v>
+        <v>88.47</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM11" t="n">
-        <v>42.78</v>
+        <v>42.74</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.78</v>
+        <v>10.79</v>
       </c>
       <c r="DQ11" t="n">
-        <v>8.94</v>
+        <v>9.26</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.16</v>
+        <v>8.26</v>
       </c>
       <c r="DS11" t="n">
         <v>0.16</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>45.28</v>
+        <v>44.95</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.44</v>
+        <v>12.37</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.109999999999999</v>
+        <v>8.16</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.33</v>
+        <v>4.21</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.67</v>
+        <v>19.47</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="12">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
-        <v>90.11</v>
+        <v>92.2</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="K12" t="n">
-        <v>4.11</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="M12" t="n">
-        <v>43.33</v>
+        <v>69</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="P12" t="n">
-        <v>13.56</v>
+        <v>13.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="R12" t="n">
-        <v>8.220000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="S12" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="T12" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>44.11</v>
+        <v>46.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>11.44</v>
+        <v>12.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.44</v>
+        <v>8</v>
       </c>
       <c r="AB12" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>21.89</v>
+        <v>23</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.32</v>
+        <v>1.59</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
         <v>0.11</v>
@@ -5580,70 +5580,70 @@
         <v>2.11</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.06</v>
+        <v>3.16</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.390000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.06</v>
+        <v>3.16</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.22</v>
+        <v>4.47</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU12" t="n">
-        <v>22.22</v>
+        <v>26.32</v>
       </c>
       <c r="BV12" t="n">
-        <v>11.11</v>
+        <v>15.79</v>
       </c>
       <c r="BW12" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX12" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.34</v>
+        <v>3.21</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="CC12" t="n">
         <v>5.12</v>
@@ -5655,16 +5655,16 @@
         <v>1.3</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CH12" t="n">
         <v>1.51</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.66</v>
@@ -5676,10 +5676,10 @@
         <v>1.82</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CO12" t="n">
         <v>1.2</v>
@@ -5688,7 +5688,7 @@
         <v>1.68</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
@@ -5724,52 +5724,52 @@
         <v>1.22</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="DH12" t="n">
-        <v>91.66</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
         <v>2</v>
       </c>
       <c r="DK12" t="n">
-        <v>4</v>
+        <v>4.32</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="DM12" t="n">
-        <v>42</v>
+        <v>55.58</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.28</v>
+        <v>13.21</v>
       </c>
       <c r="DQ12" t="n">
-        <v>8.779999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.44</v>
+        <v>8.26</v>
       </c>
       <c r="DS12" t="n">
         <v>0.11</v>
@@ -5781,25 +5781,25 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>42.89</v>
+        <v>44.05</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.56</v>
+        <v>11.11</v>
       </c>
       <c r="DY12" t="n">
-        <v>7</v>
+        <v>7.32</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.56</v>
+        <v>3.79</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.44</v>
+        <v>22.05</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="EC12" t="n">
         <v>1.89</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>0.22</v>
@@ -5908,46 +5908,46 @@
         <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AI13" t="n">
-        <v>104.56</v>
+        <v>106.9</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AN13" t="n">
-        <v>47.56</v>
+        <v>49.6</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.89</v>
+        <v>12.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.109999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>48.44</v>
+        <v>48.9</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>12.78</v>
+        <v>12.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="BD13" t="n">
-        <v>17.33</v>
+        <v>17.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.720000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.94</v>
+        <v>4.11</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BT13" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BU13" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV13" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW13" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX13" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY13" t="n">
         <v>2.74</v>
@@ -6043,55 +6043,55 @@
         <v>2.95</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.63</v>
+        <v>3.48</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.77</v>
+        <v>3.61</v>
       </c>
       <c r="CE13" t="n">
         <v>1.29</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CH13" t="n">
         <v>1.53</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.59</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL13" t="n">
         <v>1.73</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CN13" t="n">
         <v>2.07</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP13" t="n">
         <v>1.64</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
@@ -6106,106 +6106,106 @@
         <v>1.56</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CW13" t="n">
         <v>1.61</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY13" t="n">
         <v>1.73</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DB13" t="n">
         <v>1.21</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF13" t="n">
         <v>0.84</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DH13" t="n">
-        <v>97.12</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.5</v>
+        <v>4.84</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.44</v>
+        <v>0.58</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.56</v>
+        <v>44.84</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.11</v>
+        <v>11.1</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.34</v>
+        <v>12.21</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.72</v>
+        <v>7.68</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48</v>
+        <v>48.27</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.5</v>
+        <v>11.63</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.11</v>
+        <v>7.26</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.27</v>
+        <v>18.53</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="F5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="H5" t="n">
-        <v>132.44</v>
+        <v>125.7</v>
       </c>
       <c r="I5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J5" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>58.11</v>
+        <v>61.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="P5" t="n">
-        <v>11.78</v>
+        <v>12.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.56</v>
+        <v>9.9</v>
       </c>
       <c r="R5" t="n">
-        <v>5.89</v>
+        <v>6</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="U5" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="V5" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>57.78</v>
+        <v>55.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.67</v>
+        <v>17.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.78</v>
+        <v>12.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.89</v>
+        <v>5</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.78</v>
+        <v>19.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>1.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.109999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BM5" t="n">
         <v>0.95</v>
       </c>
-      <c r="BM5" t="n">
-        <v>0.89</v>
-      </c>
       <c r="BN5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP5" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="BQ5" t="n">
         <v>5</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS5" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT5" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU5" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV5" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW5" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX5" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.48</v>
+        <v>4.46</v>
       </c>
       <c r="CC5" t="n">
         <v>1.89</v>
@@ -2843,16 +2843,16 @@
         <v>1.52</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CK5" t="n">
         <v>1.53</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CM5" t="n">
         <v>2.35</v>
@@ -2864,28 +2864,28 @@
         <v>1.19</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CT5" t="n">
         <v>3.27</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX5" t="n">
         <v>1.56</v>
@@ -2906,82 +2906,82 @@
         <v>1.7</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="DH5" t="n">
-        <v>126</v>
+        <v>122.95</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.21</v>
+        <v>5.15</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM5" t="n">
-        <v>55.63</v>
+        <v>57.45</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="DO5" t="n">
         <v>2.1</v>
       </c>
       <c r="DP5" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10</v>
+        <v>10.15</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.79</v>
+        <v>5.85</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.32</v>
+        <v>55.25</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DX5" t="n">
-        <v>16.42</v>
+        <v>16.35</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.42</v>
+        <v>11.3</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.21</v>
+        <v>19.75</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="6">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0.3</v>
@@ -3484,139 +3484,139 @@
         <v>1.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AI7" t="n">
-        <v>113</v>
+        <v>110.9</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AL7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AN7" t="n">
-        <v>40.56</v>
+        <v>46.9</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.67</v>
+        <v>10</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.89</v>
+        <v>12.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>55.11</v>
+        <v>56.1</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.11</v>
+        <v>11.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.44</v>
+        <v>6.7</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="BD7" t="n">
-        <v>19.22</v>
+        <v>18.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.050000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT7" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BU7" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV7" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BW7" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BX7" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BY7" t="n">
         <v>2.26</v>
@@ -3625,22 +3625,22 @@
         <v>2.37</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="CB7" t="n">
         <v>3.98</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.85</v>
+        <v>2.98</v>
       </c>
       <c r="CE7" t="n">
         <v>1.26</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CG7" t="n">
         <v>3.5</v>
@@ -3649,7 +3649,7 @@
         <v>1.58</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.54</v>
@@ -3658,10 +3658,10 @@
         <v>1.53</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CN7" t="n">
         <v>1.83</v>
@@ -3673,22 +3673,22 @@
         <v>1.56</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CR7" t="n">
         <v>1.35</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CT7" t="n">
         <v>3.34</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CW7" t="n">
         <v>1.53</v>
@@ -3715,16 +3715,16 @@
         <v>2.43</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="DH7" t="n">
-        <v>111.47</v>
+        <v>110.5</v>
       </c>
       <c r="DI7" t="n">
         <v>0.05</v>
@@ -3733,61 +3733,61 @@
         <v>2</v>
       </c>
       <c r="DK7" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="DM7" t="n">
-        <v>51.53</v>
+        <v>54.15</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.84</v>
+        <v>10</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.37</v>
+        <v>10.6</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.58</v>
+        <v>6.55</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>57.47</v>
+        <v>57.85</v>
       </c>
       <c r="DW7" t="n">
         <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.95</v>
+        <v>13</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.37</v>
+        <v>7.45</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.58</v>
+        <v>5.55</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.42</v>
+        <v>17.2</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="8">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
@@ -4212,82 +4212,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="H9" t="n">
-        <v>93.67</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="K9" t="n">
-        <v>4.89</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M9" t="n">
-        <v>44.44</v>
+        <v>44.1</v>
       </c>
       <c r="N9" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>10.44</v>
+        <v>10.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.67</v>
+        <v>9.6</v>
       </c>
       <c r="R9" t="n">
-        <v>6.89</v>
+        <v>7</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="V9" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>46.44</v>
+        <v>47</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.56</v>
+        <v>11.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.78</v>
+        <v>6.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>15.11</v>
+        <v>16.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
         <v>0.1</v>
@@ -4371,70 +4371,70 @@
         <v>2.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.58</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="BQ9" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>80</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>60</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>40</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BW9" t="n">
         <v>5</v>
       </c>
-      <c r="BR9" t="n">
-        <v>78.95</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>57.89</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>42.11</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>15.79</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>15.79</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>5.26</v>
-      </c>
       <c r="BX9" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.81</v>
+        <v>2.71</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.07</v>
+        <v>2.95</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CC9" t="n">
         <v>3.11</v>
@@ -4443,22 +4443,22 @@
         <v>3.22</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CK9" t="n">
         <v>1.47</v>
@@ -4467,19 +4467,19 @@
         <v>1.92</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO9" t="n">
         <v>1.2</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
@@ -4494,106 +4494,106 @@
         <v>1.53</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CX9" t="n">
         <v>1.52</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.43</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="DE9" t="n">
         <v>0.05</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="DH9" t="n">
-        <v>94.69</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.05</v>
+        <v>4.9</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM9" t="n">
-        <v>47.47</v>
+        <v>47.15</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.79</v>
+        <v>11.75</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.16</v>
+        <v>10.1</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.9</v>
+        <v>6.95</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47.95</v>
+        <v>48.15</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.69</v>
+        <v>11.45</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.42</v>
+        <v>7.2</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.42</v>
+        <v>17.9</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0.1</v>
@@ -5499,52 +5499,52 @@
         <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AI12" t="n">
-        <v>93.22</v>
+        <v>94.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.89</v>
+        <v>4.2</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>40.67</v>
+        <v>43.7</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.890000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.67</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>41.67</v>
+        <v>42.3</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.67</v>
+        <v>10.1</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.56</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="BD12" t="n">
         <v>21</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.630000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.16</v>
+        <v>5.1</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BT12" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU12" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV12" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW12" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX12" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY12" t="n">
         <v>3.21</v>
@@ -5643,28 +5643,28 @@
         <v>3.96</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="CC12" t="n">
-        <v>5.12</v>
+        <v>5.04</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.57</v>
+        <v>5.47</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.66</v>
@@ -5676,19 +5676,19 @@
         <v>1.82</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CN12" t="n">
         <v>2.06</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
@@ -5703,7 +5703,7 @@
         <v>1.54</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CW12" t="n">
         <v>1.67</v>
@@ -5724,85 +5724,85 @@
         <v>1.22</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="DE12" t="n">
         <v>0.1</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="DH12" t="n">
-        <v>92.68000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DJ12" t="n">
         <v>2</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.32</v>
+        <v>4.45</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DM12" t="n">
-        <v>55.58</v>
+        <v>56.35</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.21</v>
+        <v>13.05</v>
       </c>
       <c r="DQ12" t="n">
-        <v>8.74</v>
+        <v>8.85</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.26</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>44.05</v>
+        <v>44.25</v>
       </c>
       <c r="DW12" t="n">
         <v>0.1</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.11</v>
+        <v>11.25</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.32</v>
+        <v>7.5</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="EA12" t="n">
-        <v>22.05</v>
+        <v>22</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="13">

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0.4</v>
@@ -1469,139 +1469,139 @@
         <v>1.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.78</v>
+        <v>2.6</v>
       </c>
       <c r="AI2" t="n">
-        <v>81.78</v>
+        <v>84.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.11</v>
+        <v>4.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.56</v>
+        <v>50.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10.33</v>
+        <v>10.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.33</v>
+        <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.78</v>
+        <v>7.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>47.56</v>
+        <v>48.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.78</v>
+        <v>13.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>18.11</v>
+        <v>17.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.470000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.16</v>
+        <v>5.45</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS2" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT2" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU2" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV2" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW2" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX2" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BY2" t="n">
         <v>1.89</v>
@@ -1610,28 +1610,28 @@
         <v>1.88</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.75</v>
+        <v>3.83</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.93</v>
+        <v>3.97</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI2" t="n">
         <v>2.22</v>
@@ -1640,40 +1640,40 @@
         <v>1.63</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CO2" t="n">
         <v>1.2</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="CR2" t="n">
         <v>1.35</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CT2" t="n">
         <v>3.3</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CW2" t="n">
         <v>1.64</v>
@@ -1682,97 +1682,97 @@
         <v>1.54</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.41</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="DB2" t="n">
         <v>1.22</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="DH2" t="n">
-        <v>100</v>
+        <v>100.3</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.58</v>
+        <v>5.85</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DM2" t="n">
-        <v>69.20999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DO2" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.31</v>
+        <v>10.4</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.58</v>
+        <v>11.9</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.21</v>
+        <v>6.2</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.11</v>
+        <v>54.25</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.16</v>
+        <v>16.3</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.53</v>
+        <v>10.7</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.63</v>
+        <v>5.6</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.47</v>
+        <v>17.25</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>0.2</v>
@@ -1872,52 +1872,52 @@
         <v>1.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AI3" t="n">
-        <v>102.78</v>
+        <v>99.2</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.56</v>
+        <v>4.4</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>55.11</v>
+        <v>54.1</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.56</v>
+        <v>9.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.44</v>
+        <v>12.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.89</v>
+        <v>5.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>53.78</v>
+        <v>54.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>15.33</v>
+        <v>14.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>10.33</v>
+        <v>9.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.11</v>
+        <v>19.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="BF3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.16</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BP3" t="n">
         <v>4.05</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS3" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT3" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BU3" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BY3" t="n">
         <v>2.05</v>
@@ -2013,28 +2013,28 @@
         <v>2.13</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI3" t="n">
         <v>2.22</v>
@@ -2046,10 +2046,10 @@
         <v>1.47</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN3" t="n">
         <v>1.93</v>
@@ -2061,7 +2061,7 @@
         <v>1.66</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CR3" t="n">
         <v>1.35</v>
@@ -2085,10 +2085,10 @@
         <v>1.56</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="DA3" t="n">
         <v>1.92</v>
@@ -2100,82 +2100,82 @@
         <v>1.68</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="DH3" t="n">
-        <v>103.11</v>
+        <v>101.3</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM3" t="n">
-        <v>57.84</v>
+        <v>57.2</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.37</v>
+        <v>10.35</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.21</v>
+        <v>12.5</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.16</v>
+        <v>6.15</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>52.63</v>
+        <v>53.05</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.58</v>
+        <v>14.25</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.369999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.21</v>
+        <v>5.05</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.53</v>
+        <v>19.65</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4">
@@ -2185,61 +2185,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="G4" t="n">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="H4" t="n">
-        <v>86.33</v>
+        <v>85.8</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J4" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="K4" t="n">
-        <v>5.89</v>
+        <v>5.7</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>44.44</v>
+        <v>44.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="P4" t="n">
-        <v>9.33</v>
+        <v>10.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.22</v>
+        <v>10.4</v>
       </c>
       <c r="R4" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="S4" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>45.44</v>
+        <v>45.2</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.22</v>
+        <v>7.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>0.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.89</v>
+        <v>11.1</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BL4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BM4" t="n">
         <v>1</v>
       </c>
-      <c r="BM4" t="n">
-        <v>1.05</v>
-      </c>
       <c r="BN4" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="BP4" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.58</v>
+        <v>5.85</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BT4" t="n">
-        <v>73.68000000000001</v>
+        <v>70</v>
       </c>
       <c r="BU4" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BV4" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX4" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.11</v>
+        <v>4.35</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.62</v>
+        <v>4.74</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.31</v>
+        <v>4.36</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="CC4" t="n">
         <v>5.84</v>
@@ -2431,10 +2431,10 @@
         <v>1.26</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="CH4" t="n">
         <v>1.59</v>
@@ -2446,25 +2446,25 @@
         <v>1.64</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CO4" t="n">
         <v>1.16</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CR4" t="n">
         <v>1.34</v>
@@ -2488,13 +2488,13 @@
         <v>1.48</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.53</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DB4" t="n">
         <v>1.17</v>
@@ -2506,46 +2506,46 @@
         <v>2.37</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="DH4" t="n">
-        <v>80</v>
+        <v>80.05</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.73</v>
+        <v>44.75</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DO4" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.31</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.369999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.630000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="DS4" t="n">
         <v>0.05</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>42.26</v>
+        <v>42.3</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.26</v>
+        <v>10.2</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.58</v>
+        <v>6.65</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.69</v>
+        <v>3.55</v>
       </c>
       <c r="EA4" t="n">
-        <v>16.74</v>
+        <v>16.7</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="5">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>0.3</v>
@@ -3081,139 +3081,139 @@
         <v>1.6</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AI6" t="n">
-        <v>97.67</v>
+        <v>99.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AN6" t="n">
-        <v>40.78</v>
+        <v>41.7</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.67</v>
+        <v>11.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.44</v>
+        <v>11.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.779999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.44</v>
+        <v>13</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.78</v>
+        <v>7.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.67</v>
+        <v>5.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>21.78</v>
+        <v>21.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.74</v>
+        <v>9.75</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.53</v>
+        <v>0.7</v>
       </c>
       <c r="BL6" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BN6" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.16</v>
+        <v>4.3</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.58</v>
+        <v>5.45</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS6" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT6" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU6" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BV6" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BW6" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BX6" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY6" t="n">
         <v>1.63</v>
@@ -3222,25 +3222,25 @@
         <v>1.67</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CF6" t="n">
         <v>2.19</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CH6" t="n">
         <v>1.63</v>
@@ -3255,10 +3255,10 @@
         <v>1.42</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CN6" t="n">
         <v>2.03</v>
@@ -3270,7 +3270,7 @@
         <v>1.52</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
@@ -3291,97 +3291,97 @@
         <v>1.56</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.46</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DB6" t="n">
         <v>1.16</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="DG6" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="DH6" t="n">
-        <v>104.11</v>
+        <v>104.6</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.16</v>
+        <v>5.2</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="DM6" t="n">
-        <v>47.74</v>
+        <v>47.85</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.16</v>
+        <v>2.35</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.58</v>
+        <v>11.45</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.05</v>
+        <v>12.85</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.11</v>
+        <v>7.05</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>53.68</v>
+        <v>53.7</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.31</v>
+        <v>14.5</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.210000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>6.11</v>
+        <v>6.3</v>
       </c>
       <c r="EA6" t="n">
         <v>20</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="EC6" t="n">
         <v>2</v>
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="H8" t="n">
-        <v>107.56</v>
+        <v>104.7</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="K8" t="n">
-        <v>5.56</v>
+        <v>5.4</v>
       </c>
       <c r="L8" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="M8" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O8" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Q8" t="n">
-        <v>10.44</v>
-      </c>
-      <c r="R8" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>49.11</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>12.11</v>
-      </c>
       <c r="AA8" t="n">
-        <v>6.67</v>
+        <v>6.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.44</v>
+        <v>5.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>18.33</v>
+        <v>18.2</v>
       </c>
       <c r="AD8" t="n">
         <v>1.51</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
         <v>0.4</v>
@@ -3968,70 +3968,70 @@
         <v>1.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.890000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.74</v>
+        <v>4.85</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.16</v>
+        <v>4.1</v>
       </c>
       <c r="BR8" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS8" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BT8" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BU8" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BV8" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BW8" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BX8" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="CC8" t="n">
         <v>4.07</v>
@@ -4049,7 +4049,7 @@
         <v>3.37</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CI8" t="n">
         <v>2.31</v>
@@ -4061,10 +4061,10 @@
         <v>1.42</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CN8" t="n">
         <v>1.99</v>
@@ -4082,7 +4082,7 @@
         <v>1.34</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CT8" t="n">
         <v>3.31</v>
@@ -4100,7 +4100,7 @@
         <v>1.52</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.44</v>
@@ -4109,88 +4109,88 @@
         <v>2.02</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DC8" t="n">
         <v>1.64</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.53</v>
+        <v>92.8</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.42</v>
+        <v>46.55</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="DP8" t="n">
-        <v>12</v>
+        <v>11.95</v>
       </c>
       <c r="DQ8" t="n">
-        <v>9.52</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.16</v>
+        <v>6.1</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47.89</v>
+        <v>47.8</v>
       </c>
       <c r="DW8" t="n">
         <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.47</v>
+        <v>11.45</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.74</v>
+        <v>6.65</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.73</v>
+        <v>4.8</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.31</v>
+        <v>18.25</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="9">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,139 +4693,139 @@
         <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AI10" t="n">
-        <v>85.33</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.78</v>
+        <v>1.1</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN10" t="n">
-        <v>33.89</v>
+        <v>32.7</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.11</v>
+        <v>11.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.33</v>
+        <v>8</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>47.78</v>
+        <v>48.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.89</v>
+        <v>10.7</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="BD10" t="n">
-        <v>14.22</v>
+        <v>14.7</v>
       </c>
       <c r="BE10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BN10" t="n">
         <v>1.25</v>
       </c>
-      <c r="BF10" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BO10" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.32</v>
+        <v>5.05</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.74</v>
+        <v>4.8</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS10" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT10" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU10" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV10" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW10" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BX10" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY10" t="n">
         <v>2.8</v>
@@ -4834,25 +4834,25 @@
         <v>2.91</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.27</v>
+        <v>4.19</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.62</v>
+        <v>4.53</v>
       </c>
       <c r="CE10" t="n">
         <v>1.28</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="CH10" t="n">
         <v>1.55</v>
@@ -4861,25 +4861,25 @@
         <v>2.32</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CM10" t="n">
         <v>2.39</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CQ10" t="n">
         <v>2.53</v>
@@ -4897,7 +4897,7 @@
         <v>1.61</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CW10" t="n">
         <v>1.58</v>
@@ -4918,52 +4918,52 @@
         <v>1.2</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="DD10" t="n">
         <v>2.56</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="DH10" t="n">
-        <v>92.37</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.1</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.63</v>
+        <v>4.55</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DM10" t="n">
-        <v>41.16</v>
+        <v>40.2</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="DP10" t="n">
-        <v>7.11</v>
+        <v>7.2</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.79</v>
+        <v>11.65</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.52</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DS10" t="n">
         <v>0.1</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.42</v>
+        <v>50.6</v>
       </c>
       <c r="DW10" t="n">
         <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.47</v>
+        <v>11.35</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.05</v>
+        <v>7</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.42</v>
+        <v>4.35</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.53</v>
+        <v>15.7</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F11" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="H11" t="n">
-        <v>83</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="K11" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="L11" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M11" t="n">
-        <v>44.11</v>
+        <v>47.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="P11" t="n">
-        <v>9.779999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.779999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="S11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U11" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="V11" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>44.56</v>
+        <v>44.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.78</v>
+        <v>13.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.44</v>
+        <v>8.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.78</v>
+        <v>19.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
         <v>0.1</v>
@@ -5180,64 +5180,64 @@
         <v>3.05</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.05</v>
+        <v>9.85</v>
       </c>
       <c r="BI11" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BL11" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BP11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BQ11" t="n">
         <v>5.05</v>
       </c>
-      <c r="BQ11" t="n">
+      <c r="BR11" t="n">
+        <v>95</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>85</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>60</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>30</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW11" t="n">
         <v>5</v>
       </c>
-      <c r="BR11" t="n">
-        <v>94.73999999999999</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>84.20999999999999</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>57.89</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>31.58</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>5.26</v>
-      </c>
       <c r="BX11" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.34</v>
+        <v>3.19</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.47</v>
+        <v>3.31</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="CB11" t="n">
         <v>3.96</v>
@@ -5249,7 +5249,7 @@
         <v>4.12</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF11" t="n">
         <v>2.39</v>
@@ -5258,7 +5258,7 @@
         <v>3.37</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CI11" t="n">
         <v>2.3</v>
@@ -5270,10 +5270,10 @@
         <v>1.44</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CN11" t="n">
         <v>1.96</v>
@@ -5282,7 +5282,7 @@
         <v>1.19</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CQ11" t="n">
         <v>2.56</v>
@@ -5300,7 +5300,7 @@
         <v>1.59</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CW11" t="n">
         <v>1.6</v>
@@ -5321,85 +5321,85 @@
         <v>1.2</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="DH11" t="n">
-        <v>88.47</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="DI11" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="DK11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM11" t="n">
-        <v>42.74</v>
+        <v>44.3</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.79</v>
+        <v>10.7</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.26</v>
+        <v>9.25</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.26</v>
+        <v>8.15</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.95</v>
+        <v>45</v>
       </c>
       <c r="DW11" t="n">
         <v>0.1</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.37</v>
+        <v>12.55</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.16</v>
+        <v>8.25</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.21</v>
+        <v>4.3</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.47</v>
+        <v>19.4</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="12">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="F13" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="G13" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="H13" t="n">
-        <v>89.67</v>
+        <v>84.7</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J13" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="K13" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M13" t="n">
-        <v>39.56</v>
+        <v>37.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P13" t="n">
-        <v>10.22</v>
+        <v>10.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.78</v>
+        <v>11.6</v>
       </c>
       <c r="R13" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>47.56</v>
+        <v>46.7</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>10.22</v>
+        <v>10.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.22</v>
+        <v>6.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>19.22</v>
+        <v>20.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>1.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.050000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS13" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT13" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BU13" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV13" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW13" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX13" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="CA13" t="n">
         <v>3.67</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="CC13" t="n">
         <v>3.48</v>
@@ -6058,16 +6058,16 @@
         <v>1.29</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CH13" t="n">
         <v>1.53</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.59</v>
@@ -6076,22 +6076,22 @@
         <v>1.39</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP13" t="n">
         <v>1.64</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
@@ -6106,7 +6106,7 @@
         <v>1.56</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CW13" t="n">
         <v>1.61</v>
@@ -6115,64 +6115,64 @@
         <v>1.5</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DB13" t="n">
         <v>1.21</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="DG13" t="n">
         <v>1.9</v>
       </c>
       <c r="DH13" t="n">
-        <v>98.73999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.84</v>
+        <v>4.75</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DM13" t="n">
-        <v>44.84</v>
+        <v>43.5</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.21</v>
+        <v>12.1</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.68</v>
+        <v>7.75</v>
       </c>
       <c r="DS13" t="n">
         <v>0.1</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.27</v>
+        <v>47.8</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.63</v>
+        <v>11.75</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.26</v>
+        <v>7.3</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.37</v>
+        <v>4.45</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.53</v>
+        <v>19</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>116.4</v>
+        <v>114.73</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="K2" t="n">
-        <v>6.9</v>
+        <v>6.82</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="M2" t="n">
-        <v>89.59999999999999</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="O2" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="P2" t="n">
-        <v>10.3</v>
+        <v>10.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.8</v>
+        <v>11.82</v>
       </c>
       <c r="R2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>60</v>
+        <v>59.73</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.2</v>
+        <v>18.82</v>
       </c>
       <c r="AA2" t="n">
-        <v>12.8</v>
+        <v>12.18</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.4</v>
+        <v>6.64</v>
       </c>
       <c r="AC2" t="n">
-        <v>16.9</v>
+        <v>16.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF2" t="n">
         <v>0.2</v>
@@ -1550,70 +1550,70 @@
         <v>1.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.75</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.2</v>
+        <v>4.29</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.45</v>
+        <v>5.24</v>
       </c>
       <c r="BR2" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT2" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU2" t="n">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>14.29</v>
       </c>
       <c r="BX2" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="CC2" t="n">
         <v>2.64</v>
@@ -1640,16 +1640,16 @@
         <v>1.63</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CO2" t="n">
         <v>1.2</v>
@@ -1658,7 +1658,7 @@
         <v>1.69</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CR2" t="n">
         <v>1.35</v>
@@ -1682,13 +1682,13 @@
         <v>1.54</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.41</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="DB2" t="n">
         <v>1.22</v>
@@ -1700,79 +1700,79 @@
         <v>2.73</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DF2" t="n">
         <v>1.1</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="DH2" t="n">
-        <v>100.3</v>
+        <v>100.19</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="DM2" t="n">
-        <v>70.05</v>
+        <v>69</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.4</v>
+        <v>10.62</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.9</v>
+        <v>11.91</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.2</v>
+        <v>6.24</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.25</v>
+        <v>54.38</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.3</v>
+        <v>16.24</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.7</v>
+        <v>10.48</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.6</v>
+        <v>5.76</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.25</v>
+        <v>17.05</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="H3" t="n">
-        <v>103.4</v>
+        <v>103</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M3" t="n">
-        <v>60.3</v>
+        <v>60.36</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>11.1</v>
+        <v>11.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.9</v>
+        <v>12.91</v>
       </c>
       <c r="R3" t="n">
-        <v>6.4</v>
+        <v>6.82</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>51.6</v>
+        <v>51.82</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.5</v>
+        <v>8.91</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.4</v>
+        <v>5.09</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.9</v>
+        <v>19.82</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AF3" t="n">
         <v>0.1</v>
@@ -1953,70 +1953,70 @@
         <v>1.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.050000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.05</v>
+        <v>4.19</v>
       </c>
       <c r="BQ3" t="n">
         <v>3.95</v>
       </c>
       <c r="BR3" t="n">
-        <v>95</v>
+        <v>90.48</v>
       </c>
       <c r="BS3" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV3" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX3" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BY3" t="n">
         <v>2.05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="CC3" t="n">
         <v>2.27</v>
@@ -2031,7 +2031,7 @@
         <v>2.4</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CH3" t="n">
         <v>1.52</v>
@@ -2046,13 +2046,13 @@
         <v>1.47</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CM3" t="n">
         <v>2.49</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO3" t="n">
         <v>1.18</v>
@@ -2067,7 +2067,7 @@
         <v>1.35</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CT3" t="n">
         <v>3.3</v>
@@ -2085,10 +2085,10 @@
         <v>1.56</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA3" t="n">
         <v>1.92</v>
@@ -2097,85 +2097,85 @@
         <v>1.21</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD3" t="n">
         <v>2.68</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DH3" t="n">
-        <v>101.3</v>
+        <v>101.19</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM3" t="n">
-        <v>57.2</v>
+        <v>57.38</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO3" t="n">
         <v>1.85</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.35</v>
+        <v>10.67</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.5</v>
+        <v>12.52</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.15</v>
+        <v>6.38</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>53.05</v>
+        <v>53.1</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.25</v>
+        <v>14.29</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.05</v>
+        <v>4.9</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.65</v>
+        <v>19.62</v>
       </c>
       <c r="EB3" t="n">
         <v>1.66</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>0.2</v>
@@ -2275,139 +2275,139 @@
         <v>1.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AI4" t="n">
-        <v>74.3</v>
+        <v>74.45</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.2</v>
+        <v>-0.09</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AL4" t="n">
         <v>3</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AN4" t="n">
-        <v>45</v>
+        <v>43.73</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.300000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.6</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.2</v>
+        <v>10.36</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>39.4</v>
+        <v>39.55</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.6</v>
+        <v>10.27</v>
       </c>
       <c r="BB4" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="BD4" t="n">
-        <v>15.6</v>
+        <v>15.45</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="BH4" t="n">
-        <v>11.1</v>
+        <v>11.38</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK4" t="n">
         <v>0.9</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BM4" t="n">
         <v>1</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.85</v>
+        <v>6.05</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU4" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BV4" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BW4" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX4" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY4" t="n">
         <v>4.35</v>
@@ -2416,16 +2416,16 @@
         <v>4.74</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.66</v>
+        <v>4.64</v>
       </c>
       <c r="CC4" t="n">
-        <v>5.84</v>
+        <v>5.75</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.49</v>
+        <v>6.35</v>
       </c>
       <c r="CE4" t="n">
         <v>1.26</v>
@@ -2434,13 +2434,13 @@
         <v>2.26</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CH4" t="n">
         <v>1.59</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.64</v>
@@ -2449,7 +2449,7 @@
         <v>1.42</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM4" t="n">
         <v>2.6</v>
@@ -2461,25 +2461,25 @@
         <v>1.16</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CT4" t="n">
         <v>3.35</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CW4" t="n">
         <v>1.63</v>
@@ -2488,7 +2488,7 @@
         <v>1.48</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.53</v>
@@ -2500,52 +2500,52 @@
         <v>1.17</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="DH4" t="n">
-        <v>80.05</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.15</v>
+        <v>-0.09</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.75</v>
+        <v>44.1</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.91</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.5</v>
+        <v>9.33</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="DS4" t="n">
         <v>0.05</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>42.3</v>
+        <v>42.24</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.2</v>
+        <v>10.52</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.65</v>
+        <v>6.85</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="EA4" t="n">
-        <v>16.7</v>
+        <v>16.57</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0.3</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="AI5" t="n">
-        <v>120.2</v>
+        <v>120.64</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="AN5" t="n">
-        <v>53.4</v>
+        <v>55</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.2</v>
+        <v>12.82</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.4</v>
+        <v>10.36</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>55</v>
+        <v>54.45</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>15.3</v>
+        <v>15.09</v>
       </c>
       <c r="BB5" t="n">
-        <v>10.2</v>
+        <v>9.91</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.1</v>
+        <v>5.18</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.7</v>
+        <v>20.18</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.15</v>
+        <v>9.1</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL5" t="n">
         <v>0.9</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="BQ5" t="n">
         <v>5</v>
       </c>
       <c r="BR5" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BT5" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU5" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BV5" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW5" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX5" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY5" t="n">
         <v>1.56</v>
@@ -2822,10 +2822,10 @@
         <v>4.18</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.46</v>
+        <v>4.44</v>
       </c>
       <c r="CC5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CD5" t="n">
         <v>1.92</v>
@@ -2837,13 +2837,13 @@
         <v>2.42</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CH5" t="n">
         <v>1.52</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.71</v>
@@ -2852,19 +2852,19 @@
         <v>1.53</v>
       </c>
       <c r="CL5" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CM5" t="n">
         <v>2.35</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CO5" t="n">
         <v>1.19</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CQ5" t="n">
         <v>2.65</v>
@@ -2882,10 +2882,10 @@
         <v>1.58</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CX5" t="n">
         <v>1.56</v>
@@ -2894,10 +2894,10 @@
         <v>1.93</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB5" t="n">
         <v>1.22</v>
@@ -2909,79 +2909,79 @@
         <v>2.73</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="DG5" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="DH5" t="n">
-        <v>122.95</v>
+        <v>123.05</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="DM5" t="n">
-        <v>57.45</v>
+        <v>58.1</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="DO5" t="n">
         <v>2.1</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.25</v>
+        <v>12.57</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.15</v>
+        <v>10.14</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.85</v>
+        <v>6</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.25</v>
+        <v>54.95</v>
       </c>
       <c r="DW5" t="n">
         <v>0.1</v>
       </c>
       <c r="DX5" t="n">
-        <v>16.35</v>
+        <v>16.19</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.75</v>
+        <v>20</v>
       </c>
       <c r="EB5" t="n">
         <v>1.81</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0.3</v>
@@ -3081,139 +3081,139 @@
         <v>1.6</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AI6" t="n">
-        <v>99.3</v>
+        <v>100.18</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AN6" t="n">
-        <v>41.7</v>
+        <v>42.18</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.4</v>
+        <v>11.36</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.2</v>
+        <v>10.91</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.5</v>
+        <v>8.27</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AU6" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>51.3</v>
+        <v>52.09</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BA6" t="n">
-        <v>13</v>
+        <v>13.36</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.8</v>
+        <v>7.82</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.2</v>
+        <v>5.55</v>
       </c>
       <c r="BD6" t="n">
-        <v>21.6</v>
+        <v>20.82</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.75</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BL6" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BM6" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="BN6" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.3</v>
+        <v>4.43</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.45</v>
+        <v>5.43</v>
       </c>
       <c r="BR6" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BT6" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU6" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BV6" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BW6" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BX6" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY6" t="n">
         <v>1.63</v>
@@ -3225,16 +3225,16 @@
         <v>4.21</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.43</v>
+        <v>4.46</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CF6" t="n">
         <v>2.19</v>
@@ -3255,10 +3255,10 @@
         <v>1.42</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CN6" t="n">
         <v>2.03</v>
@@ -3270,13 +3270,13 @@
         <v>1.52</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CT6" t="n">
         <v>3.21</v>
@@ -3285,106 +3285,106 @@
         <v>1.7</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CX6" t="n">
         <v>1.52</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.46</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DB6" t="n">
         <v>1.16</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="DH6" t="n">
-        <v>104.6</v>
+        <v>104.81</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM6" t="n">
-        <v>47.85</v>
+        <v>47.81</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.45</v>
+        <v>11.43</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.85</v>
+        <v>12.62</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.05</v>
+        <v>7</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>53.7</v>
+        <v>54</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.5</v>
+        <v>14.62</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="DZ6" t="n">
-        <v>6.3</v>
+        <v>6.43</v>
       </c>
       <c r="EA6" t="n">
-        <v>20</v>
+        <v>19.67</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="EC6" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="H7" t="n">
-        <v>110.1</v>
+        <v>110.64</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="K7" t="n">
-        <v>5.9</v>
+        <v>5.82</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="M7" t="n">
-        <v>61.4</v>
+        <v>59.91</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>9.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>9</v>
+        <v>9.27</v>
       </c>
       <c r="R7" t="n">
-        <v>6.2</v>
+        <v>6.36</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>59.6</v>
+        <v>60.18</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.6</v>
+        <v>14.27</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.82</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.4</v>
+        <v>6.45</v>
       </c>
       <c r="AC7" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AF7" t="n">
         <v>0.1</v>
@@ -3565,70 +3565,70 @@
         <v>1.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.15</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="BJ7" t="n">
         <v>1.1</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL7" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT7" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU7" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BV7" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BW7" t="n">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="BX7" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.79</v>
+        <v>3.82</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.98</v>
+        <v>4.06</v>
       </c>
       <c r="CC7" t="n">
         <v>2.78</v>
@@ -3640,7 +3640,7 @@
         <v>1.26</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CG7" t="n">
         <v>3.5</v>
@@ -3649,7 +3649,7 @@
         <v>1.58</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.54</v>
@@ -3661,10 +3661,10 @@
         <v>1.97</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CO7" t="n">
         <v>1.16</v>
@@ -3673,7 +3673,7 @@
         <v>1.56</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CR7" t="n">
         <v>1.35</v>
@@ -3688,10 +3688,10 @@
         <v>1.65</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CX7" t="n">
         <v>1.57</v>
@@ -3709,22 +3709,22 @@
         <v>1.18</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="DH7" t="n">
-        <v>110.5</v>
+        <v>110.76</v>
       </c>
       <c r="DI7" t="n">
         <v>0.05</v>
@@ -3736,58 +3736,58 @@
         <v>5.05</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="DM7" t="n">
-        <v>54.15</v>
+        <v>53.71</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="DP7" t="n">
-        <v>10</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.6</v>
+        <v>10.67</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.55</v>
+        <v>6.62</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>57.85</v>
+        <v>58.24</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.45</v>
+        <v>7.29</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.55</v>
+        <v>5.62</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.2</v>
+        <v>17.24</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>104.7</v>
+        <v>104.18</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="K8" t="n">
-        <v>5.4</v>
+        <v>5.27</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="M8" t="n">
-        <v>49.9</v>
+        <v>50.09</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="P8" t="n">
-        <v>11.9</v>
+        <v>11.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.4</v>
+        <v>11.18</v>
       </c>
       <c r="R8" t="n">
-        <v>5.4</v>
+        <v>5.64</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>12</v>
+        <v>12.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.5</v>
+        <v>6.73</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.5</v>
+        <v>5.82</v>
       </c>
       <c r="AC8" t="n">
-        <v>18.2</v>
+        <v>18.64</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AF8" t="n">
         <v>0.4</v>
@@ -3968,67 +3968,67 @@
         <v>1.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.9</v>
+        <v>9.81</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="BJ8" t="n">
         <v>1.05</v>
       </c>
       <c r="BK8" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BL8" t="n">
         <v>0.9</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.85</v>
+        <v>4.76</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="BR8" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BU8" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BV8" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BW8" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BX8" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.55</v>
+        <v>2.71</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="CB8" t="n">
         <v>4</v>
@@ -4043,7 +4043,7 @@
         <v>1.28</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CG8" t="n">
         <v>3.37</v>
@@ -4058,10 +4058,10 @@
         <v>1.57</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CM8" t="n">
         <v>2.6</v>
@@ -4070,7 +4070,7 @@
         <v>1.99</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP8" t="n">
         <v>1.62</v>
@@ -4103,94 +4103,94 @@
         <v>1.81</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC8" t="n">
         <v>1.64</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="DH8" t="n">
-        <v>92.8</v>
+        <v>93.09</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.8</v>
+        <v>4.76</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.55</v>
+        <v>46.81</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.95</v>
+        <v>11.86</v>
       </c>
       <c r="DQ8" t="n">
-        <v>9.550000000000001</v>
+        <v>10</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.1</v>
+        <v>6.19</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47.8</v>
+        <v>47.95</v>
       </c>
       <c r="DW8" t="n">
         <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.45</v>
+        <v>11.76</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.65</v>
+        <v>6.76</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.25</v>
+        <v>18.48</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="9">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
@@ -4212,82 +4212,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>94.59999999999999</v>
+        <v>97</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>5.45</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M9" t="n">
-        <v>44.1</v>
+        <v>45.18</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="P9" t="n">
-        <v>10.5</v>
+        <v>10.09</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.6</v>
+        <v>9.82</v>
       </c>
       <c r="R9" t="n">
-        <v>7</v>
+        <v>6.82</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>47</v>
+        <v>48.09</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.1</v>
+        <v>12.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.4</v>
+        <v>7.73</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.7</v>
+        <v>4.82</v>
       </c>
       <c r="AC9" t="n">
-        <v>16.3</v>
+        <v>16.09</v>
       </c>
       <c r="AD9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
         <v>0.1</v>
@@ -4371,70 +4371,70 @@
         <v>2.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.550000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.55</v>
+        <v>4.67</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.95</v>
+        <v>5.19</v>
       </c>
       <c r="BR9" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BS9" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BT9" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU9" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV9" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW9" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX9" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="CC9" t="n">
         <v>3.11</v>
@@ -4446,7 +4446,7 @@
         <v>1.32</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CG9" t="n">
         <v>3.16</v>
@@ -4455,19 +4455,19 @@
         <v>1.49</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CK9" t="n">
         <v>1.47</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CN9" t="n">
         <v>1.95</v>
@@ -4479,7 +4479,7 @@
         <v>1.71</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
@@ -4494,7 +4494,7 @@
         <v>1.53</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CW9" t="n">
         <v>1.62</v>
@@ -4503,97 +4503,97 @@
         <v>1.52</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.43</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DC9" t="n">
         <v>1.74</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="DE9" t="n">
         <v>0.05</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="DH9" t="n">
-        <v>95.09999999999999</v>
+        <v>96.33</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.9</v>
+        <v>5.33</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM9" t="n">
-        <v>47.15</v>
+        <v>47.57</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.75</v>
+        <v>11.48</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.1</v>
+        <v>10.19</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.95</v>
+        <v>6.86</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.15</v>
+        <v>48.67</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.45</v>
+        <v>12.19</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.2</v>
+        <v>7.86</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.9</v>
+        <v>17.71</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="EC9" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="G10" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H10" t="n">
-        <v>98.7</v>
+        <v>94</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="K10" t="n">
-        <v>5.3</v>
+        <v>5.36</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="M10" t="n">
-        <v>47.7</v>
+        <v>45.18</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="P10" t="n">
-        <v>7.2</v>
+        <v>7.27</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.5</v>
+        <v>11.45</v>
       </c>
       <c r="R10" t="n">
-        <v>9.6</v>
+        <v>9.73</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>52.8</v>
+        <v>51.64</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>12</v>
+        <v>11.64</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.6</v>
+        <v>7.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.4</v>
+        <v>4.09</v>
       </c>
       <c r="AC10" t="n">
-        <v>16.7</v>
+        <v>16.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AF10" t="n">
         <v>0.3</v>
@@ -4774,70 +4774,70 @@
         <v>0.9</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.85</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.05</v>
+        <v>5.14</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
       <c r="BR10" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU10" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BV10" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW10" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BX10" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.91</v>
+        <v>3.19</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.01</v>
+        <v>4.06</v>
       </c>
       <c r="CC10" t="n">
         <v>4.19</v>
@@ -4852,7 +4852,7 @@
         <v>2.33</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CH10" t="n">
         <v>1.55</v>
@@ -4867,28 +4867,28 @@
         <v>1.52</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CO10" t="n">
         <v>1.17</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="CR10" t="n">
         <v>1.34</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CT10" t="n">
         <v>3.36</v>
@@ -4897,7 +4897,7 @@
         <v>1.61</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CW10" t="n">
         <v>1.58</v>
@@ -4906,97 +4906,97 @@
         <v>1.53</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.41</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DC10" t="n">
         <v>1.63</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="DH10" t="n">
-        <v>91.65000000000001</v>
+        <v>89.52</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.55</v>
+        <v>4.62</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="DM10" t="n">
-        <v>40.2</v>
+        <v>39.24</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="DP10" t="n">
-        <v>7.2</v>
+        <v>7.24</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.65</v>
+        <v>11.62</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.6</v>
+        <v>50.1</v>
       </c>
       <c r="DW10" t="n">
         <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.35</v>
+        <v>11.19</v>
       </c>
       <c r="DY10" t="n">
         <v>7</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.35</v>
+        <v>4.19</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.7</v>
+        <v>15.48</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>0.3</v>
@@ -5096,139 +5096,139 @@
         <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>92.09</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AK11" t="n">
         <v>2</v>
       </c>
-      <c r="AI11" t="n">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AL11" t="n">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN11" t="n">
-        <v>41.5</v>
+        <v>42.91</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11.7</v>
+        <v>11.82</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.5</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>45.3</v>
+        <v>45.36</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA11" t="n">
-        <v>12</v>
+        <v>12.45</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.9</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="BD11" t="n">
-        <v>19.2</v>
+        <v>20</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.85</v>
+        <v>9.9</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="BR11" t="n">
-        <v>95</v>
+        <v>90.48</v>
       </c>
       <c r="BS11" t="n">
-        <v>85</v>
+        <v>80.95</v>
       </c>
       <c r="BT11" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU11" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV11" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW11" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX11" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY11" t="n">
         <v>3.19</v>
@@ -5237,43 +5237,43 @@
         <v>3.31</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.12</v>
+        <v>4.14</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF11" t="n">
         <v>2.39</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.59</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CN11" t="n">
         <v>1.96</v>
@@ -5282,7 +5282,7 @@
         <v>1.19</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CQ11" t="n">
         <v>2.56</v>
@@ -5291,7 +5291,7 @@
         <v>1.34</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CT11" t="n">
         <v>3.34</v>
@@ -5309,97 +5309,97 @@
         <v>1.53</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.42</v>
       </c>
       <c r="DA11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB11" t="n">
         <v>1.2</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="DH11" t="n">
-        <v>89.90000000000001</v>
+        <v>89.38</v>
       </c>
       <c r="DI11" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.3</v>
+        <v>44.91</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.7</v>
+        <v>10.81</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.25</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.15</v>
+        <v>8.19</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>45</v>
+        <v>45.05</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.55</v>
+        <v>12.76</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.25</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.4</v>
+        <v>19.81</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0.1</v>
@@ -5499,52 +5499,52 @@
         <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AI12" t="n">
-        <v>94.8</v>
+        <v>93.91</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.2</v>
+        <v>4.09</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN12" t="n">
-        <v>43.7</v>
+        <v>44.18</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12.7</v>
+        <v>12.64</v>
       </c>
       <c r="AR12" t="n">
-        <v>9.1</v>
+        <v>8.91</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.199999999999999</v>
+        <v>7.82</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>42.3</v>
+        <v>41.55</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.1</v>
+        <v>10.64</v>
       </c>
       <c r="BB12" t="n">
-        <v>7</v>
+        <v>7.27</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="BD12" t="n">
-        <v>21</v>
+        <v>19.64</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.6</v>
+        <v>9.52</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.5</v>
+        <v>4.62</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU12" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BV12" t="n">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="BW12" t="n">
-        <v>10</v>
+        <v>14.29</v>
       </c>
       <c r="BX12" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY12" t="n">
         <v>3.21</v>
@@ -5640,28 +5640,28 @@
         <v>3.28</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.05</v>
+        <v>4.12</v>
       </c>
       <c r="CC12" t="n">
-        <v>5.04</v>
+        <v>5.1</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.47</v>
+        <v>5.77</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF12" t="n">
         <v>2.45</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI12" t="n">
         <v>2.16</v>
@@ -5670,25 +5670,25 @@
         <v>1.66</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM12" t="n">
         <v>2.67</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
@@ -5706,7 +5706,7 @@
         <v>2.29</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX12" t="n">
         <v>1.5</v>
@@ -5724,52 +5724,52 @@
         <v>1.22</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="DH12" t="n">
-        <v>93.5</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.45</v>
+        <v>4.38</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM12" t="n">
-        <v>56.35</v>
+        <v>56</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DO12" t="n">
         <v>2</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.05</v>
+        <v>13</v>
       </c>
       <c r="DQ12" t="n">
-        <v>8.85</v>
+        <v>8.76</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.050000000000001</v>
+        <v>7.86</v>
       </c>
       <c r="DS12" t="n">
         <v>0.1</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>44.25</v>
+        <v>43.76</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.25</v>
+        <v>11.48</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.5</v>
+        <v>7.62</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.75</v>
+        <v>3.86</v>
       </c>
       <c r="EA12" t="n">
-        <v>22</v>
+        <v>21.24</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>0.3</v>
@@ -5908,46 +5908,46 @@
         <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AI13" t="n">
-        <v>106.9</v>
+        <v>105.36</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL13" t="n">
-        <v>5</v>
+        <v>4.64</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AN13" t="n">
-        <v>49.6</v>
+        <v>48.55</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.6</v>
+        <v>12.73</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>7.91</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.1</v>
+        <v>1.45</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>48.9</v>
+        <v>48.36</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>12.9</v>
+        <v>12.73</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.7</v>
+        <v>4.64</v>
       </c>
       <c r="BD13" t="n">
-        <v>17.9</v>
+        <v>17.45</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.9</v>
+        <v>8.81</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="BJ13" t="n">
         <v>1.1</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.75</v>
+        <v>3.86</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="BR13" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT13" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BV13" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BW13" t="n">
-        <v>10</v>
+        <v>14.29</v>
       </c>
       <c r="BX13" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY13" t="n">
         <v>2.7</v>
@@ -6043,16 +6043,16 @@
         <v>2.9</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.61</v>
+        <v>3.69</v>
       </c>
       <c r="CE13" t="n">
         <v>1.29</v>
@@ -6061,7 +6061,7 @@
         <v>2.37</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CH13" t="n">
         <v>1.53</v>
@@ -6076,22 +6076,22 @@
         <v>1.39</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO13" t="n">
         <v>1.19</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
@@ -6121,7 +6121,7 @@
         <v>2.5</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DB13" t="n">
         <v>1.21</v>
@@ -6133,46 +6133,46 @@
         <v>2.68</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF13" t="n">
         <v>0.95</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="DH13" t="n">
-        <v>95.8</v>
+        <v>95.52</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.75</v>
+        <v>4.57</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.5</v>
+        <v>43.24</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.4</v>
+        <v>11.48</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.1</v>
+        <v>12.19</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.75</v>
+        <v>7.71</v>
       </c>
       <c r="DS13" t="n">
         <v>0.1</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.8</v>
+        <v>47.57</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.75</v>
+        <v>11.72</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.3</v>
+        <v>7.29</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="EA13" t="n">
-        <v>19</v>
+        <v>18.71</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>0.36</v>
@@ -1469,139 +1469,139 @@
         <v>1.36</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AI2" t="n">
-        <v>84.2</v>
+        <v>84.73</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.8</v>
+        <v>4.73</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AN2" t="n">
-        <v>50.5</v>
+        <v>48.45</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10.5</v>
+        <v>10.73</v>
       </c>
       <c r="AR2" t="n">
-        <v>12</v>
+        <v>12.55</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.6</v>
+        <v>7.36</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>48.5</v>
+        <v>49.36</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.4</v>
+        <v>12.91</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.8</v>
+        <v>4.91</v>
       </c>
       <c r="BD2" t="n">
-        <v>17.6</v>
+        <v>19</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="BG2" t="n">
         <v>3.14</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.619999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BI2" t="n">
         <v>3.14</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL2" t="n">
         <v>0.86</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.24</v>
+        <v>5.09</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS2" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU2" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BV2" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BW2" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX2" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BY2" t="n">
         <v>1.87</v>
@@ -1610,46 +1610,46 @@
         <v>1.87</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.84</v>
+        <v>3.87</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="CE2" t="n">
         <v>1.29</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CG2" t="n">
         <v>3.3</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK2" t="n">
         <v>1.48</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CO2" t="n">
         <v>1.2</v>
@@ -1658,7 +1658,7 @@
         <v>1.69</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CR2" t="n">
         <v>1.35</v>
@@ -1673,10 +1673,10 @@
         <v>1.55</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CX2" t="n">
         <v>1.54</v>
@@ -1700,79 +1700,79 @@
         <v>2.73</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="DH2" t="n">
-        <v>100.19</v>
+        <v>99.73</v>
       </c>
       <c r="DI2" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.86</v>
+        <v>5.78</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DM2" t="n">
-        <v>69</v>
+        <v>67.14</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="DO2" t="n">
         <v>3</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.62</v>
+        <v>10.73</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.91</v>
+        <v>12.19</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.24</v>
+        <v>6.18</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.38</v>
+        <v>54.54</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.24</v>
+        <v>15.86</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.48</v>
+        <v>10.09</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.76</v>
+        <v>5.78</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.05</v>
+        <v>17.78</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>0.18</v>
@@ -1872,52 +1872,52 @@
         <v>1.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AI3" t="n">
-        <v>99.2</v>
+        <v>94.64</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.4</v>
+        <v>4.18</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN3" t="n">
-        <v>54.1</v>
+        <v>51.64</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.6</v>
+        <v>10.64</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.1</v>
+        <v>12.45</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.9</v>
+        <v>6.36</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>54.5</v>
+        <v>52.64</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA3" t="n">
-        <v>14.6</v>
+        <v>14.09</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.9</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.7</v>
+        <v>4.64</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.4</v>
+        <v>19.27</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.19</v>
+        <v>8.18</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="BQ3" t="n">
         <v>3.95</v>
       </c>
       <c r="BR3" t="n">
-        <v>90.48</v>
+        <v>86.36</v>
       </c>
       <c r="BS3" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV3" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX3" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BY3" t="n">
         <v>2.05</v>
@@ -2013,16 +2013,16 @@
         <v>2.1</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.78</v>
+        <v>3.83</v>
       </c>
       <c r="CB3" t="n">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.27</v>
+        <v>2.61</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.45</v>
+        <v>2.78</v>
       </c>
       <c r="CE3" t="n">
         <v>1.3</v>
@@ -2031,13 +2031,13 @@
         <v>2.4</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CH3" t="n">
         <v>1.52</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.62</v>
@@ -2052,7 +2052,7 @@
         <v>2.49</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CO3" t="n">
         <v>1.18</v>
@@ -2067,7 +2067,7 @@
         <v>1.35</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CT3" t="n">
         <v>3.3</v>
@@ -2082,13 +2082,13 @@
         <v>1.63</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY3" t="n">
         <v>1.9</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DA3" t="n">
         <v>1.92</v>
@@ -2097,52 +2097,52 @@
         <v>1.21</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="DG3" t="n">
         <v>2</v>
       </c>
       <c r="DH3" t="n">
-        <v>101.19</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.86</v>
+        <v>3.77</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM3" t="n">
-        <v>57.38</v>
+        <v>56</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.67</v>
+        <v>11.14</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.52</v>
+        <v>12.68</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.38</v>
+        <v>6.59</v>
       </c>
       <c r="DS3" t="n">
         <v>0.09</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>53.1</v>
+        <v>52.23</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.29</v>
+        <v>14.04</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.380000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.9</v>
+        <v>4.86</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.62</v>
+        <v>19.55</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="4">
@@ -2185,61 +2185,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="H4" t="n">
-        <v>85.8</v>
+        <v>85.91</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="K4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="M4" t="n">
-        <v>44.5</v>
+        <v>45.09</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O4" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="P4" t="n">
-        <v>10.3</v>
+        <v>10.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.4</v>
+        <v>10.09</v>
       </c>
       <c r="R4" t="n">
-        <v>9.6</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>45.2</v>
+        <v>45.55</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.8</v>
+        <v>11.82</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.3</v>
+        <v>7.82</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.8</v>
+        <v>17.64</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AF4" t="n">
         <v>0.09</v>
@@ -2356,70 +2356,70 @@
         <v>1</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="BH4" t="n">
-        <v>11.38</v>
+        <v>11.32</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BM4" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="BP4" t="n">
         <v>5.05</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BT4" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BU4" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BV4" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX4" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.74</v>
+        <v>4.54</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.34</v>
+        <v>4.31</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="CC4" t="n">
         <v>5.75</v>
@@ -2431,19 +2431,19 @@
         <v>1.26</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK4" t="n">
         <v>1.42</v>
@@ -2452,10 +2452,10 @@
         <v>1.81</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CN4" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CO4" t="n">
         <v>1.16</v>
@@ -2464,7 +2464,7 @@
         <v>1.56</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CR4" t="n">
         <v>1.33</v>
@@ -2479,7 +2479,7 @@
         <v>1.67</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CW4" t="n">
         <v>1.63</v>
@@ -2494,7 +2494,7 @@
         <v>2.53</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DB4" t="n">
         <v>1.17</v>
@@ -2506,79 +2506,79 @@
         <v>2.39</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="DH4" t="n">
-        <v>79.84999999999999</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.09</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.29</v>
+        <v>4.5</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.1</v>
+        <v>44.41</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.91</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.33</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DR4" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>42.24</v>
+        <v>42.55</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.52</v>
+        <v>11.04</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.85</v>
+        <v>7.14</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.67</v>
+        <v>3.91</v>
       </c>
       <c r="EA4" t="n">
-        <v>16.57</v>
+        <v>16.55</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H5" t="n">
-        <v>125.7</v>
+        <v>126.55</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="K5" t="n">
-        <v>5.2</v>
+        <v>5.27</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="M5" t="n">
-        <v>61.5</v>
+        <v>62.09</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O5" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="P5" t="n">
-        <v>12.3</v>
+        <v>12.27</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.9</v>
+        <v>9.91</v>
       </c>
       <c r="R5" t="n">
-        <v>6</v>
+        <v>6.09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>55.5</v>
+        <v>55.55</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.4</v>
+        <v>17.45</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.4</v>
+        <v>12.55</v>
       </c>
       <c r="AB5" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.8</v>
+        <v>20.64</v>
       </c>
       <c r="AD5" t="n">
         <v>1.9</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2762,64 +2762,64 @@
         <v>3.14</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.1</v>
+        <v>9.23</v>
       </c>
       <c r="BI5" t="n">
         <v>3.14</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM5" t="n">
         <v>1</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BP5" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="BQ5" t="n">
         <v>5</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS5" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BT5" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU5" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV5" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX5" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY5" t="n">
         <v>1.56</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="CB5" t="n">
         <v>4.44</v>
@@ -2837,7 +2837,7 @@
         <v>2.42</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CH5" t="n">
         <v>1.52</v>
@@ -2852,10 +2852,10 @@
         <v>1.53</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CN5" t="n">
         <v>1.84</v>
@@ -2867,10 +2867,10 @@
         <v>1.66</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS5" t="n">
         <v>2.5</v>
@@ -2879,7 +2879,7 @@
         <v>3.27</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV5" t="n">
         <v>2.17</v>
@@ -2888,13 +2888,13 @@
         <v>1.74</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DA5" t="n">
         <v>1.88</v>
@@ -2912,76 +2912,76 @@
         <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DG5" t="n">
         <v>2.95</v>
       </c>
       <c r="DH5" t="n">
-        <v>123.05</v>
+        <v>123.6</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.1</v>
+        <v>5.14</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="DM5" t="n">
-        <v>58.1</v>
+        <v>58.54</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.57</v>
+        <v>12.54</v>
       </c>
       <c r="DQ5" t="n">
         <v>10.14</v>
       </c>
       <c r="DR5" t="n">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.95</v>
+        <v>55</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX5" t="n">
-        <v>16.19</v>
+        <v>16.27</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.1</v>
+        <v>11.23</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.09</v>
+        <v>5.05</v>
       </c>
       <c r="EA5" t="n">
-        <v>20</v>
+        <v>20.41</v>
       </c>
       <c r="EB5" t="n">
         <v>1.81</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="H6" t="n">
-        <v>109.9</v>
+        <v>108.18</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="K6" t="n">
-        <v>6.3</v>
+        <v>6.27</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M6" t="n">
-        <v>54</v>
+        <v>55.09</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="P6" t="n">
-        <v>11.5</v>
+        <v>11.82</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="R6" t="n">
-        <v>5.6</v>
+        <v>5.64</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="T6" t="n">
-        <v>3.4</v>
+        <v>3.09</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>56.1</v>
+        <v>57</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>16</v>
+        <v>15.73</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.6</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.4</v>
+        <v>7.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>18.4</v>
+        <v>18.64</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AF6" t="n">
         <v>0.18</v>
@@ -3162,70 +3162,70 @@
         <v>2.27</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.86</v>
+        <v>3.68</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.859999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.86</v>
+        <v>3.68</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BL6" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BN6" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.43</v>
+        <v>5.36</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="BS6" t="n">
-        <v>90.48</v>
+        <v>86.36</v>
       </c>
       <c r="BT6" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BU6" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BV6" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BW6" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BX6" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.21</v>
+        <v>4.24</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.46</v>
+        <v>4.47</v>
       </c>
       <c r="CC6" t="n">
         <v>2.03</v>
@@ -3237,16 +3237,16 @@
         <v>1.24</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CH6" t="n">
         <v>1.63</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.55</v>
@@ -3255,7 +3255,7 @@
         <v>1.42</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CM6" t="n">
         <v>2.62</v>
@@ -3270,13 +3270,13 @@
         <v>1.52</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CT6" t="n">
         <v>3.21</v>
@@ -3285,19 +3285,19 @@
         <v>1.7</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CW6" t="n">
         <v>1.57</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DA6" t="n">
         <v>2.04</v>
@@ -3306,52 +3306,52 @@
         <v>1.16</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="DH6" t="n">
-        <v>104.81</v>
+        <v>104.18</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.24</v>
+        <v>5.27</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM6" t="n">
-        <v>47.81</v>
+        <v>48.64</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.43</v>
+        <v>11.59</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.62</v>
+        <v>12.96</v>
       </c>
       <c r="DR6" t="n">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="DS6" t="n">
         <v>0.09</v>
@@ -3363,22 +3363,22 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54</v>
+        <v>54.54</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.62</v>
+        <v>14.54</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.19</v>
+        <v>8.23</v>
       </c>
       <c r="DZ6" t="n">
-        <v>6.43</v>
+        <v>6.32</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.67</v>
+        <v>19.73</v>
       </c>
       <c r="EB6" t="n">
         <v>1.72</v>
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0.27</v>
@@ -3484,100 +3484,100 @@
         <v>1.73</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AI7" t="n">
-        <v>110.9</v>
+        <v>108</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN7" t="n">
-        <v>46.9</v>
+        <v>45.73</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10</v>
+        <v>10.64</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.2</v>
+        <v>11.82</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.9</v>
+        <v>7.27</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>56.1</v>
+        <v>55.73</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.4</v>
+        <v>11.73</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.7</v>
+        <v>7.09</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.7</v>
+        <v>4.64</v>
       </c>
       <c r="BD7" t="n">
-        <v>18.6</v>
+        <v>18.36</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.140000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL7" t="n">
         <v>1.05</v>
@@ -3589,10 +3589,10 @@
         <v>2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BQ7" t="n">
         <v>4.05</v>
@@ -3601,22 +3601,22 @@
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT7" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BU7" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BV7" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BW7" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BX7" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
         <v>2.18</v>
@@ -3625,16 +3625,16 @@
         <v>2.27</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="CC7" t="n">
         <v>2.78</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="CE7" t="n">
         <v>1.26</v>
@@ -3646,7 +3646,7 @@
         <v>3.5</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CI7" t="n">
         <v>2.41</v>
@@ -3658,16 +3658,16 @@
         <v>1.53</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CN7" t="n">
         <v>1.84</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CP7" t="n">
         <v>1.56</v>
@@ -3688,22 +3688,22 @@
         <v>1.65</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CW7" t="n">
         <v>1.54</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DB7" t="n">
         <v>1.18</v>
@@ -3715,46 +3715,46 @@
         <v>2.42</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="DH7" t="n">
-        <v>110.76</v>
+        <v>109.32</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.05</v>
+        <v>4.91</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DM7" t="n">
-        <v>53.71</v>
+        <v>52.82</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.859999999999999</v>
+        <v>10.18</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.67</v>
+        <v>10.54</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.62</v>
+        <v>6.82</v>
       </c>
       <c r="DS7" t="n">
         <v>0.09</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>58.24</v>
+        <v>57.96</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.29</v>
+        <v>7.45</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.62</v>
+        <v>5.55</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.24</v>
+        <v>17.18</v>
       </c>
       <c r="EB7" t="n">
         <v>1.6</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>0.09</v>
@@ -3887,139 +3887,139 @@
         <v>1.64</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="AI8" t="n">
-        <v>80.90000000000001</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT8" t="n">
         <v>2</v>
       </c>
-      <c r="AL8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AU8" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>46.8</v>
+        <v>48.18</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA8" t="n">
-        <v>10.9</v>
+        <v>11.09</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.8</v>
+        <v>7.18</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.3</v>
+        <v>18.45</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.86</v>
+        <v>3.73</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.81</v>
+        <v>10</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.86</v>
+        <v>3.73</v>
       </c>
       <c r="BJ8" t="n">
         <v>1.05</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="BO8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.76</v>
+        <v>4.82</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.14</v>
+        <v>4.32</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS8" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="BT8" t="n">
-        <v>80.95</v>
+        <v>77.27</v>
       </c>
       <c r="BU8" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BV8" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BW8" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BX8" t="n">
-        <v>85.70999999999999</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BY8" t="n">
         <v>2.71</v>
@@ -4028,16 +4028,16 @@
         <v>2.82</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="CB8" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.07</v>
+        <v>3.97</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.17</v>
+        <v>4.06</v>
       </c>
       <c r="CE8" t="n">
         <v>1.28</v>
@@ -4049,10 +4049,10 @@
         <v>3.37</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.57</v>
@@ -4061,7 +4061,7 @@
         <v>1.43</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM8" t="n">
         <v>2.6</v>
@@ -4076,7 +4076,7 @@
         <v>1.62</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CR8" t="n">
         <v>1.34</v>
@@ -4106,7 +4106,7 @@
         <v>2.45</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB8" t="n">
         <v>1.2</v>
@@ -4118,79 +4118,79 @@
         <v>2.59</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.09</v>
+        <v>93.5</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.76</v>
+        <v>4.91</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.81</v>
+        <v>47.96</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.86</v>
+        <v>11.69</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10</v>
+        <v>10.09</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.19</v>
+        <v>6.32</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47.95</v>
+        <v>48.59</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.76</v>
+        <v>11.82</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.76</v>
+        <v>6.95</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5</v>
+        <v>4.87</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.48</v>
+        <v>18.55</v>
       </c>
       <c r="EB8" t="n">
         <v>1.44</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,139 +4290,139 @@
         <v>1.36</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AI9" t="n">
-        <v>95.59999999999999</v>
+        <v>94.27</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.2</v>
+        <v>5.27</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AN9" t="n">
-        <v>50.2</v>
+        <v>48.91</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>12.73</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.6</v>
+        <v>10.64</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.9</v>
+        <v>7.27</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>49.3</v>
+        <v>48.82</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.8</v>
+        <v>11.91</v>
       </c>
       <c r="BB9" t="n">
         <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.5</v>
+        <v>19.27</v>
       </c>
       <c r="BE9" t="n">
         <v>1.38</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.67</v>
+        <v>4.77</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
       <c r="BR9" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT9" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU9" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BV9" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX9" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BY9" t="n">
         <v>2.61</v>
@@ -4431,16 +4431,16 @@
         <v>2.84</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.76</v>
+        <v>3.79</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.11</v>
+        <v>3.25</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.22</v>
+        <v>3.48</v>
       </c>
       <c r="CE9" t="n">
         <v>1.32</v>
@@ -4449,13 +4449,13 @@
         <v>2.45</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CH9" t="n">
         <v>1.49</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.61</v>
@@ -4464,13 +4464,13 @@
         <v>1.47</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CM9" t="n">
         <v>2.5</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO9" t="n">
         <v>1.2</v>
@@ -4485,28 +4485,28 @@
         <v>1.35</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY9" t="n">
         <v>1.84</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="DA9" t="n">
         <v>1.96</v>
@@ -4521,79 +4521,79 @@
         <v>2.79</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="DH9" t="n">
-        <v>96.33</v>
+        <v>95.64</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.33</v>
+        <v>5.36</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="DM9" t="n">
-        <v>47.57</v>
+        <v>47.04</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.48</v>
+        <v>11.41</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.19</v>
+        <v>10.23</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.86</v>
+        <v>7.05</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.67</v>
+        <v>48.46</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.19</v>
+        <v>12.23</v>
       </c>
       <c r="DY9" t="n">
         <v>7.86</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.71</v>
+        <v>17.68</v>
       </c>
       <c r="EB9" t="n">
         <v>1.42</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,85 +4693,85 @@
         <v>1.18</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AI10" t="n">
-        <v>84.59999999999999</v>
+        <v>85.36</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AN10" t="n">
-        <v>32.7</v>
+        <v>35.27</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.2</v>
+        <v>7.18</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.8</v>
+        <v>11.64</v>
       </c>
       <c r="AS10" t="n">
-        <v>8</v>
+        <v>8.27</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>48.4</v>
+        <v>48.64</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.7</v>
+        <v>10.91</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.4</v>
+        <v>6.55</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.3</v>
+        <v>4.36</v>
       </c>
       <c r="BD10" t="n">
-        <v>14.7</v>
+        <v>14.55</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BG10" t="n">
         <v>3.14</v>
@@ -4786,46 +4786,46 @@
         <v>1</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BP10" t="n">
         <v>5.14</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="BR10" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS10" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT10" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU10" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV10" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW10" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX10" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY10" t="n">
         <v>3.02</v>
@@ -4837,13 +4837,13 @@
         <v>3.84</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.53</v>
+        <v>4.37</v>
       </c>
       <c r="CE10" t="n">
         <v>1.28</v>
@@ -4852,28 +4852,28 @@
         <v>2.33</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CH10" t="n">
         <v>1.55</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.57</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CO10" t="n">
         <v>1.17</v>
@@ -4882,7 +4882,7 @@
         <v>1.6</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CR10" t="n">
         <v>1.34</v>
@@ -4897,73 +4897,73 @@
         <v>1.61</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CX10" t="n">
         <v>1.53</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.41</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="DB10" t="n">
         <v>1.19</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="DE10" t="n">
         <v>0.14</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.48</v>
+        <v>2.37</v>
       </c>
       <c r="DH10" t="n">
-        <v>89.52</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ10" t="n">
         <v>1.14</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.62</v>
+        <v>4.45</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="DM10" t="n">
-        <v>39.24</v>
+        <v>40.22</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="DP10" t="n">
-        <v>7.24</v>
+        <v>7.22</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.62</v>
+        <v>11.54</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.91</v>
+        <v>9</v>
       </c>
       <c r="DS10" t="n">
         <v>0.09</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.1</v>
+        <v>50.14</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.19</v>
+        <v>11.28</v>
       </c>
       <c r="DY10" t="n">
-        <v>7</v>
+        <v>7.05</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.19</v>
+        <v>4.22</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.48</v>
+        <v>15.36</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="H11" t="n">
-        <v>86.40000000000001</v>
+        <v>85</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="M11" t="n">
-        <v>47.1</v>
+        <v>46.91</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="O11" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="P11" t="n">
-        <v>9.699999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.699999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>7.8</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>44.7</v>
+        <v>44.09</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.1</v>
+        <v>13.18</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.6</v>
+        <v>8.82</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.5</v>
+        <v>4.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.6</v>
+        <v>19.27</v>
       </c>
       <c r="AD11" t="n">
         <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AF11" t="n">
         <v>0.09</v>
@@ -5177,70 +5177,70 @@
         <v>1.82</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.9</v>
+        <v>10.09</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL11" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="BR11" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS11" t="n">
-        <v>80.95</v>
+        <v>77.27</v>
       </c>
       <c r="BT11" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BU11" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV11" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX11" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="CC11" t="n">
         <v>4</v>
@@ -5249,19 +5249,19 @@
         <v>4.14</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF11" t="n">
         <v>2.39</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="CH11" t="n">
         <v>1.52</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.59</v>
@@ -5270,13 +5270,13 @@
         <v>1.45</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CO11" t="n">
         <v>1.19</v>
@@ -5315,7 +5315,7 @@
         <v>2.42</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DB11" t="n">
         <v>1.2</v>
@@ -5324,82 +5324,82 @@
         <v>1.66</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="DH11" t="n">
-        <v>89.38</v>
+        <v>88.54000000000001</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="DM11" t="n">
         <v>44.91</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.81</v>
+        <v>10.87</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.619999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.19</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>45.05</v>
+        <v>44.72</v>
       </c>
       <c r="DW11" t="n">
         <v>0.09</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.76</v>
+        <v>12.81</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.470000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.29</v>
+        <v>4.22</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.81</v>
+        <v>19.64</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="12">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="H12" t="n">
-        <v>92.2</v>
+        <v>92.64</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M12" t="n">
-        <v>69</v>
+        <v>66.73</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="O12" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="P12" t="n">
-        <v>13.4</v>
+        <v>13.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="R12" t="n">
-        <v>7.9</v>
+        <v>7.55</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>46.2</v>
+        <v>45.82</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.4</v>
+        <v>12.27</v>
       </c>
       <c r="AA12" t="n">
-        <v>8</v>
+        <v>7.82</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AC12" t="n">
-        <v>23</v>
+        <v>23.09</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AF12" t="n">
         <v>0.09</v>
@@ -5580,70 +5580,70 @@
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.52</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.62</v>
+        <v>4.59</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.9</v>
+        <v>4.77</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BT12" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU12" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV12" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW12" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX12" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.21</v>
+        <v>3.43</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.28</v>
+        <v>3.52</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.12</v>
+        <v>4.14</v>
       </c>
       <c r="CC12" t="n">
         <v>5.1</v>
@@ -5661,19 +5661,19 @@
         <v>3.25</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CK12" t="n">
         <v>1.41</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM12" t="n">
         <v>2.67</v>
@@ -5685,25 +5685,25 @@
         <v>1.2</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="CU12" t="n">
         <v>1.54</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CW12" t="n">
         <v>1.68</v>
@@ -5727,82 +5727,82 @@
         <v>1.71</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="DE12" t="n">
         <v>0.09</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="DH12" t="n">
-        <v>93.09999999999999</v>
+        <v>93.28</v>
       </c>
       <c r="DI12" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DO12" t="n">
         <v>1.95</v>
       </c>
-      <c r="DK12" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="DL12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DM12" t="n">
-        <v>56</v>
-      </c>
-      <c r="DN12" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="DO12" t="n">
-        <v>2</v>
-      </c>
       <c r="DP12" t="n">
-        <v>13</v>
+        <v>13.23</v>
       </c>
       <c r="DQ12" t="n">
-        <v>8.76</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.86</v>
+        <v>7.68</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.76</v>
+        <v>43.68</v>
       </c>
       <c r="DW12" t="n">
         <v>0.09</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.48</v>
+        <v>11.46</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.62</v>
+        <v>7.55</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.24</v>
+        <v>21.36</v>
       </c>
       <c r="EB12" t="n">
         <v>1.4</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="H13" t="n">
-        <v>84.7</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="M13" t="n">
-        <v>37.4</v>
+        <v>39.45</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O13" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="P13" t="n">
-        <v>10.9</v>
+        <v>10.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.6</v>
+        <v>12.09</v>
       </c>
       <c r="R13" t="n">
-        <v>7.5</v>
+        <v>7.64</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>46.7</v>
+        <v>46.82</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>10.6</v>
+        <v>11.73</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.4</v>
+        <v>7.27</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="AC13" t="n">
-        <v>20.1</v>
+        <v>19.73</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>1.55</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.81</v>
+        <v>8.68</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM13" t="n">
         <v>0.95</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.86</v>
+        <v>3.77</v>
       </c>
       <c r="BQ13" t="n">
         <v>3.86</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS13" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT13" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU13" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV13" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BW13" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX13" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="CA13" t="n">
         <v>3.69</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="CC13" t="n">
         <v>3.56</v>
@@ -6061,13 +6061,13 @@
         <v>2.37</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CH13" t="n">
         <v>1.53</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.59</v>
@@ -6079,19 +6079,19 @@
         <v>1.74</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
@@ -6118,7 +6118,7 @@
         <v>1.74</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="DA13" t="n">
         <v>2.09</v>
@@ -6130,82 +6130,82 @@
         <v>1.69</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="DH13" t="n">
-        <v>95.52</v>
+        <v>95.09</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.57</v>
+        <v>4.55</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.24</v>
+        <v>44</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.48</v>
+        <v>11.32</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.19</v>
+        <v>12.41</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.71</v>
+        <v>7.78</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.57</v>
+        <v>47.59</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.72</v>
+        <v>12.23</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.29</v>
+        <v>7.68</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.43</v>
+        <v>4.55</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.71</v>
+        <v>18.59</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -5884,19 +5884,19 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>11.73</v>
+        <v>11.64</v>
       </c>
       <c r="AA13" t="n">
         <v>7.27</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.45</v>
+        <v>4.36</v>
       </c>
       <c r="AC13" t="n">
         <v>19.73</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
         <v>1.45</v>
@@ -6190,19 +6190,19 @@
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.23</v>
+        <v>12.19</v>
       </c>
       <c r="DY13" t="n">
         <v>7.68</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="EA13" t="n">
         <v>18.59</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="EC13" t="n">
         <v>1.5</v>

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -2185,61 +2185,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="n">
-        <v>85.91</v>
+        <v>89.42</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>45.09</v>
+        <v>45.58</v>
       </c>
       <c r="N4" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="P4" t="n">
-        <v>10.18</v>
+        <v>10.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.09</v>
+        <v>10.83</v>
       </c>
       <c r="R4" t="n">
-        <v>9.550000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>45.55</v>
+        <v>46.42</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.82</v>
+        <v>11.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.82</v>
+        <v>7.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.64</v>
+        <v>17.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AF4" t="n">
         <v>0.09</v>
@@ -2356,34 +2356,34 @@
         <v>1</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="BH4" t="n">
-        <v>11.32</v>
+        <v>11.22</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.05</v>
+        <v>4.96</v>
       </c>
       <c r="BQ4" t="n">
         <v>6</v>
@@ -2392,34 +2392,34 @@
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BU4" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BV4" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX4" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.17</v>
+        <v>4.07</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.54</v>
+        <v>4.44</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.31</v>
+        <v>4.28</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.6</v>
+        <v>4.57</v>
       </c>
       <c r="CC4" t="n">
         <v>5.75</v>
@@ -2431,10 +2431,10 @@
         <v>1.26</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CH4" t="n">
         <v>1.58</v>
@@ -2446,16 +2446,16 @@
         <v>1.63</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CO4" t="n">
         <v>1.16</v>
@@ -2464,7 +2464,7 @@
         <v>1.56</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CR4" t="n">
         <v>1.33</v>
@@ -2482,19 +2482,19 @@
         <v>2.39</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CX4" t="n">
         <v>1.48</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.53</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DB4" t="n">
         <v>1.17</v>
@@ -2509,43 +2509,43 @@
         <v>0.13</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="DH4" t="n">
-        <v>80.18000000000001</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.41</v>
+        <v>44.7</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.220000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DS4" t="n">
         <v>0.04</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>42.55</v>
+        <v>43.13</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.04</v>
+        <v>11</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.14</v>
+        <v>7.13</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="EA4" t="n">
-        <v>16.55</v>
+        <v>16.65</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="5">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,139 +4290,139 @@
         <v>1.36</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="n">
         <v>3</v>
       </c>
       <c r="AI9" t="n">
-        <v>94.27</v>
+        <v>93</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.27</v>
+        <v>5.33</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>48.91</v>
+        <v>47.58</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.73</v>
+        <v>13.17</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.64</v>
+        <v>10.67</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.27</v>
+        <v>7.58</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AU9" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>48.82</v>
+        <v>48.42</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.91</v>
+        <v>11.92</v>
       </c>
       <c r="BB9" t="n">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.27</v>
+        <v>19</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="BH9" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.77</v>
+        <v>4.7</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.18</v>
+        <v>5.22</v>
       </c>
       <c r="BR9" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS9" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT9" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU9" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BV9" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX9" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BY9" t="n">
         <v>2.61</v>
@@ -4431,19 +4431,19 @@
         <v>2.84</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.48</v>
+        <v>3.36</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CF9" t="n">
         <v>2.45</v>
@@ -4455,37 +4455,37 @@
         <v>1.49</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.61</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CO9" t="n">
         <v>1.2</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CT9" t="n">
         <v>3.31</v>
@@ -4494,73 +4494,73 @@
         <v>1.54</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CX9" t="n">
         <v>1.51</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.45</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="DB9" t="n">
         <v>1.22</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DG9" t="n">
         <v>3</v>
       </c>
       <c r="DH9" t="n">
-        <v>95.64</v>
+        <v>94.91</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.36</v>
+        <v>5.39</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="DM9" t="n">
-        <v>47.04</v>
+        <v>46.43</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.41</v>
+        <v>11.7</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.23</v>
+        <v>10.26</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.05</v>
+        <v>7.22</v>
       </c>
       <c r="DS9" t="n">
         <v>0.13</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.46</v>
+        <v>48.26</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.23</v>
+        <v>12.22</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.86</v>
+        <v>7.91</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.36</v>
+        <v>4.3</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.68</v>
+        <v>17.61</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="10">

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>0.36</v>
@@ -1469,139 +1469,139 @@
         <v>1.36</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>84.73</v>
+        <v>86.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.73</v>
+        <v>4.83</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="AN2" t="n">
-        <v>48.45</v>
+        <v>48.42</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10.73</v>
+        <v>10.75</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.55</v>
+        <v>12.67</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.36</v>
+        <v>7.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>49.36</v>
+        <v>49.67</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.91</v>
+        <v>13.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>8</v>
+        <v>8.67</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="BD2" t="n">
-        <v>19</v>
+        <v>19.25</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.449999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM2" t="n">
         <v>0.91</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.27</v>
+        <v>4.52</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.09</v>
+        <v>4.91</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS2" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT2" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BU2" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV2" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX2" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BY2" t="n">
         <v>1.87</v>
@@ -1610,16 +1610,16 @@
         <v>1.87</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="CB2" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="CE2" t="n">
         <v>1.29</v>
@@ -1628,7 +1628,7 @@
         <v>2.46</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CH2" t="n">
         <v>1.51</v>
@@ -1643,7 +1643,7 @@
         <v>1.48</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CM2" t="n">
         <v>2.47</v>
@@ -1655,7 +1655,7 @@
         <v>1.2</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CQ2" t="n">
         <v>2.7</v>
@@ -1664,7 +1664,7 @@
         <v>1.35</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CT2" t="n">
         <v>3.3</v>
@@ -1673,7 +1673,7 @@
         <v>1.55</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CW2" t="n">
         <v>1.65</v>
@@ -1694,52 +1694,52 @@
         <v>1.22</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="DH2" t="n">
-        <v>99.73</v>
+        <v>100</v>
       </c>
       <c r="DI2" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="DK2" t="n">
         <v>5.78</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="DM2" t="n">
-        <v>67.14</v>
+        <v>66.31</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="DO2" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.73</v>
+        <v>10.74</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.19</v>
+        <v>12.26</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.18</v>
+        <v>6.3</v>
       </c>
       <c r="DS2" t="n">
         <v>0.22</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.54</v>
+        <v>54.48</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.86</v>
+        <v>16.04</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.09</v>
+        <v>10.35</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.78</v>
+        <v>17.96</v>
       </c>
       <c r="EB2" t="n">
         <v>1.89</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G3" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="H3" t="n">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="K3" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>60.36</v>
+        <v>60.67</v>
       </c>
       <c r="N3" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="O3" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="P3" t="n">
-        <v>11.64</v>
+        <v>11.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.91</v>
+        <v>12.75</v>
       </c>
       <c r="R3" t="n">
-        <v>6.82</v>
+        <v>7.08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="U3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>51.82</v>
+        <v>51.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z3" t="n">
         <v>14</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.91</v>
+        <v>9.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.09</v>
+        <v>4.75</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.82</v>
+        <v>19.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
         <v>0.09</v>
@@ -1953,70 +1953,70 @@
         <v>2.18</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.18</v>
+        <v>8.48</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.18</v>
+        <v>4.26</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.95</v>
+        <v>4.17</v>
       </c>
       <c r="BR3" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BT3" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BU3" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV3" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX3" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BY3" t="n">
         <v>2.05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="CC3" t="n">
         <v>2.61</v>
@@ -2031,7 +2031,7 @@
         <v>2.4</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CH3" t="n">
         <v>1.52</v>
@@ -2058,7 +2058,7 @@
         <v>1.18</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CQ3" t="n">
         <v>2.63</v>
@@ -2067,7 +2067,7 @@
         <v>1.35</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CT3" t="n">
         <v>3.3</v>
@@ -2076,7 +2076,7 @@
         <v>1.57</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CW3" t="n">
         <v>1.63</v>
@@ -2097,52 +2097,52 @@
         <v>1.21</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="DE3" t="n">
         <v>0.13</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="DG3" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DH3" t="n">
-        <v>98.81999999999999</v>
+        <v>98.22</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.77</v>
+        <v>3.83</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="DM3" t="n">
-        <v>56</v>
+        <v>56.35</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.14</v>
+        <v>11.13</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.68</v>
+        <v>12.61</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.59</v>
+        <v>6.74</v>
       </c>
       <c r="DS3" t="n">
         <v>0.09</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>52.23</v>
+        <v>51.96</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX3" t="n">
         <v>14.04</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.18</v>
+        <v>9.35</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.86</v>
+        <v>4.7</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.55</v>
+        <v>19.35</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="4">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>0.27</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="AI5" t="n">
-        <v>120.64</v>
+        <v>119.17</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AL5" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="BC5" t="n">
         <v>5</v>
       </c>
-      <c r="AM5" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>12.82</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>10.36</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>54.45</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>15.09</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>9.91</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.18</v>
-      </c>
       <c r="BD5" t="n">
-        <v>20.18</v>
+        <v>20.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.23</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BM5" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS5" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BT5" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU5" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV5" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX5" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY5" t="n">
         <v>1.56</v>
@@ -2819,16 +2819,16 @@
         <v>1.56</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.44</v>
+        <v>4.41</v>
       </c>
       <c r="CC5" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CD5" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="CE5" t="n">
         <v>1.29</v>
@@ -2837,16 +2837,16 @@
         <v>2.42</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CH5" t="n">
         <v>1.52</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CK5" t="n">
         <v>1.53</v>
@@ -2855,10 +2855,10 @@
         <v>2</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CO5" t="n">
         <v>1.19</v>
@@ -2873,19 +2873,19 @@
         <v>1.35</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CT5" t="n">
         <v>3.27</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CX5" t="n">
         <v>1.55</v>
@@ -2903,85 +2903,85 @@
         <v>1.22</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="DH5" t="n">
-        <v>123.6</v>
+        <v>122.7</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.14</v>
+        <v>5.09</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="DM5" t="n">
-        <v>58.54</v>
+        <v>57.96</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.54</v>
+        <v>12.43</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.14</v>
+        <v>10.13</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.05</v>
+        <v>6.26</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55</v>
+        <v>54.35</v>
       </c>
       <c r="DW5" t="n">
         <v>0.09</v>
       </c>
       <c r="DX5" t="n">
-        <v>16.27</v>
+        <v>16</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.23</v>
+        <v>11.05</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.05</v>
+        <v>4.96</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.41</v>
+        <v>20.57</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F6" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="G6" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="H6" t="n">
-        <v>108.18</v>
+        <v>107.08</v>
       </c>
       <c r="I6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J6" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="K6" t="n">
-        <v>6.27</v>
+        <v>6.17</v>
       </c>
       <c r="L6" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M6" t="n">
-        <v>55.09</v>
+        <v>54.42</v>
       </c>
       <c r="N6" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="O6" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="P6" t="n">
-        <v>11.82</v>
+        <v>11.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>14.83</v>
       </c>
       <c r="R6" t="n">
-        <v>5.64</v>
+        <v>6.08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>3.09</v>
+        <v>2.83</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>57</v>
+        <v>57.25</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.73</v>
+        <v>15.17</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.640000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.09</v>
+        <v>6.83</v>
       </c>
       <c r="AC6" t="n">
-        <v>18.64</v>
+        <v>19.58</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AF6" t="n">
         <v>0.18</v>
@@ -3162,70 +3162,70 @@
         <v>2.27</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.68</v>
+        <v>3.57</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.77</v>
+        <v>9.65</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.68</v>
+        <v>3.57</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL6" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.36</v>
+        <v>5.3</v>
       </c>
       <c r="BR6" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS6" t="n">
-        <v>86.36</v>
+        <v>82.61</v>
       </c>
       <c r="BT6" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BU6" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BV6" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BW6" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BX6" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.24</v>
+        <v>4.27</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="CC6" t="n">
         <v>2.03</v>
@@ -3237,10 +3237,10 @@
         <v>1.24</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="CH6" t="n">
         <v>1.63</v>
@@ -3258,25 +3258,25 @@
         <v>1.82</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="CP6" t="n">
         <v>1.52</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CT6" t="n">
         <v>3.21</v>
@@ -3297,94 +3297,94 @@
         <v>1.78</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DB6" t="n">
         <v>1.16</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DE6" t="n">
         <v>0.22</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="DG6" t="n">
         <v>2.78</v>
       </c>
       <c r="DH6" t="n">
-        <v>104.18</v>
+        <v>103.78</v>
       </c>
       <c r="DI6" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM6" t="n">
-        <v>48.64</v>
+        <v>48.57</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.59</v>
+        <v>11.65</v>
       </c>
       <c r="DQ6" t="n">
         <v>12.96</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.95</v>
+        <v>7.13</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54.54</v>
+        <v>54.78</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.54</v>
+        <v>14.3</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.23</v>
+        <v>8.09</v>
       </c>
       <c r="DZ6" t="n">
-        <v>6.32</v>
+        <v>6.22</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.73</v>
+        <v>20.17</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>0.27</v>
@@ -3484,139 +3484,139 @@
         <v>1.73</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AI7" t="n">
-        <v>108</v>
+        <v>106.33</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AL7" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AN7" t="n">
-        <v>45.73</v>
+        <v>45.83</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.64</v>
+        <v>10.83</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.82</v>
+        <v>11.92</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.27</v>
+        <v>7.25</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>55.73</v>
+        <v>54.42</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.73</v>
+        <v>11.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>18.36</v>
+        <v>17.83</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.050000000000001</v>
+        <v>8</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BN7" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="BP7" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>77.27</v>
+        <v>73.91</v>
       </c>
       <c r="BT7" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BU7" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV7" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BW7" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY7" t="n">
         <v>2.18</v>
@@ -3625,37 +3625,37 @@
         <v>2.27</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.81</v>
+        <v>3.86</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.04</v>
+        <v>4.09</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.78</v>
+        <v>3.07</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.01</v>
+        <v>3.31</v>
       </c>
       <c r="CE7" t="n">
         <v>1.26</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CI7" t="n">
         <v>2.41</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL7" t="n">
         <v>1.96</v>
@@ -3670,22 +3670,22 @@
         <v>1.15</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CR7" t="n">
         <v>1.35</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CT7" t="n">
         <v>3.34</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CV7" t="n">
         <v>2.58</v>
@@ -3700,94 +3700,94 @@
         <v>1.91</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA7" t="n">
         <v>1.89</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DH7" t="n">
-        <v>109.32</v>
+        <v>108.39</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.91</v>
+        <v>4.78</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.82</v>
+        <v>52.56</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.18</v>
+        <v>10.3</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.54</v>
+        <v>10.65</v>
       </c>
       <c r="DR7" t="n">
         <v>6.82</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>57.96</v>
+        <v>57.17</v>
       </c>
       <c r="DW7" t="n">
         <v>0.13</v>
       </c>
       <c r="DX7" t="n">
-        <v>13</v>
+        <v>12.82</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.45</v>
+        <v>7.39</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.55</v>
+        <v>5.43</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.18</v>
+        <v>16.95</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>104.18</v>
+        <v>105.08</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="K8" t="n">
-        <v>5.27</v>
+        <v>5.58</v>
       </c>
       <c r="L8" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="M8" t="n">
-        <v>50.09</v>
+        <v>51.42</v>
       </c>
       <c r="N8" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O8" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="P8" t="n">
-        <v>11.73</v>
+        <v>11.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.18</v>
+        <v>11.08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.64</v>
+        <v>5.5</v>
       </c>
       <c r="S8" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="T8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>49</v>
+        <v>49.92</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.55</v>
+        <v>12.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.73</v>
+        <v>6.42</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.82</v>
+        <v>5.83</v>
       </c>
       <c r="AC8" t="n">
-        <v>18.64</v>
+        <v>18.58</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AF8" t="n">
         <v>0.36</v>
@@ -3968,70 +3968,70 @@
         <v>1.82</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="BH8" t="n">
-        <v>10</v>
+        <v>10.13</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BK8" t="n">
         <v>0.91</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.32</v>
+        <v>4.52</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS8" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BT8" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BU8" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BV8" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BW8" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BX8" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.71</v>
+        <v>2.77</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="CC8" t="n">
         <v>3.97</v>
@@ -4067,7 +4067,7 @@
         <v>2.6</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CO8" t="n">
         <v>1.17</v>
@@ -4082,7 +4082,7 @@
         <v>1.34</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CT8" t="n">
         <v>3.31</v>
@@ -4091,10 +4091,10 @@
         <v>1.59</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CX8" t="n">
         <v>1.52</v>
@@ -4115,49 +4115,49 @@
         <v>1.64</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.5</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.91</v>
+        <v>5.09</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="DM8" t="n">
-        <v>47.96</v>
+        <v>48.74</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.69</v>
+        <v>11.61</v>
       </c>
       <c r="DQ8" t="n">
         <v>10.09</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.32</v>
+        <v>6.22</v>
       </c>
       <c r="DS8" t="n">
         <v>0.22</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.59</v>
+        <v>49.09</v>
       </c>
       <c r="DW8" t="n">
         <v>0.04</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.82</v>
+        <v>11.7</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.95</v>
+        <v>6.78</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.87</v>
+        <v>4.91</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.55</v>
+        <v>18.52</v>
       </c>
       <c r="EB8" t="n">
         <v>1.44</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="9">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F11" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="G11" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="H11" t="n">
-        <v>85</v>
+        <v>85.08</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="L11" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M11" t="n">
-        <v>46.91</v>
+        <v>46.42</v>
       </c>
       <c r="N11" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="O11" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="P11" t="n">
-        <v>9.91</v>
+        <v>10.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.640000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="R11" t="n">
-        <v>8.359999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="U11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>44.09</v>
+        <v>44.33</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.18</v>
+        <v>13.08</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.82</v>
+        <v>8.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.36</v>
+        <v>4.17</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.27</v>
+        <v>18.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AF11" t="n">
         <v>0.09</v>
@@ -5177,70 +5177,70 @@
         <v>1.82</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.09</v>
+        <v>10.13</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.95</v>
+        <v>5.17</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.14</v>
+        <v>4.96</v>
       </c>
       <c r="BR11" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS11" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU11" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV11" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX11" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="CC11" t="n">
         <v>4</v>
@@ -5249,19 +5249,19 @@
         <v>4.14</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF11" t="n">
         <v>2.39</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CH11" t="n">
         <v>1.52</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.59</v>
@@ -5273,10 +5273,10 @@
         <v>1.85</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CO11" t="n">
         <v>1.19</v>
@@ -5285,19 +5285,19 @@
         <v>1.64</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CR11" t="n">
         <v>1.34</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CT11" t="n">
         <v>3.34</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CV11" t="n">
         <v>2.44</v>
@@ -5315,91 +5315,91 @@
         <v>2.42</v>
       </c>
       <c r="DA11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="DH11" t="n">
-        <v>88.54000000000001</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="DI11" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.14</v>
+        <v>4.17</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.91</v>
+        <v>44.74</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.87</v>
+        <v>11</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.6</v>
+        <v>9.65</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.460000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.72</v>
+        <v>44.82</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.81</v>
+        <v>12.78</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.59</v>
+        <v>8.65</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.22</v>
+        <v>4.13</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.64</v>
+        <v>19.35</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="12">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>0.36</v>
@@ -5905,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AH13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AI13" t="n">
-        <v>105.36</v>
+        <v>104.17</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.64</v>
+        <v>5.08</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="AN13" t="n">
-        <v>48.55</v>
+        <v>51</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12</v>
+        <v>11.92</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.73</v>
+        <v>12.42</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.91</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>48.36</v>
+        <v>48.83</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>12.73</v>
+        <v>13.92</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.09</v>
+        <v>9.25</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.64</v>
+        <v>4.67</v>
       </c>
       <c r="BD13" t="n">
-        <v>17.45</v>
+        <v>16.83</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.68</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.77</v>
+        <v>3.87</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.86</v>
+        <v>4.09</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS13" t="n">
-        <v>77.27</v>
+        <v>73.91</v>
       </c>
       <c r="BT13" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BU13" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV13" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BW13" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX13" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BY13" t="n">
         <v>2.66</v>
@@ -6043,16 +6043,16 @@
         <v>2.84</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CE13" t="n">
         <v>1.29</v>
@@ -6061,25 +6061,25 @@
         <v>2.37</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.59</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CN13" t="n">
         <v>2.06</v>
@@ -6088,10 +6088,10 @@
         <v>1.18</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
@@ -6130,82 +6130,82 @@
         <v>1.69</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF13" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DH13" t="n">
-        <v>95.09</v>
+        <v>94.92</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.55</v>
+        <v>4.78</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="DM13" t="n">
-        <v>44</v>
+        <v>45.48</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.32</v>
+        <v>11.31</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.41</v>
+        <v>12.26</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.78</v>
+        <v>7.83</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.59</v>
+        <v>47.87</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.19</v>
+        <v>12.83</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.68</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.5</v>
+        <v>4.52</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.59</v>
+        <v>18.22</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="H10" t="n">
-        <v>94</v>
+        <v>97.58</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J10" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="K10" t="n">
-        <v>5.36</v>
+        <v>5.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="M10" t="n">
-        <v>45.18</v>
+        <v>48.08</v>
       </c>
       <c r="N10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="O10" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="P10" t="n">
-        <v>7.27</v>
+        <v>7.17</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.45</v>
+        <v>11.08</v>
       </c>
       <c r="R10" t="n">
-        <v>9.73</v>
+        <v>9.67</v>
       </c>
       <c r="S10" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="T10" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="U10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>51.64</v>
+        <v>52.83</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>11.64</v>
+        <v>12.42</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.55</v>
+        <v>8</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.09</v>
+        <v>4.42</v>
       </c>
       <c r="AC10" t="n">
-        <v>16.18</v>
+        <v>16.92</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF10" t="n">
         <v>0.27</v>
@@ -4774,70 +4774,70 @@
         <v>0.91</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.949999999999999</v>
+        <v>10</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.14</v>
+        <v>5.22</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="BR10" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS10" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BU10" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV10" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW10" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX10" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="CC10" t="n">
         <v>4.05</v>
@@ -4861,16 +4861,16 @@
         <v>2.33</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CK10" t="n">
         <v>1.51</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CN10" t="n">
         <v>1.89</v>
@@ -4879,7 +4879,7 @@
         <v>1.17</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ10" t="n">
         <v>2.5</v>
@@ -4918,85 +4918,85 @@
         <v>1.19</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="DH10" t="n">
-        <v>89.68000000000001</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.45</v>
+        <v>4.57</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM10" t="n">
-        <v>40.22</v>
+        <v>41.95</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="DP10" t="n">
-        <v>7.22</v>
+        <v>7.17</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.54</v>
+        <v>11.35</v>
       </c>
       <c r="DR10" t="n">
         <v>9</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.14</v>
+        <v>50.83</v>
       </c>
       <c r="DW10" t="n">
         <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.28</v>
+        <v>11.7</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.05</v>
+        <v>7.31</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.22</v>
+        <v>4.39</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.36</v>
+        <v>15.79</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="11">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>0.09</v>
@@ -5499,52 +5499,52 @@
         <v>1.64</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>93.91</v>
+        <v>92.42</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>44.18</v>
+        <v>43.75</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12.64</v>
+        <v>12.25</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.91</v>
+        <v>8.67</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.82</v>
+        <v>8.33</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>41.55</v>
+        <v>40.92</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.64</v>
+        <v>10.75</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.27</v>
+        <v>7.25</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>19.64</v>
+        <v>18.42</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="BF12" t="n">
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.359999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.59</v>
+        <v>4.7</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BU12" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV12" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW12" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX12" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BY12" t="n">
         <v>3.43</v>
@@ -5640,16 +5640,16 @@
         <v>3.52</v>
       </c>
       <c r="CA12" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="CC12" t="n">
-        <v>5.1</v>
+        <v>4.91</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.77</v>
+        <v>5.53</v>
       </c>
       <c r="CE12" t="n">
         <v>1.3</v>
@@ -5661,13 +5661,13 @@
         <v>3.25</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CK12" t="n">
         <v>1.41</v>
@@ -5685,10 +5685,10 @@
         <v>1.2</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
@@ -5727,19 +5727,19 @@
         <v>1.71</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="DH12" t="n">
-        <v>93.28</v>
+        <v>92.53</v>
       </c>
       <c r="DI12" t="n">
         <v>0.09</v>
@@ -5748,28 +5748,28 @@
         <v>1.91</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.27</v>
+        <v>4.26</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="DM12" t="n">
-        <v>55.46</v>
+        <v>54.74</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.23</v>
+        <v>13</v>
       </c>
       <c r="DQ12" t="n">
-        <v>8.960000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.68</v>
+        <v>7.96</v>
       </c>
       <c r="DS12" t="n">
         <v>0.09</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.68</v>
+        <v>43.26</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.46</v>
+        <v>11.48</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.55</v>
+        <v>7.52</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.36</v>
+        <v>20.65</v>
       </c>
       <c r="EB12" t="n">
         <v>1.4</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="13">

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>0.08</v>
@@ -3887,139 +3887,139 @@
         <v>1.58</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="AI8" t="n">
-        <v>82.81999999999999</v>
+        <v>86.75</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN8" t="n">
-        <v>45.82</v>
+        <v>47.67</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.64</v>
+        <v>11.25</v>
       </c>
       <c r="AR8" t="n">
-        <v>9</v>
+        <v>9.33</v>
       </c>
       <c r="AS8" t="n">
-        <v>7</v>
+        <v>6.83</v>
       </c>
       <c r="AT8" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>48.18</v>
+        <v>49.33</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.09</v>
+        <v>11.08</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.18</v>
+        <v>7.25</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.45</v>
+        <v>19.25</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.13</v>
+        <v>10.08</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.78</v>
+        <v>4.75</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.52</v>
+        <v>4.54</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS8" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BT8" t="n">
-        <v>78.26000000000001</v>
+        <v>75</v>
       </c>
       <c r="BU8" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BV8" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BW8" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BX8" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BY8" t="n">
         <v>2.77</v>
@@ -4028,25 +4028,25 @@
         <v>2.83</v>
       </c>
       <c r="CA8" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="CC8" t="n">
         <v>3.82</v>
       </c>
-      <c r="CB8" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="CC8" t="n">
-        <v>3.97</v>
-      </c>
       <c r="CD8" t="n">
-        <v>4.06</v>
+        <v>3.91</v>
       </c>
       <c r="CE8" t="n">
         <v>1.28</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CH8" t="n">
         <v>1.55</v>
@@ -4058,13 +4058,13 @@
         <v>1.57</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CN8" t="n">
         <v>2</v>
@@ -4073,124 +4073,124 @@
         <v>1.17</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CR8" t="n">
         <v>1.34</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX8" t="n">
         <v>1.52</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.45</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DB8" t="n">
         <v>1.2</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="DE8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>95.92</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="DS8" t="n">
         <v>0.21</v>
       </c>
-      <c r="DF8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="DH8" t="n">
-        <v>94.43000000000001</v>
-      </c>
-      <c r="DI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="DK8" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="DL8" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>48.74</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>11.61</v>
-      </c>
-      <c r="DQ8" t="n">
-        <v>10.09</v>
-      </c>
-      <c r="DR8" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="DS8" t="n">
-        <v>0.22</v>
-      </c>
       <c r="DT8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.09</v>
+        <v>49.62</v>
       </c>
       <c r="DW8" t="n">
         <v>0.04</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.7</v>
+        <v>11.66</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.78</v>
+        <v>6.84</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.52</v>
+        <v>18.92</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="9">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F12" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="H12" t="n">
-        <v>92.64</v>
+        <v>94</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="K12" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="L12" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M12" t="n">
-        <v>66.73</v>
+        <v>64.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O12" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="P12" t="n">
-        <v>13.82</v>
+        <v>13.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>9</v>
+        <v>8.83</v>
       </c>
       <c r="R12" t="n">
-        <v>7.55</v>
+        <v>7.33</v>
       </c>
       <c r="S12" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="T12" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="U12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>45.82</v>
+        <v>45.17</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.27</v>
+        <v>11.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.82</v>
+        <v>7.58</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.45</v>
+        <v>4.17</v>
       </c>
       <c r="AC12" t="n">
-        <v>23.09</v>
+        <v>22.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AF12" t="n">
         <v>0.17</v>
@@ -5580,70 +5580,70 @@
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.43</v>
+        <v>9.42</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BL12" t="n">
         <v>0.83</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.7</v>
+        <v>4.67</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BT12" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BU12" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV12" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW12" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX12" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.12</v>
+        <v>4.1</v>
       </c>
       <c r="CC12" t="n">
         <v>4.91</v>
@@ -5655,16 +5655,16 @@
         <v>1.3</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.66</v>
@@ -5673,10 +5673,10 @@
         <v>1.41</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CN12" t="n">
         <v>2.05</v>
@@ -5685,13 +5685,13 @@
         <v>1.2</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ12" t="n">
         <v>2.67</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CS12" t="n">
         <v>2.56</v>
@@ -5718,7 +5718,7 @@
         <v>2.48</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DB12" t="n">
         <v>1.22</v>
@@ -5727,82 +5727,82 @@
         <v>1.71</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="DH12" t="n">
-        <v>92.53</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.26</v>
+        <v>4.16</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="DM12" t="n">
-        <v>54.74</v>
+        <v>54.12</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="DO12" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DP12" t="n">
-        <v>13</v>
+        <v>13.04</v>
       </c>
       <c r="DQ12" t="n">
-        <v>8.83</v>
+        <v>8.75</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.96</v>
+        <v>7.83</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.26</v>
+        <v>43.04</v>
       </c>
       <c r="DW12" t="n">
         <v>0.08</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.48</v>
+        <v>11.25</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.52</v>
+        <v>7.42</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.95</v>
+        <v>3.83</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.65</v>
+        <v>20.54</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="13">

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="F2" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="H2" t="n">
-        <v>114.73</v>
+        <v>112.83</v>
       </c>
       <c r="I2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="J2" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="K2" t="n">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
       <c r="L2" t="n">
-        <v>0.55</v>
+        <v>0.83</v>
       </c>
       <c r="M2" t="n">
-        <v>85.81999999999999</v>
+        <v>81.83</v>
       </c>
       <c r="N2" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="O2" t="n">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="P2" t="n">
-        <v>10.73</v>
+        <v>11</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.82</v>
+        <v>12.33</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="U2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>59.73</v>
+        <v>59.75</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.82</v>
+        <v>18.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>12.18</v>
+        <v>11.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.64</v>
+        <v>6.58</v>
       </c>
       <c r="AC2" t="n">
-        <v>16.55</v>
+        <v>16.58</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AF2" t="n">
         <v>0.17</v>
@@ -1550,70 +1550,70 @@
         <v>1.75</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.09</v>
+        <v>2.96</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.52</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.09</v>
+        <v>2.96</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.52</v>
+        <v>4.71</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.65000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="BS2" t="n">
-        <v>82.61</v>
+        <v>79.17</v>
       </c>
       <c r="BT2" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BU2" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV2" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>73.91</v>
+        <v>70.83</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CA2" t="n">
         <v>3.85</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="CC2" t="n">
         <v>2.5</v>
@@ -1622,7 +1622,7 @@
         <v>2.49</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF2" t="n">
         <v>2.46</v>
@@ -1637,7 +1637,7 @@
         <v>2.2</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CK2" t="n">
         <v>1.48</v>
@@ -1646,7 +1646,7 @@
         <v>1.9</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CN2" t="n">
         <v>1.91</v>
@@ -1661,19 +1661,19 @@
         <v>2.7</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CS2" t="n">
         <v>2.55</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CW2" t="n">
         <v>1.65</v>
@@ -1682,13 +1682,13 @@
         <v>1.54</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB2" t="n">
         <v>1.22</v>
@@ -1700,79 +1700,79 @@
         <v>2.74</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="DH2" t="n">
-        <v>100</v>
+        <v>99.66</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.78</v>
+        <v>5.83</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.7</v>
+        <v>0.83</v>
       </c>
       <c r="DM2" t="n">
-        <v>66.31</v>
+        <v>65.12</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO2" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.74</v>
+        <v>10.88</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.26</v>
+        <v>12.5</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.48</v>
+        <v>54.71</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.04</v>
+        <v>16</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.35</v>
+        <v>10.3</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.7</v>
+        <v>5.71</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.96</v>
+        <v>17.92</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
         <v>0.17</v>
@@ -1872,52 +1872,52 @@
         <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AI3" t="n">
-        <v>94.64</v>
+        <v>94.25</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.18</v>
+        <v>4.25</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN3" t="n">
-        <v>51.64</v>
+        <v>52</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.64</v>
+        <v>11.25</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.45</v>
+        <v>12.58</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.36</v>
+        <v>6.42</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>52.64</v>
+        <v>51.58</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA3" t="n">
-        <v>14.09</v>
+        <v>13.83</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.449999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.64</v>
+        <v>4.42</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.27</v>
+        <v>19.67</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.48</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.26</v>
+        <v>4.46</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.17</v>
+        <v>4.12</v>
       </c>
       <c r="BR3" t="n">
-        <v>86.95999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS3" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV3" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX3" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BY3" t="n">
         <v>2.05</v>
@@ -2016,19 +2016,19 @@
         <v>3.81</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.61</v>
+        <v>2.79</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="CE3" t="n">
         <v>1.3</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CG3" t="n">
         <v>3.28</v>
@@ -2037,31 +2037,31 @@
         <v>1.52</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CN3" t="n">
         <v>1.93</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP3" t="n">
         <v>1.67</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CR3" t="n">
         <v>1.35</v>
@@ -2070,19 +2070,19 @@
         <v>2.51</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY3" t="n">
         <v>1.9</v>
@@ -2091,7 +2091,7 @@
         <v>2.38</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB3" t="n">
         <v>1.21</v>
@@ -2100,82 +2100,82 @@
         <v>1.69</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="DG3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>97.88</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ3" t="n">
         <v>2.08</v>
       </c>
-      <c r="DH3" t="n">
-        <v>98.22</v>
-      </c>
-      <c r="DI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ3" t="n">
-        <v>1.96</v>
-      </c>
       <c r="DK3" t="n">
-        <v>3.83</v>
+        <v>3.88</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DM3" t="n">
-        <v>56.35</v>
+        <v>56.34</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.13</v>
+        <v>11.42</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.61</v>
+        <v>12.66</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.74</v>
+        <v>6.75</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>51.96</v>
+        <v>51.46</v>
       </c>
       <c r="DW3" t="n">
         <v>0.17</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.04</v>
+        <v>13.92</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.35</v>
+        <v>9.33</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.7</v>
+        <v>4.58</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.35</v>
+        <v>19.55</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0.17</v>
@@ -2275,79 +2275,79 @@
         <v>1.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.09</v>
+        <v>0.92</v>
       </c>
       <c r="AI4" t="n">
-        <v>74.45</v>
+        <v>73.67</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AL4" t="n">
         <v>3</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>43.73</v>
+        <v>46.25</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.550000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.359999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.36</v>
+        <v>10.33</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>39.55</v>
+        <v>39</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.27</v>
+        <v>10.08</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.45</v>
+        <v>6.33</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="BD4" t="n">
-        <v>15.45</v>
+        <v>15.33</v>
       </c>
       <c r="BE4" t="n">
         <v>1.23</v>
@@ -2356,58 +2356,58 @@
         <v>1</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="BH4" t="n">
-        <v>11.22</v>
+        <v>11.46</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.96</v>
+        <v>4.71</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6</v>
+        <v>5.71</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BT4" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BU4" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BV4" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX4" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY4" t="n">
         <v>4.07</v>
@@ -2416,28 +2416,28 @@
         <v>4.44</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.28</v>
+        <v>4.32</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
       <c r="CC4" t="n">
-        <v>5.75</v>
+        <v>5.88</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.35</v>
+        <v>6.47</v>
       </c>
       <c r="CE4" t="n">
         <v>1.26</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CI4" t="n">
         <v>2.2</v>
@@ -2446,7 +2446,7 @@
         <v>1.63</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL4" t="n">
         <v>1.8</v>
@@ -2461,16 +2461,16 @@
         <v>1.16</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CR4" t="n">
         <v>1.33</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CT4" t="n">
         <v>3.35</v>
@@ -2494,58 +2494,58 @@
         <v>2.53</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DB4" t="n">
         <v>1.17</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="DH4" t="n">
-        <v>82.26000000000001</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.7</v>
+        <v>45.92</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.92</v>
+        <v>10</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.65</v>
+        <v>9.75</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.779999999999999</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="DS4" t="n">
         <v>0.04</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>43.13</v>
+        <v>42.71</v>
       </c>
       <c r="DW4" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DX4" t="n">
-        <v>11</v>
+        <v>10.88</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.13</v>
+        <v>7.04</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.87</v>
+        <v>3.83</v>
       </c>
       <c r="EA4" t="n">
-        <v>16.65</v>
+        <v>16.54</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F5" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="n">
-        <v>126.55</v>
+        <v>128.58</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="K5" t="n">
-        <v>5.27</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>0.64</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>62.09</v>
+        <v>72.83</v>
       </c>
       <c r="N5" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="P5" t="n">
-        <v>12.27</v>
+        <v>12.17</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.91</v>
+        <v>10.08</v>
       </c>
       <c r="R5" t="n">
-        <v>6.09</v>
+        <v>6.33</v>
       </c>
       <c r="S5" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="U5" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="V5" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>55.55</v>
+        <v>56.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.45</v>
+        <v>18.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.55</v>
+        <v>13.33</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.91</v>
+        <v>5.42</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.64</v>
+        <v>21</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>1.75</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.390000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.13</v>
+        <v>3.92</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.17</v>
+        <v>4.92</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS5" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV5" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX5" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.15</v>
+        <v>4.19</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.41</v>
+        <v>4.47</v>
       </c>
       <c r="CC5" t="n">
         <v>1.9</v>
@@ -2834,13 +2834,13 @@
         <v>1.29</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CI5" t="n">
         <v>2.11</v>
@@ -2849,40 +2849,40 @@
         <v>1.7</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO5" t="n">
         <v>1.19</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CR5" t="n">
         <v>1.35</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CT5" t="n">
         <v>3.27</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CW5" t="n">
         <v>1.73</v>
@@ -2891,97 +2891,97 @@
         <v>1.55</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.38</v>
       </c>
       <c r="DA5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>123.88</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>54.88</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="EB5" t="n">
         <v>1.88</v>
       </c>
-      <c r="DB5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="DD5" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>122.7</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="DK5" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>57.96</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="DP5" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="DQ5" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="DR5" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="DS5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="DT5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="DU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV5" t="n">
-        <v>54.35</v>
-      </c>
-      <c r="DW5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DX5" t="n">
-        <v>16</v>
-      </c>
-      <c r="DY5" t="n">
-        <v>11.05</v>
-      </c>
-      <c r="DZ5" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="EA5" t="n">
-        <v>20.57</v>
-      </c>
-      <c r="EB5" t="n">
-        <v>1.78</v>
-      </c>
       <c r="EC5" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>0.25</v>
@@ -3081,100 +3081,100 @@
         <v>1.83</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AI6" t="n">
-        <v>100.18</v>
+        <v>100.75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.27</v>
+        <v>4.42</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN6" t="n">
-        <v>42.18</v>
+        <v>43</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.36</v>
+        <v>12.08</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.91</v>
+        <v>11.08</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.27</v>
+        <v>7.92</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>52.09</v>
+        <v>52</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.36</v>
+        <v>13.67</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.82</v>
+        <v>8.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.55</v>
+        <v>5.42</v>
       </c>
       <c r="BD6" t="n">
-        <v>20.82</v>
+        <v>21.08</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.65</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL6" t="n">
         <v>1</v>
@@ -3186,34 +3186,34 @@
         <v>2.04</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.3</v>
+        <v>5.33</v>
       </c>
       <c r="BR6" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS6" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT6" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BV6" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BW6" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BX6" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BY6" t="n">
         <v>1.6</v>
@@ -3222,10 +3222,10 @@
         <v>1.64</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="CC6" t="n">
         <v>2.03</v>
@@ -3240,7 +3240,7 @@
         <v>2.19</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CH6" t="n">
         <v>1.63</v>
@@ -3258,19 +3258,19 @@
         <v>1.82</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CN6" t="n">
         <v>2.02</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="CP6" t="n">
         <v>1.52</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
@@ -3300,7 +3300,7 @@
         <v>2.48</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DB6" t="n">
         <v>1.16</v>
@@ -3309,49 +3309,49 @@
         <v>1.52</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="DH6" t="n">
-        <v>103.78</v>
+        <v>103.92</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.26</v>
+        <v>5.29</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM6" t="n">
-        <v>48.57</v>
+        <v>48.71</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.65</v>
+        <v>12</v>
       </c>
       <c r="DQ6" t="n">
         <v>12.96</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.13</v>
+        <v>7</v>
       </c>
       <c r="DS6" t="n">
         <v>0.08</v>
@@ -3363,25 +3363,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54.78</v>
+        <v>54.62</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.3</v>
+        <v>14.42</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.09</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>6.22</v>
+        <v>6.12</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.17</v>
+        <v>20.33</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="EC6" t="n">
         <v>2.04</v>
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="G7" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="H7" t="n">
-        <v>110.64</v>
+        <v>110.25</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>5.82</v>
+        <v>5.83</v>
       </c>
       <c r="L7" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="M7" t="n">
-        <v>59.91</v>
+        <v>59</v>
       </c>
       <c r="N7" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O7" t="n">
-        <v>3.27</v>
+        <v>3.42</v>
       </c>
       <c r="P7" t="n">
-        <v>9.73</v>
+        <v>9.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.27</v>
+        <v>9.17</v>
       </c>
       <c r="R7" t="n">
-        <v>6.36</v>
+        <v>6.42</v>
       </c>
       <c r="S7" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="T7" t="n">
         <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>60.18</v>
+        <v>59.92</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.27</v>
+        <v>14.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.82</v>
+        <v>8.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.45</v>
+        <v>6.42</v>
       </c>
       <c r="AC7" t="n">
         <v>16</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF7" t="n">
         <v>0.08</v>
@@ -3565,64 +3565,64 @@
         <v>1.75</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.35</v>
+        <v>3.29</v>
       </c>
       <c r="BH7" t="n">
         <v>8</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.35</v>
+        <v>3.29</v>
       </c>
       <c r="BJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BL7" t="n">
         <v>1.04</v>
       </c>
-      <c r="BK7" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1</v>
-      </c>
       <c r="BM7" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BN7" t="n">
         <v>1.96</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="BP7" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>3.96</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>4.04</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT7" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BW7" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BX7" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CA7" t="n">
         <v>3.86</v>
@@ -3643,13 +3643,13 @@
         <v>2.27</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CH7" t="n">
         <v>1.58</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.53</v>
@@ -3658,7 +3658,7 @@
         <v>1.52</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CM7" t="n">
         <v>2.36</v>
@@ -3715,46 +3715,46 @@
         <v>2.4</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>108.39</v>
+        <v>108.29</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.78</v>
+        <v>4.83</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.56</v>
+        <v>52.42</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.3</v>
+        <v>10.33</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.65</v>
+        <v>10.54</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.82</v>
+        <v>6.84</v>
       </c>
       <c r="DS7" t="n">
         <v>0.08</v>
@@ -3769,25 +3769,25 @@
         <v>57.17</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.82</v>
+        <v>13</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.39</v>
+        <v>7.54</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.43</v>
+        <v>5.46</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.95</v>
+        <v>16.92</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="8">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
@@ -4212,82 +4212,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="H9" t="n">
-        <v>97</v>
+        <v>100.67</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="K9" t="n">
-        <v>5.45</v>
+        <v>5.33</v>
       </c>
       <c r="L9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="M9" t="n">
-        <v>45.18</v>
+        <v>47.83</v>
       </c>
       <c r="N9" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="O9" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="P9" t="n">
-        <v>10.09</v>
+        <v>10.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.82</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>6.82</v>
+        <v>7</v>
       </c>
       <c r="S9" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="U9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>48.09</v>
+        <v>49</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.55</v>
+        <v>12.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.73</v>
+        <v>7.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.82</v>
+        <v>4.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>16.09</v>
+        <v>16.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AF9" t="n">
         <v>0.17</v>
@@ -4371,70 +4371,70 @@
         <v>2.33</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.960000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BN9" t="n">
         <v>0.83</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.7</v>
+        <v>4.54</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.22</v>
+        <v>5.25</v>
       </c>
       <c r="BR9" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BS9" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX9" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CC9" t="n">
         <v>3.17</v>
@@ -4443,19 +4443,19 @@
         <v>3.36</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CG9" t="n">
         <v>3.15</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.61</v>
@@ -4464,10 +4464,10 @@
         <v>1.46</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CN9" t="n">
         <v>1.97</v>
@@ -4479,22 +4479,22 @@
         <v>1.7</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CT9" t="n">
         <v>3.31</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CW9" t="n">
         <v>1.62</v>
@@ -4515,85 +4515,85 @@
         <v>1.22</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="DG9" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="DH9" t="n">
-        <v>94.91</v>
+        <v>96.84</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.39</v>
+        <v>5.33</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DM9" t="n">
-        <v>46.43</v>
+        <v>47.71</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.7</v>
+        <v>11.71</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.26</v>
+        <v>10.34</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.22</v>
+        <v>7.29</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.26</v>
+        <v>48.71</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.22</v>
+        <v>12.25</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.91</v>
+        <v>8</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.61</v>
+        <v>17.88</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,139 +4693,139 @@
         <v>1.25</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AI10" t="n">
-        <v>85.36</v>
+        <v>86.08</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN10" t="n">
-        <v>35.27</v>
+        <v>35.17</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.18</v>
+        <v>7.58</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.64</v>
+        <v>11.67</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.27</v>
+        <v>8.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>48.64</v>
+        <v>48</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.91</v>
+        <v>11</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.55</v>
+        <v>6.67</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="BD10" t="n">
-        <v>14.55</v>
+        <v>14.25</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="BH10" t="n">
-        <v>10</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.22</v>
+        <v>5.04</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.78</v>
+        <v>4.83</v>
       </c>
       <c r="BR10" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS10" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW10" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX10" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY10" t="n">
         <v>2.97</v>
@@ -4834,16 +4834,16 @@
         <v>3.13</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.05</v>
+        <v>4.02</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.37</v>
+        <v>4.39</v>
       </c>
       <c r="CE10" t="n">
         <v>1.28</v>
@@ -4852,7 +4852,7 @@
         <v>2.33</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="CH10" t="n">
         <v>1.55</v>
@@ -4867,13 +4867,13 @@
         <v>1.51</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CO10" t="n">
         <v>1.17</v>
@@ -4888,7 +4888,7 @@
         <v>1.34</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CT10" t="n">
         <v>3.36</v>
@@ -4897,7 +4897,7 @@
         <v>1.61</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CW10" t="n">
         <v>1.57</v>
@@ -4921,49 +4921,49 @@
         <v>1.63</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DH10" t="n">
-        <v>91.73999999999999</v>
+        <v>91.83</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="DM10" t="n">
-        <v>41.95</v>
+        <v>41.62</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="DP10" t="n">
-        <v>7.17</v>
+        <v>7.38</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.35</v>
+        <v>11.38</v>
       </c>
       <c r="DR10" t="n">
-        <v>9</v>
+        <v>9.08</v>
       </c>
       <c r="DS10" t="n">
         <v>0.08</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.83</v>
+        <v>50.42</v>
       </c>
       <c r="DW10" t="n">
         <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.7</v>
+        <v>11.71</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.31</v>
+        <v>7.34</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.79</v>
+        <v>15.58</v>
       </c>
       <c r="EB10" t="n">
         <v>1.35</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>0.25</v>
@@ -5096,139 +5096,139 @@
         <v>1.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AI11" t="n">
-        <v>92.09</v>
+        <v>91.83</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.27</v>
+        <v>4.08</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>42.91</v>
+        <v>43.42</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11.82</v>
+        <v>11.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.550000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.550000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>45.36</v>
+        <v>45.17</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.45</v>
+        <v>12.58</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.359999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.09</v>
+        <v>4.17</v>
       </c>
       <c r="BD11" t="n">
-        <v>20</v>
+        <v>19.25</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.13</v>
+        <v>10.04</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.17</v>
+        <v>5.21</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.96</v>
+        <v>4.83</v>
       </c>
       <c r="BR11" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS11" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT11" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV11" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX11" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BY11" t="n">
         <v>3.14</v>
@@ -5243,13 +5243,13 @@
         <v>3.92</v>
       </c>
       <c r="CC11" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.14</v>
+        <v>4.07</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF11" t="n">
         <v>2.39</v>
@@ -5261,7 +5261,7 @@
         <v>1.52</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.59</v>
@@ -5270,10 +5270,10 @@
         <v>1.45</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN11" t="n">
         <v>1.96</v>
@@ -5291,115 +5291,115 @@
         <v>1.34</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CT11" t="n">
         <v>3.34</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB11" t="n">
         <v>1.21</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DH11" t="n">
-        <v>88.43000000000001</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="DI11" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.74</v>
+        <v>44.92</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="DP11" t="n">
-        <v>11</v>
+        <v>10.88</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.65</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.57</v>
+        <v>8.58</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.82</v>
+        <v>44.75</v>
       </c>
       <c r="DW11" t="n">
         <v>0.08</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.78</v>
+        <v>12.83</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.65</v>
+        <v>8.67</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.35</v>
+        <v>19</v>
       </c>
       <c r="EB11" t="n">
         <v>1.42</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="12">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="H13" t="n">
-        <v>84.81999999999999</v>
+        <v>85.25</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J13" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K13" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="M13" t="n">
-        <v>39.45</v>
+        <v>39.33</v>
       </c>
       <c r="N13" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="P13" t="n">
-        <v>10.64</v>
+        <v>10.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.09</v>
+        <v>12.75</v>
       </c>
       <c r="R13" t="n">
-        <v>7.64</v>
+        <v>7.83</v>
       </c>
       <c r="S13" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="T13" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>46.82</v>
+        <v>47</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>11.64</v>
+        <v>11.42</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.27</v>
+        <v>7.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.36</v>
+        <v>4.17</v>
       </c>
       <c r="AC13" t="n">
-        <v>19.73</v>
+        <v>20.08</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,64 +5983,64 @@
         <v>1.67</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.960000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM13" t="n">
         <v>0.96</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.87</v>
+        <v>3.92</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.09</v>
+        <v>4.17</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS13" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT13" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV13" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BW13" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX13" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="CA13" t="n">
         <v>3.67</v>
@@ -6079,7 +6079,7 @@
         <v>1.75</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CN13" t="n">
         <v>2.06</v>
@@ -6121,7 +6121,7 @@
         <v>2.51</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DB13" t="n">
         <v>1.21</v>
@@ -6130,10 +6130,10 @@
         <v>1.69</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF13" t="n">
         <v>1.04</v>
@@ -6142,70 +6142,70 @@
         <v>2</v>
       </c>
       <c r="DH13" t="n">
-        <v>94.92</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="DM13" t="n">
-        <v>45.48</v>
+        <v>45.16</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.31</v>
+        <v>11.38</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.26</v>
+        <v>12.58</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.83</v>
+        <v>7.92</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.87</v>
+        <v>47.92</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.83</v>
+        <v>12.67</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.300000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.52</v>
+        <v>4.42</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.22</v>
+        <v>18.45</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -1803,7 +1803,7 @@
         <v>101.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J3" t="n">
         <v>1.42</v>
@@ -2115,7 +2115,7 @@
         <v>97.88</v>
       </c>
       <c r="DI3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DJ3" t="n">
         <v>2.08</v>
@@ -3487,7 +3487,7 @@
         <v>0.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AH7" t="n">
         <v>1.58</v>
@@ -3499,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AL7" t="n">
         <v>3.83</v>
@@ -3562,7 +3562,7 @@
         <v>1.38</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="BG7" t="n">
         <v>3.29</v>
@@ -3718,7 +3718,7 @@
         <v>0.16</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="DG7" t="n">
         <v>2</v>
@@ -3730,7 +3730,7 @@
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DK7" t="n">
         <v>4.83</v>
@@ -3787,7 +3787,7 @@
         <v>1.59</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="8">
@@ -4696,7 +4696,7 @@
         <v>0.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="AH10" t="n">
         <v>1.92</v>
@@ -4705,10 +4705,10 @@
         <v>86.08</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AL10" t="n">
         <v>3.5</v>
@@ -4771,7 +4771,7 @@
         <v>1.26</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="BG10" t="n">
         <v>3.08</v>
@@ -4927,7 +4927,7 @@
         <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DG10" t="n">
         <v>2.38</v>
@@ -4936,10 +4936,10 @@
         <v>91.83</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="DK10" t="n">
         <v>4.5</v>
@@ -4996,7 +4996,7 @@
         <v>1.35</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="11">

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="G6" t="n">
-        <v>3.83</v>
+        <v>3.92</v>
       </c>
       <c r="H6" t="n">
-        <v>107.08</v>
+        <v>106.62</v>
       </c>
       <c r="I6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="J6" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="K6" t="n">
-        <v>6.17</v>
+        <v>6.38</v>
       </c>
       <c r="L6" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="M6" t="n">
-        <v>54.42</v>
+        <v>54.46</v>
       </c>
       <c r="N6" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="O6" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="P6" t="n">
-        <v>11.92</v>
+        <v>12.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.83</v>
+        <v>14.85</v>
       </c>
       <c r="R6" t="n">
-        <v>6.08</v>
+        <v>6</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T6" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="U6" t="n">
         <v>0.08</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>57.25</v>
+        <v>57.08</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.17</v>
+        <v>15.38</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.33</v>
+        <v>8.77</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.83</v>
+        <v>6.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.58</v>
+        <v>19.31</v>
       </c>
       <c r="AD6" t="n">
         <v>1.83</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
         <v>0.17</v>
@@ -3162,70 +3162,70 @@
         <v>2.25</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.710000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BN6" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.38</v>
+        <v>4.4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.33</v>
+        <v>5.48</v>
       </c>
       <c r="BR6" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS6" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT6" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BU6" t="n">
-        <v>45.83</v>
+        <v>48</v>
       </c>
       <c r="BV6" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BW6" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BX6" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.47</v>
+        <v>4.49</v>
       </c>
       <c r="CC6" t="n">
         <v>2.03</v>
@@ -3246,7 +3246,7 @@
         <v>1.63</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.55</v>
@@ -3255,7 +3255,7 @@
         <v>1.42</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM6" t="n">
         <v>2.6</v>
@@ -3264,7 +3264,7 @@
         <v>2.02</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="CP6" t="n">
         <v>1.52</v>
@@ -3309,49 +3309,49 @@
         <v>1.52</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="DH6" t="n">
-        <v>103.92</v>
+        <v>103.8</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.29</v>
+        <v>5.44</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="DM6" t="n">
-        <v>48.71</v>
+        <v>48.96</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="DP6" t="n">
-        <v>12</v>
+        <v>12.12</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.96</v>
+        <v>13.04</v>
       </c>
       <c r="DR6" t="n">
-        <v>7</v>
+        <v>6.92</v>
       </c>
       <c r="DS6" t="n">
         <v>0.08</v>
@@ -3363,22 +3363,22 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54.62</v>
+        <v>54.64</v>
       </c>
       <c r="DW6" t="n">
         <v>0.16</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.42</v>
+        <v>14.56</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.289999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="DZ6" t="n">
-        <v>6.12</v>
+        <v>6.04</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.33</v>
+        <v>20.16</v>
       </c>
       <c r="EB6" t="n">
         <v>1.7</v>
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
         <v>0.25</v>
@@ -5099,49 +5099,49 @@
         <v>0.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>91.83</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="AJ11" t="n">
         <v>0.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.08</v>
+        <v>4.15</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AN11" t="n">
-        <v>43.42</v>
+        <v>43.15</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11.5</v>
+        <v>11.77</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.67</v>
+        <v>10</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.58</v>
+        <v>9</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AV11" t="n">
         <v>0.08</v>
@@ -5153,82 +5153,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>45.17</v>
+        <v>45.15</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.08</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.58</v>
+        <v>12.23</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.42</v>
+        <v>8.08</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="BD11" t="n">
-        <v>19.25</v>
+        <v>18.92</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.04</v>
+        <v>10.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL11" t="n">
         <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="BO11" t="n">
         <v>1.12</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="BR11" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS11" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BV11" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX11" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BY11" t="n">
         <v>3.14</v>
@@ -5237,28 +5237,28 @@
         <v>3.26</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.77</v>
+        <v>3.81</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.92</v>
+        <v>4.08</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.07</v>
+        <v>4.22</v>
       </c>
       <c r="CE11" t="n">
         <v>1.28</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CI11" t="n">
         <v>2.3</v>
@@ -5270,7 +5270,7 @@
         <v>1.45</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CM11" t="n">
         <v>2.51</v>
@@ -5279,19 +5279,19 @@
         <v>1.96</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CR11" t="n">
         <v>1.34</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CT11" t="n">
         <v>3.34</v>
@@ -5318,55 +5318,55 @@
         <v>1.98</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="DE11" t="n">
         <v>0.16</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="DH11" t="n">
-        <v>88.45999999999999</v>
+        <v>88.08</v>
       </c>
       <c r="DI11" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.08</v>
+        <v>4.12</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.92</v>
+        <v>44.72</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.88</v>
+        <v>11.04</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.710000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.58</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DS11" t="n">
         <v>0.16</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.75</v>
+        <v>44.76</v>
       </c>
       <c r="DW11" t="n">
         <v>0.08</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.83</v>
+        <v>12.64</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.67</v>
+        <v>8.48</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="EA11" t="n">
-        <v>19</v>
+        <v>18.84</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="12">

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
         <v>0.33</v>
@@ -1469,139 +1469,139 @@
         <v>1.42</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AI2" t="n">
-        <v>86.5</v>
+        <v>87.23</v>
       </c>
       <c r="AJ2" t="n">
         <v>-0.08</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.83</v>
+        <v>4.62</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AN2" t="n">
-        <v>48.42</v>
+        <v>46.46</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10.75</v>
+        <v>10.85</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.67</v>
+        <v>12.46</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.5</v>
+        <v>7.54</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AU2" t="n">
         <v>2.08</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>49.67</v>
+        <v>49</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.5</v>
+        <v>13.46</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.67</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="BD2" t="n">
-        <v>19.25</v>
+        <v>19.46</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="BG2" t="n">
         <v>2.96</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.619999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="BI2" t="n">
         <v>2.96</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.71</v>
+        <v>4.6</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.83</v>
+        <v>4.8</v>
       </c>
       <c r="BR2" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS2" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT2" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BU2" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BV2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX2" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BY2" t="n">
         <v>1.86</v>
@@ -1610,31 +1610,31 @@
         <v>1.86</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="CC2" t="n">
         <v>2.5</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CE2" t="n">
         <v>1.3</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CH2" t="n">
         <v>1.51</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.65</v>
@@ -1643,7 +1643,7 @@
         <v>1.48</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM2" t="n">
         <v>2.46</v>
@@ -1694,85 +1694,85 @@
         <v>1.22</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="DH2" t="n">
-        <v>99.66</v>
+        <v>99.52</v>
       </c>
       <c r="DI2" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.83</v>
+        <v>5.68</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="DM2" t="n">
-        <v>65.12</v>
+        <v>63.44</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DO2" t="n">
-        <v>3.17</v>
+        <v>3.04</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.88</v>
+        <v>10.92</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.5</v>
+        <v>6.56</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.71</v>
+        <v>54.16</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>16</v>
+        <v>15.88</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.71</v>
+        <v>5.68</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.92</v>
+        <v>18.08</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
         <v>0.17</v>
@@ -1875,46 +1875,46 @@
         <v>0.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AH3" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AI3" t="n">
-        <v>94.25</v>
+        <v>94</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>52</v>
+        <v>52.38</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.25</v>
+        <v>11.31</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.58</v>
+        <v>12.46</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.42</v>
+        <v>6.62</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="AU3" t="n">
         <v>1</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>51.58</v>
+        <v>51.23</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA3" t="n">
-        <v>13.83</v>
+        <v>13.31</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.42</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.42</v>
+        <v>4.31</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.67</v>
+        <v>19.08</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.619999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BO3" t="n">
         <v>1.08</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.46</v>
+        <v>4.52</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.12</v>
+        <v>4.16</v>
       </c>
       <c r="BR3" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BS3" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BT3" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="BU3" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BV3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX3" t="n">
-        <v>33.33</v>
+        <v>36</v>
       </c>
       <c r="BY3" t="n">
         <v>2.05</v>
@@ -2013,22 +2013,22 @@
         <v>2.11</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="CB3" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="CE3" t="n">
         <v>1.3</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CG3" t="n">
         <v>3.28</v>
@@ -2037,22 +2037,22 @@
         <v>1.52</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CK3" t="n">
         <v>1.48</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CM3" t="n">
         <v>2.48</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO3" t="n">
         <v>1.19</v>
@@ -2061,7 +2061,7 @@
         <v>1.67</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CR3" t="n">
         <v>1.35</v>
@@ -2085,13 +2085,13 @@
         <v>1.56</v>
       </c>
       <c r="CY3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DA3" t="n">
         <v>1.9</v>
-      </c>
-      <c r="CZ3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="DA3" t="n">
-        <v>1.91</v>
       </c>
       <c r="DB3" t="n">
         <v>1.21</v>
@@ -2100,19 +2100,19 @@
         <v>1.69</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="DE3" t="n">
         <v>0.12</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="DH3" t="n">
-        <v>97.88</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="DI3" t="n">
         <v>0.04</v>
@@ -2121,28 +2121,28 @@
         <v>2.08</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.88</v>
+        <v>3.96</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="DM3" t="n">
-        <v>56.34</v>
+        <v>56.36</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.42</v>
+        <v>11.44</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.66</v>
+        <v>12.6</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.75</v>
+        <v>6.84</v>
       </c>
       <c r="DS3" t="n">
         <v>0.08</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>51.46</v>
+        <v>51.28</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.92</v>
+        <v>13.64</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.33</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.58</v>
+        <v>4.52</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.55</v>
+        <v>19.24</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
         <v>0.17</v>
@@ -2278,49 +2278,49 @@
         <v>0.08</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.92</v>
+        <v>1.31</v>
       </c>
       <c r="AI4" t="n">
-        <v>73.67</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AL4" t="n">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>46.25</v>
+        <v>44.38</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.67</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.33</v>
+        <v>10.77</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AV4" t="n">
         <v>0.08</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>39</v>
+        <v>38.62</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.08</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.08</v>
+        <v>10.15</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.33</v>
+        <v>6.62</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="BD4" t="n">
-        <v>15.33</v>
+        <v>16</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BF4" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="BH4" t="n">
-        <v>11.46</v>
+        <v>11.56</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BK4" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BL4" t="n">
         <v>0.88</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.71</v>
+        <v>4.6</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.71</v>
+        <v>5.96</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>95.83</v>
+        <v>92</v>
       </c>
       <c r="BT4" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="BU4" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BV4" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX4" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BY4" t="n">
         <v>4.07</v>
@@ -2422,40 +2422,40 @@
         <v>4.62</v>
       </c>
       <c r="CC4" t="n">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.47</v>
+        <v>6.35</v>
       </c>
       <c r="CE4" t="n">
         <v>1.26</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="CH4" t="n">
         <v>1.59</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL4" t="n">
         <v>1.8</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CO4" t="n">
         <v>1.16</v>
@@ -2464,7 +2464,7 @@
         <v>1.55</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CR4" t="n">
         <v>1.33</v>
@@ -2488,13 +2488,13 @@
         <v>1.48</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.53</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DB4" t="n">
         <v>1.17</v>
@@ -2503,49 +2503,49 @@
         <v>1.55</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DE4" t="n">
         <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="DH4" t="n">
-        <v>81.54000000000001</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM4" t="n">
-        <v>45.92</v>
+        <v>44.96</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="DP4" t="n">
-        <v>10</v>
+        <v>10.12</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.75</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.789999999999999</v>
+        <v>10.04</v>
       </c>
       <c r="DS4" t="n">
         <v>0.04</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>42.71</v>
+        <v>42.36</v>
       </c>
       <c r="DW4" t="n">
         <v>0.04</v>
@@ -2566,19 +2566,19 @@
         <v>10.88</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.04</v>
+        <v>7.16</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.83</v>
+        <v>3.72</v>
       </c>
       <c r="EA4" t="n">
-        <v>16.54</v>
+        <v>16.84</v>
       </c>
       <c r="EB4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="EC4" t="n">
         <v>1.28</v>
-      </c>
-      <c r="EC4" t="n">
-        <v>1.25</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="F5" t="n">
         <v>1.08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H5" t="n">
-        <v>128.58</v>
+        <v>128.54</v>
       </c>
       <c r="I5" t="n">
         <v>0.08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="K5" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M5" t="n">
+        <v>70.84999999999999</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P5" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>56.46</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="AB5" t="n">
         <v>6</v>
       </c>
-      <c r="L5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>72.83</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="P5" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>5.42</v>
-      </c>
       <c r="AC5" t="n">
-        <v>21</v>
+        <v>20.85</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>1.75</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.710000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.58</v>
+        <v>0.72</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.92</v>
+        <v>4.16</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.92</v>
+        <v>4.88</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS5" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BT5" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BU5" t="n">
-        <v>33.33</v>
+        <v>36</v>
       </c>
       <c r="BV5" t="n">
-        <v>20.83</v>
+        <v>24</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.33</v>
+        <v>12</v>
       </c>
       <c r="BX5" t="n">
-        <v>70.83</v>
+        <v>68</v>
       </c>
       <c r="BY5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BZ5" t="n">
         <v>1.54</v>
       </c>
-      <c r="BZ5" t="n">
-        <v>1.55</v>
-      </c>
       <c r="CA5" t="n">
-        <v>4.19</v>
+        <v>4.24</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.47</v>
+        <v>4.49</v>
       </c>
       <c r="CC5" t="n">
         <v>1.9</v>
@@ -2831,43 +2831,43 @@
         <v>1.95</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CI5" t="n">
         <v>2.11</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CK5" t="n">
         <v>1.52</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="CR5" t="n">
         <v>1.35</v>
@@ -2894,7 +2894,7 @@
         <v>1.91</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA5" t="n">
         <v>1.9</v>
@@ -2903,85 +2903,85 @@
         <v>1.21</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DF5" t="n">
         <v>1.12</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="DH5" t="n">
-        <v>123.88</v>
+        <v>124.04</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.46</v>
+        <v>5.68</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="DM5" t="n">
-        <v>63.5</v>
+        <v>62.84</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.38</v>
+        <v>12.2</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.2</v>
+        <v>9.92</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.38</v>
+        <v>6.32</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.88</v>
+        <v>54.92</v>
       </c>
       <c r="DW5" t="n">
         <v>0.08</v>
       </c>
       <c r="DX5" t="n">
-        <v>16.71</v>
+        <v>17.16</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.5</v>
+        <v>11.64</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.21</v>
+        <v>5.52</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.75</v>
+        <v>20.68</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="6">
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="G7" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H7" t="n">
-        <v>110.25</v>
+        <v>108.85</v>
       </c>
       <c r="I7" t="n">
         <v>0.08</v>
@@ -3421,31 +3421,31 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>5.83</v>
+        <v>5.77</v>
       </c>
       <c r="L7" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="M7" t="n">
-        <v>59</v>
+        <v>58.92</v>
       </c>
       <c r="N7" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="O7" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="P7" t="n">
-        <v>9.83</v>
+        <v>9.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.17</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>6.42</v>
+        <v>6.38</v>
       </c>
       <c r="S7" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T7" t="n">
         <v>2</v>
@@ -3460,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>59.92</v>
+        <v>59.38</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.5</v>
+        <v>14.38</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.08</v>
+        <v>7.92</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.42</v>
+        <v>6.46</v>
       </c>
       <c r="AC7" t="n">
-        <v>16</v>
+        <v>16.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AF7" t="n">
         <v>0.08</v>
@@ -3565,70 +3565,70 @@
         <v>1.83</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="BH7" t="n">
-        <v>8</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BN7" t="n">
         <v>1.96</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.04</v>
+        <v>4.12</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BT7" t="n">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="BU7" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BV7" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BW7" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BX7" t="n">
-        <v>45.83</v>
+        <v>48</v>
       </c>
       <c r="BY7" t="n">
         <v>2.17</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="CC7" t="n">
         <v>3.07</v>
@@ -3643,7 +3643,7 @@
         <v>2.27</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CH7" t="n">
         <v>1.58</v>
@@ -3658,7 +3658,7 @@
         <v>1.52</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CM7" t="n">
         <v>2.36</v>
@@ -3697,13 +3697,13 @@
         <v>1.56</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.37</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB7" t="n">
         <v>1.17</v>
@@ -3718,13 +3718,13 @@
         <v>0.16</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="DG7" t="n">
         <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>108.29</v>
+        <v>107.64</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
@@ -3733,28 +3733,28 @@
         <v>2</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.83</v>
+        <v>4.84</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.42</v>
+        <v>52.64</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.33</v>
+        <v>10.36</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.54</v>
+        <v>10.6</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="DS7" t="n">
         <v>0.08</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>57.17</v>
+        <v>57</v>
       </c>
       <c r="DW7" t="n">
         <v>0.12</v>
@@ -3775,19 +3775,19 @@
         <v>13</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.54</v>
+        <v>7.48</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.46</v>
+        <v>5.52</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.92</v>
+        <v>16.96</v>
       </c>
       <c r="EB7" t="n">
         <v>1.59</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
         <v>12</v>
@@ -3809,82 +3809,82 @@
         <v>0.08</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="H8" t="n">
-        <v>105.08</v>
+        <v>107.77</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="K8" t="n">
-        <v>5.58</v>
+        <v>5.77</v>
       </c>
       <c r="L8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="M8" t="n">
-        <v>51.42</v>
+        <v>52.54</v>
       </c>
       <c r="N8" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="O8" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="P8" t="n">
-        <v>11.58</v>
+        <v>11.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.08</v>
+        <v>11.23</v>
       </c>
       <c r="R8" t="n">
-        <v>5.5</v>
+        <v>5.69</v>
       </c>
       <c r="S8" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="T8" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="U8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>49.92</v>
+        <v>51.15</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.25</v>
+        <v>12.54</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.42</v>
+        <v>7</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.83</v>
+        <v>5.54</v>
       </c>
       <c r="AC8" t="n">
-        <v>18.58</v>
+        <v>18.46</v>
       </c>
       <c r="AD8" t="n">
         <v>1.56</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AF8" t="n">
         <v>0.33</v>
@@ -3968,70 +3968,70 @@
         <v>1.75</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.62</v>
+        <v>3.52</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.08</v>
+        <v>10.24</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.62</v>
+        <v>3.52</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BL8" t="n">
         <v>0.92</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.75</v>
+        <v>4.64</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.54</v>
+        <v>4.84</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS8" t="n">
-        <v>91.67</v>
+        <v>88</v>
       </c>
       <c r="BT8" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="BU8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BV8" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BW8" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BX8" t="n">
-        <v>83.33</v>
+        <v>80</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="CC8" t="n">
         <v>3.82</v>
@@ -4040,22 +4040,22 @@
         <v>3.91</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CK8" t="n">
         <v>1.42</v>
@@ -4064,19 +4064,19 @@
         <v>1.81</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CN8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CO8" t="n">
         <v>1.17</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CR8" t="n">
         <v>1.34</v>
@@ -4100,97 +4100,97 @@
         <v>1.52</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.45</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="DB8" t="n">
         <v>1.2</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="DE8" t="n">
         <v>0.2</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="DH8" t="n">
-        <v>95.92</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.16</v>
+        <v>5.28</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM8" t="n">
-        <v>49.54</v>
+        <v>50.2</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.42</v>
+        <v>11.24</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.2</v>
+        <v>10.32</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.16</v>
+        <v>6.24</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.62</v>
+        <v>50.28</v>
       </c>
       <c r="DW8" t="n">
         <v>0.04</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.66</v>
+        <v>11.84</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.84</v>
+        <v>7.12</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.83</v>
+        <v>4.72</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.92</v>
+        <v>18.84</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,52 +4290,52 @@
         <v>1.42</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AH9" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AI9" t="n">
-        <v>93</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.33</v>
+        <v>5.15</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AN9" t="n">
-        <v>47.58</v>
+        <v>46.31</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.17</v>
+        <v>13.08</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.67</v>
+        <v>10.85</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.58</v>
+        <v>7.92</v>
       </c>
       <c r="AT9" t="n">
         <v>1.08</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AV9" t="n">
         <v>0.08</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>48.42</v>
+        <v>47.85</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.92</v>
+        <v>12</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.08</v>
+        <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="BD9" t="n">
-        <v>19</v>
+        <v>18.85</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.83</v>
+        <v>9.68</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.54</v>
+        <v>4.48</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.25</v>
+        <v>5.16</v>
       </c>
       <c r="BR9" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BS9" t="n">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BU9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BV9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX9" t="n">
-        <v>41.67</v>
+        <v>44</v>
       </c>
       <c r="BY9" t="n">
         <v>2.54</v>
@@ -4431,31 +4431,31 @@
         <v>2.75</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="CE9" t="n">
         <v>1.32</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.61</v>
@@ -4464,7 +4464,7 @@
         <v>1.46</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CM9" t="n">
         <v>2.52</v>
@@ -4479,19 +4479,19 @@
         <v>1.7</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV9" t="n">
         <v>2.39</v>
@@ -4503,64 +4503,64 @@
         <v>1.51</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.45</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DB9" t="n">
         <v>1.22</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DF9" t="n">
         <v>1.12</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="DH9" t="n">
-        <v>96.84</v>
+        <v>96.08</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.33</v>
+        <v>5.24</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="DM9" t="n">
-        <v>47.71</v>
+        <v>47.04</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.71</v>
+        <v>11.72</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.34</v>
+        <v>10.44</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.29</v>
+        <v>7.48</v>
       </c>
       <c r="DS9" t="n">
         <v>0.12</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.71</v>
+        <v>48.4</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.25</v>
+        <v>12.28</v>
       </c>
       <c r="DY9" t="n">
-        <v>8</v>
+        <v>7.96</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.25</v>
+        <v>4.32</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.88</v>
+        <v>17.84</v>
       </c>
       <c r="EB9" t="n">
         <v>1.42</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,16 +4693,16 @@
         <v>1.25</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AH10" t="n">
         <v>1.92</v>
       </c>
       <c r="AI10" t="n">
-        <v>86.08</v>
+        <v>84.69</v>
       </c>
       <c r="AJ10" t="n">
         <v>0.08</v>
@@ -4711,34 +4711,34 @@
         <v>1.08</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AN10" t="n">
-        <v>35.17</v>
+        <v>33.77</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.58</v>
+        <v>7.23</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.67</v>
+        <v>11.38</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.5</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AV10" t="n">
         <v>0.08</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>48</v>
+        <v>47.69</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.08</v>
       </c>
       <c r="BA10" t="n">
-        <v>11</v>
+        <v>10.46</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.67</v>
+        <v>6.38</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.33</v>
+        <v>4.08</v>
       </c>
       <c r="BD10" t="n">
-        <v>14.25</v>
+        <v>14.77</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BF10" t="n">
         <v>0.92</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.880000000000001</v>
+        <v>10.04</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.92</v>
+        <v>1.04</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.04</v>
+        <v>5.24</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.83</v>
+        <v>4.8</v>
       </c>
       <c r="BR10" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS10" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BT10" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BU10" t="n">
-        <v>33.33</v>
+        <v>36</v>
       </c>
       <c r="BV10" t="n">
-        <v>20.83</v>
+        <v>24</v>
       </c>
       <c r="BW10" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BX10" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BY10" t="n">
         <v>2.97</v>
@@ -4834,28 +4834,28 @@
         <v>3.13</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.81</v>
+        <v>3.87</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.01</v>
+        <v>4.06</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.02</v>
+        <v>4.26</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.39</v>
+        <v>4.53</v>
       </c>
       <c r="CE10" t="n">
         <v>1.28</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CI10" t="n">
         <v>2.33</v>
@@ -4867,10 +4867,10 @@
         <v>1.51</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CN10" t="n">
         <v>1.9</v>
@@ -4879,10 +4879,10 @@
         <v>1.17</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CR10" t="n">
         <v>1.34</v>
@@ -4909,7 +4909,7 @@
         <v>1.88</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DA10" t="n">
         <v>1.93</v>
@@ -4918,22 +4918,22 @@
         <v>1.19</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="DE10" t="n">
         <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DH10" t="n">
-        <v>91.83</v>
+        <v>90.88</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
@@ -4942,28 +4942,28 @@
         <v>1.16</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DM10" t="n">
-        <v>41.62</v>
+        <v>40.64</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="DP10" t="n">
-        <v>7.38</v>
+        <v>7.2</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.38</v>
+        <v>11.24</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.08</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DS10" t="n">
         <v>0.08</v>
@@ -4975,25 +4975,25 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.42</v>
+        <v>50.16</v>
       </c>
       <c r="DW10" t="n">
         <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.71</v>
+        <v>11.4</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.34</v>
+        <v>7.16</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.38</v>
+        <v>4.24</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.58</v>
+        <v>15.8</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="EC10" t="n">
         <v>1.08</v>
@@ -5159,10 +5159,10 @@
         <v>0.08</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.23</v>
+        <v>12.15</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.08</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
         <v>4.15</v>
@@ -5171,7 +5171,7 @@
         <v>18.92</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="BF11" t="n">
         <v>1.85</v>
@@ -5384,10 +5384,10 @@
         <v>0.08</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.64</v>
+        <v>12.6</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.48</v>
+        <v>8.44</v>
       </c>
       <c r="DZ11" t="n">
         <v>4.16</v>
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
         <v>12</v>
@@ -5421,82 +5421,82 @@
         <v>0.08</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="G12" t="n">
         <v>2.08</v>
       </c>
       <c r="H12" t="n">
-        <v>94</v>
+        <v>98.77</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="K12" t="n">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="L12" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="M12" t="n">
-        <v>64.5</v>
+        <v>65.08</v>
       </c>
       <c r="N12" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="O12" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="P12" t="n">
-        <v>13.83</v>
+        <v>13.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.83</v>
+        <v>9</v>
       </c>
       <c r="R12" t="n">
-        <v>7.33</v>
+        <v>7.08</v>
       </c>
       <c r="S12" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="T12" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="U12" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="V12" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>45.17</v>
+        <v>46.23</v>
       </c>
       <c r="Y12" t="n">
         <v>0.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>11.75</v>
+        <v>11.38</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.58</v>
+        <v>7.31</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="AC12" t="n">
-        <v>22.67</v>
+        <v>23.15</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
         <v>0.17</v>
@@ -5580,70 +5580,70 @@
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.42</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.75</v>
+        <v>4.68</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BT12" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BU12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV12" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX12" t="n">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.1</v>
+        <v>4.06</v>
       </c>
       <c r="CC12" t="n">
         <v>4.91</v>
@@ -5652,13 +5652,13 @@
         <v>5.53</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CH12" t="n">
         <v>1.5</v>
@@ -5673,10 +5673,10 @@
         <v>1.41</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CN12" t="n">
         <v>2.05</v>
@@ -5688,19 +5688,19 @@
         <v>1.69</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV12" t="n">
         <v>2.28</v>
@@ -5718,91 +5718,91 @@
         <v>2.48</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DB12" t="n">
         <v>1.22</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="DE12" t="n">
         <v>0.12</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="DG12" t="n">
         <v>2.2</v>
       </c>
       <c r="DH12" t="n">
-        <v>93.20999999999999</v>
+        <v>95.72</v>
       </c>
       <c r="DI12" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.16</v>
+        <v>4.12</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM12" t="n">
-        <v>54.12</v>
+        <v>54.84</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="DP12" t="n">
         <v>13.04</v>
       </c>
       <c r="DQ12" t="n">
-        <v>8.75</v>
+        <v>8.84</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.83</v>
+        <v>7.68</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.04</v>
+        <v>43.68</v>
       </c>
       <c r="DW12" t="n">
         <v>0.08</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.25</v>
+        <v>11.08</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.42</v>
+        <v>7.28</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.54</v>
+        <v>20.88</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="G13" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H13" t="n">
-        <v>85.25</v>
+        <v>88.92</v>
       </c>
       <c r="I13" t="n">
         <v>-0.08</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="L13" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="M13" t="n">
-        <v>39.33</v>
+        <v>42</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="O13" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="P13" t="n">
-        <v>10.83</v>
+        <v>10.77</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.75</v>
+        <v>12.69</v>
       </c>
       <c r="R13" t="n">
-        <v>7.83</v>
+        <v>7.92</v>
       </c>
       <c r="S13" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="U13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>47</v>
+        <v>47.92</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>11.42</v>
+        <v>11.38</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.25</v>
+        <v>7.23</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>20.08</v>
+        <v>20.31</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5986,7 +5986,7 @@
         <v>3.12</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.039999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="BI13" t="n">
         <v>3.12</v>
@@ -5995,58 +5995,58 @@
         <v>1</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.92</v>
+        <v>3.84</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS13" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BT13" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BU13" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BV13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX13" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CC13" t="n">
         <v>3.52</v>
@@ -6058,10 +6058,10 @@
         <v>1.29</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CH13" t="n">
         <v>1.52</v>
@@ -6073,16 +6073,16 @@
         <v>1.59</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO13" t="n">
         <v>1.18</v>
@@ -6106,7 +6106,7 @@
         <v>1.56</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CW13" t="n">
         <v>1.61</v>
@@ -6127,52 +6127,52 @@
         <v>1.21</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="DG13" t="n">
         <v>2</v>
       </c>
       <c r="DH13" t="n">
-        <v>94.70999999999999</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.79</v>
+        <v>4.76</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="DM13" t="n">
-        <v>45.16</v>
+        <v>46.32</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DO13" t="n">
         <v>2.12</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.38</v>
+        <v>11.32</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.58</v>
+        <v>12.56</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.92</v>
+        <v>7.96</v>
       </c>
       <c r="DS13" t="n">
         <v>0.12</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.92</v>
+        <v>48.36</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.67</v>
+        <v>12.6</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.45</v>
+        <v>18.64</v>
       </c>
       <c r="EB13" t="n">
         <v>1.44</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -1935,19 +1935,19 @@
         <v>0.15</v>
       </c>
       <c r="BA3" t="n">
-        <v>13.31</v>
+        <v>13.38</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>9.08</v>
       </c>
       <c r="BC3" t="n">
         <v>4.31</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.08</v>
+        <v>19.15</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BF3" t="n">
         <v>2.38</v>
@@ -2160,16 +2160,16 @@
         <v>0.16</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.64</v>
+        <v>13.68</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.119999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="DZ3" t="n">
         <v>4.52</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.24</v>
+        <v>19.28</v>
       </c>
       <c r="EB3" t="n">
         <v>1.59</v>

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
         <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="F2" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>2.92</v>
       </c>
       <c r="H2" t="n">
-        <v>112.83</v>
+        <v>115.85</v>
       </c>
       <c r="I2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="J2" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="K2" t="n">
-        <v>6.83</v>
+        <v>6.69</v>
       </c>
       <c r="L2" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="M2" t="n">
-        <v>81.83</v>
+        <v>80.38</v>
       </c>
       <c r="N2" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="O2" t="n">
-        <v>3.92</v>
+        <v>3.77</v>
       </c>
       <c r="P2" t="n">
-        <v>11</v>
+        <v>10.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.33</v>
+        <v>12.62</v>
       </c>
       <c r="R2" t="n">
-        <v>5.5</v>
+        <v>5.23</v>
       </c>
       <c r="S2" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="T2" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="U2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>59.75</v>
+        <v>59.85</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.92</v>
+        <v>12.31</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.58</v>
+        <v>6.69</v>
       </c>
       <c r="AC2" t="n">
-        <v>16.58</v>
+        <v>17.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AF2" t="n">
         <v>0.15</v>
@@ -1550,58 +1550,58 @@
         <v>1.69</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.48</v>
+        <v>9.35</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.8</v>
+        <v>4.77</v>
       </c>
       <c r="BR2" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS2" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BT2" t="n">
-        <v>56</v>
+        <v>53.85</v>
       </c>
       <c r="BU2" t="n">
-        <v>28</v>
+        <v>26.92</v>
       </c>
       <c r="BV2" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BW2" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BX2" t="n">
-        <v>72</v>
+        <v>73.08</v>
       </c>
       <c r="BY2" t="n">
         <v>1.86</v>
@@ -1610,10 +1610,10 @@
         <v>1.86</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="CC2" t="n">
         <v>2.5</v>
@@ -1625,7 +1625,7 @@
         <v>1.3</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CG2" t="n">
         <v>3.27</v>
@@ -1634,22 +1634,22 @@
         <v>1.51</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO2" t="n">
         <v>1.2</v>
@@ -1664,13 +1664,13 @@
         <v>1.34</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CT2" t="n">
         <v>3.31</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV2" t="n">
         <v>2.34</v>
@@ -1688,7 +1688,7 @@
         <v>2.4</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DB2" t="n">
         <v>1.22</v>
@@ -1697,82 +1697,82 @@
         <v>1.72</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DH2" t="n">
-        <v>99.52</v>
+        <v>101.54</v>
       </c>
       <c r="DI2" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.68</v>
+        <v>5.66</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="DM2" t="n">
-        <v>63.44</v>
+        <v>63.42</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO2" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.92</v>
+        <v>10.88</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.4</v>
+        <v>12.54</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.56</v>
+        <v>6.38</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.16</v>
+        <v>54.42</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.88</v>
+        <v>16.23</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.2</v>
+        <v>10.46</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.68</v>
+        <v>5.77</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.08</v>
+        <v>18.27</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="n">
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
         <v>0.23</v>
@@ -3484,52 +3484,52 @@
         <v>1.69</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AI7" t="n">
-        <v>106.33</v>
+        <v>103.69</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>44.08</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="AT7" t="n">
         <v>2</v>
       </c>
-      <c r="AL7" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>45.83</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>11.92</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AU7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AV7" t="n">
         <v>0.08</v>
@@ -3541,58 +3541,58 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>54.42</v>
+        <v>53.23</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.08</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.5</v>
+        <v>11.23</v>
       </c>
       <c r="BB7" t="n">
-        <v>7</v>
+        <v>6.92</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.5</v>
+        <v>4.31</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.83</v>
+        <v>17.85</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.119999999999999</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="BL7" t="n">
         <v>1.08</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.12</v>
+        <v>4.04</v>
       </c>
       <c r="BQ7" t="n">
         <v>4</v>
@@ -3601,22 +3601,22 @@
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BT7" t="n">
-        <v>68</v>
+        <v>65.38</v>
       </c>
       <c r="BU7" t="n">
-        <v>36</v>
+        <v>34.62</v>
       </c>
       <c r="BV7" t="n">
-        <v>32</v>
+        <v>30.77</v>
       </c>
       <c r="BW7" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BX7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
         <v>2.17</v>
@@ -3625,16 +3625,16 @@
         <v>2.25</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.07</v>
+        <v>3.15</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.31</v>
+        <v>3.38</v>
       </c>
       <c r="CE7" t="n">
         <v>1.26</v>
@@ -3643,37 +3643,37 @@
         <v>2.27</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CH7" t="n">
         <v>1.58</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.53</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL7" t="n">
         <v>1.98</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN7" t="n">
         <v>1.84</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CR7" t="n">
         <v>1.35</v>
@@ -3700,61 +3700,61 @@
         <v>1.92</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA7" t="n">
         <v>1.88</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="DG7" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DH7" t="n">
-        <v>107.64</v>
+        <v>106.27</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.84</v>
+        <v>4.69</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.64</v>
+        <v>51.5</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.36</v>
+        <v>10.58</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.6</v>
+        <v>10.58</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="DS7" t="n">
         <v>0.08</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>57</v>
+        <v>56.3</v>
       </c>
       <c r="DW7" t="n">
         <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.48</v>
+        <v>7.42</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.52</v>
+        <v>5.38</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.96</v>
+        <v>17</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="8">

--- a/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Denmark_Superliga_2025-2026.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -706,667 +694,667 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>total_games</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>home_games</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>away_games</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>home_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>home_avg_2h_cards</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_avg_2h_corners</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>home_avg_attacks</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>home_avg_cards_num</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>home_avg_corners</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>home_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>home_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>home_avg_fh_cards</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>home_avg_fh_corners</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>home_avg_fouls</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>home_avg_freekicks</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>home_avg_goalkicks</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>home_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>home_avg_goals_scored</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>home_avg_penalties_won</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>home_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>home_avg_possession</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>home_avg_red_cards</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>home_avg_shots</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>home_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>home_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>home_avg_throwins</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>home_avg_xg</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>home_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>away_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>away_avg_2h_cards</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>away_avg_2h_corners</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>away_avg_attacks</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>away_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>away_avg_cards_num</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>away_avg_corners</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>away_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>away_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>away_avg_fh_cards</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>away_avg_fh_corners</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>away_avg_fouls</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>away_avg_freekicks</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>away_avg_goalkicks</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>away_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>away_avg_goals_scored</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>away_avg_penalties_won</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>away_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>away_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>away_avg_possession</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>away_avg_red_cards</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>away_avg_shots</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>away_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>away_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>away_avg_throwins</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>away_avg_xg</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>away_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>totalGoalCount</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>totalCornerCount</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>overallGoalCount</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ht_goals_team_a</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ht_goals_team_b</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>goals_2hg_team_a</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>goals_2hg_team_b</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>GoalCount_2hg</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>HTGoalCount</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>corner_fh_count</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>corner_2h_count</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>over05</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>over15</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>over35</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>over45</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>over55</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>btts</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>avg_odds_ft_1</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_1_odd</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>avg_odds_ft_x</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_x_odd</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>avg_odds_ft_2</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_2_odd</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over05</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over15</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under05</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under15</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>avg_odds_btts_no</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>avg_odds_btts_yes</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_85</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_95</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_85</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_95</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over15</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over25</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over35</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over05_odd</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over15_odd</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under05_odd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under15_odd</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_no_odd</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_yes_odd</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_85_odd</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_95_odd</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_85_odd</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_95_odd</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over15_odd</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over25_odd</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>total_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>total_avg_2h_cards</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>total_avg_2h_corners</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>total_avg_attacks</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>total_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>total_avg_cards_num</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>total_avg_corners</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>total_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>total_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>total_avg_fh_cards</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>total_avg_fh_corners</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>total_avg_fouls</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>total_avg_freekicks</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>total_avg_goalkicks</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>total_avg_penalties_won</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>total_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>total_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>total_avg_possession</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>total_avg_red_cards</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>total_avg_shots</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>total_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>total_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>total_avg_throwins</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>total_avg_xg</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>total_avg_yellow_cards</t>
         </is>
@@ -1379,196 +1367,196 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
         <v>0.31</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="G2" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H2" t="n">
-        <v>115.85</v>
+        <v>113.25</v>
       </c>
       <c r="I2" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="J2" t="n">
         <v>1.31</v>
       </c>
       <c r="K2" t="n">
-        <v>6.69</v>
+        <v>6.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.77</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>80.38</v>
+        <v>77.25</v>
       </c>
       <c r="N2" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>3.77</v>
+        <v>3.31</v>
       </c>
       <c r="P2" t="n">
-        <v>10.92</v>
+        <v>10.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.62</v>
+        <v>13.19</v>
       </c>
       <c r="R2" t="n">
-        <v>5.23</v>
+        <v>5.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="T2" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="V2" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>59.85</v>
+        <v>60.12</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>19</v>
+        <v>18.44</v>
       </c>
       <c r="AA2" t="n">
-        <v>12.31</v>
+        <v>11.81</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.69</v>
+        <v>6.62</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.08</v>
+        <v>18.38</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="AE2" t="n">
         <v>1.31</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="AG2" t="n">
         <v>1.31</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AI2" t="n">
-        <v>87.23</v>
+        <v>87</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.62</v>
+        <v>4.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.46</v>
+        <v>44.81</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.46</v>
+        <v>13</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.54</v>
+        <v>7.62</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.46</v>
+        <v>12.88</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.619999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.85</v>
+        <v>4.88</v>
       </c>
       <c r="BD2" t="n">
-        <v>19.46</v>
+        <v>19.75</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.35</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="BN2" t="n">
         <v>1.62</v>
@@ -1577,100 +1565,100 @@
         <v>1.31</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.5</v>
+        <v>4.12</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.77</v>
+        <v>4.91</v>
       </c>
       <c r="BR2" t="n">
-        <v>92.31</v>
+        <v>90.62</v>
       </c>
       <c r="BS2" t="n">
-        <v>80.77</v>
+        <v>81.25</v>
       </c>
       <c r="BT2" t="n">
-        <v>53.85</v>
+        <v>53.12</v>
       </c>
       <c r="BU2" t="n">
-        <v>26.92</v>
+        <v>25</v>
       </c>
       <c r="BV2" t="n">
-        <v>23.08</v>
+        <v>21.88</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.54</v>
+        <v>12.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>73.08</v>
+        <v>71.88</v>
       </c>
       <c r="BY2" t="n">
         <v>1.86</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="CE2" t="n">
         <v>1.3</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CH2" t="n">
         <v>1.51</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CO2" t="n">
         <v>1.2</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="CR2" t="n">
         <v>1.34</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CT2" t="n">
         <v>3.31</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CV2" t="n">
         <v>2.34</v>
@@ -1679,100 +1667,100 @@
         <v>1.65</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.4</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="DF2" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="DH2" t="n">
-        <v>101.54</v>
+        <v>100.12</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.66</v>
+        <v>5.5</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="DM2" t="n">
-        <v>63.42</v>
+        <v>61.03</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DO2" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="DP2" t="n">
         <v>10.88</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.54</v>
+        <v>13.1</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.38</v>
+        <v>6.56</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.42</v>
+        <v>53.56</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.23</v>
+        <v>15.66</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.46</v>
+        <v>9.91</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.77</v>
+        <v>5.75</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.27</v>
+        <v>19.06</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="3">
@@ -1782,142 +1770,142 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="F3" t="n">
-        <v>0.92</v>
+        <v>1.12</v>
       </c>
       <c r="G3" t="n">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="H3" t="n">
-        <v>101.5</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.42</v>
+        <v>1.82</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>0.41</v>
       </c>
       <c r="M3" t="n">
-        <v>60.67</v>
+        <v>58.06</v>
       </c>
       <c r="N3" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="O3" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="P3" t="n">
-        <v>11.58</v>
+        <v>13.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.75</v>
+        <v>12.94</v>
       </c>
       <c r="R3" t="n">
-        <v>7.08</v>
+        <v>7.47</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T3" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="U3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>51.33</v>
+        <v>51.29</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>14</v>
+        <v>14.18</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.25</v>
+        <v>9.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.75</v>
+        <v>4.82</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.42</v>
+        <v>19.18</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.08</v>
+        <v>1.47</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AI3" t="n">
-        <v>94</v>
+        <v>93.75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AK3" t="n">
         <v>2.69</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.38</v>
+        <v>4.19</v>
       </c>
       <c r="AM3" t="n">
         <v>0.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>52.38</v>
+        <v>53.19</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.77</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.31</v>
+        <v>2.12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.31</v>
+        <v>11.06</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.46</v>
+        <v>12.75</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.62</v>
+        <v>6.88</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.77</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,118 +1917,118 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>51.23</v>
+        <v>51.12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="BA3" t="n">
-        <v>13.38</v>
+        <v>14.06</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.08</v>
+        <v>9.56</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.31</v>
+        <v>4.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.15</v>
+        <v>19.12</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.720000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.52</v>
+        <v>0.61</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.52</v>
+        <v>4.3</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.16</v>
+        <v>4.06</v>
       </c>
       <c r="BR3" t="n">
-        <v>84</v>
+        <v>87.88</v>
       </c>
       <c r="BS3" t="n">
-        <v>64</v>
+        <v>69.7</v>
       </c>
       <c r="BT3" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BU3" t="n">
-        <v>20</v>
+        <v>24.24</v>
       </c>
       <c r="BV3" t="n">
-        <v>12</v>
+        <v>15.15</v>
       </c>
       <c r="BW3" t="n">
-        <v>8</v>
+        <v>9.09</v>
       </c>
       <c r="BX3" t="n">
-        <v>36</v>
+        <v>39.39</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.79</v>
+        <v>3.73</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.99</v>
+        <v>3.93</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="CE3" t="n">
         <v>1.3</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="CK3" t="n">
         <v>1.48</v>
@@ -2049,28 +2037,28 @@
         <v>1.92</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="CR3" t="n">
         <v>1.35</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CU3" t="n">
         <v>1.56</v>
@@ -2082,16 +2070,16 @@
         <v>1.64</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="DB3" t="n">
         <v>1.21</v>
@@ -2100,82 +2088,82 @@
         <v>1.69</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="DH3" t="n">
-        <v>97.59999999999999</v>
+        <v>96.58</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.96</v>
+        <v>4.09</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DM3" t="n">
-        <v>56.36</v>
+        <v>55.7</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.44</v>
+        <v>12.45</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.6</v>
+        <v>12.85</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.84</v>
+        <v>7.18</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>51.28</v>
+        <v>51.21</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.68</v>
+        <v>14.12</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.16</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.52</v>
+        <v>4.66</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.28</v>
+        <v>19.15</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="4">
@@ -2185,61 +2173,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="H4" t="n">
-        <v>89.42</v>
+        <v>89.88</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="K4" t="n">
         <v>5.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="M4" t="n">
-        <v>45.58</v>
+        <v>48.5</v>
       </c>
       <c r="N4" t="n">
         <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="P4" t="n">
-        <v>10.25</v>
+        <v>10.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.83</v>
+        <v>10.94</v>
       </c>
       <c r="R4" t="n">
-        <v>9.25</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.92</v>
+        <v>1.25</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,232 +2239,232 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>46.42</v>
+        <v>47.38</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.67</v>
+        <v>13.94</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.75</v>
+        <v>9.19</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.92</v>
+        <v>4.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.75</v>
+        <v>18.38</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.77</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="AI4" t="n">
-        <v>74.54000000000001</v>
+        <v>82.06</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.23</v>
+        <v>3.81</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AN4" t="n">
-        <v>44.38</v>
+        <v>47</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10</v>
+        <v>10.31</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.539999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.77</v>
+        <v>10.31</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>38.62</v>
+        <v>40.88</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.15</v>
+        <v>10.38</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.62</v>
+        <v>6.81</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="BD4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.44</v>
+        <v>3.53</v>
       </c>
       <c r="BH4" t="n">
-        <v>11.56</v>
+        <v>11.31</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.44</v>
+        <v>3.53</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.72</v>
+        <v>0.88</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="BM4" t="n">
         <v>0.88</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.6</v>
+        <v>4.69</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.96</v>
+        <v>5.84</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>92</v>
+        <v>93.75</v>
       </c>
       <c r="BT4" t="n">
-        <v>72</v>
+        <v>71.88</v>
       </c>
       <c r="BU4" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BV4" t="n">
-        <v>32</v>
+        <v>31.25</v>
       </c>
       <c r="BW4" t="n">
-        <v>4</v>
+        <v>6.25</v>
       </c>
       <c r="BX4" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.07</v>
+        <v>3.86</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.44</v>
+        <v>4.15</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.32</v>
+        <v>4.19</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.62</v>
+        <v>4.5</v>
       </c>
       <c r="CC4" t="n">
-        <v>5.78</v>
+        <v>5.26</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.35</v>
+        <v>5.74</v>
       </c>
       <c r="CE4" t="n">
         <v>1.26</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="CR4" t="n">
         <v>1.33</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CT4" t="n">
         <v>3.35</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CV4" t="n">
         <v>2.39</v>
@@ -2488,13 +2476,13 @@
         <v>1.48</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.53</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="DB4" t="n">
         <v>1.17</v>
@@ -2503,82 +2491,82 @@
         <v>1.55</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="DH4" t="n">
-        <v>81.68000000000001</v>
+        <v>85.97</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.44</v>
+        <v>4.78</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.96</v>
+        <v>47.75</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.12</v>
+        <v>10.34</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.640000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="DR4" t="n">
-        <v>10.04</v>
+        <v>9.6</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>42.36</v>
+        <v>44.13</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.88</v>
+        <v>12.16</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.16</v>
+        <v>8</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.72</v>
+        <v>4.16</v>
       </c>
       <c r="EA4" t="n">
-        <v>16.84</v>
+        <v>17.69</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="5">
@@ -2588,61 +2576,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="F5" t="n">
-        <v>1.08</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H5" t="n">
-        <v>128.54</v>
+        <v>120.81</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="K5" t="n">
-        <v>6.38</v>
+        <v>6.56</v>
       </c>
       <c r="L5" t="n">
-        <v>0.62</v>
+        <v>0.88</v>
       </c>
       <c r="M5" t="n">
-        <v>70.84999999999999</v>
+        <v>68.19</v>
       </c>
       <c r="N5" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="O5" t="n">
-        <v>2.62</v>
+        <v>3.06</v>
       </c>
       <c r="P5" t="n">
-        <v>11.85</v>
+        <v>11.31</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.539999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="R5" t="n">
-        <v>6.23</v>
+        <v>6.19</v>
       </c>
       <c r="S5" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="T5" t="n">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
         <v>0.38</v>
@@ -2654,232 +2642,232 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>56.46</v>
+        <v>55.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.46</v>
+        <v>19.94</v>
       </c>
       <c r="AA5" t="n">
-        <v>13.46</v>
+        <v>13.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>6</v>
+        <v>6.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.85</v>
+        <v>20.81</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.17</v>
+        <v>1.59</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.92</v>
+        <v>2.47</v>
       </c>
       <c r="AI5" t="n">
-        <v>119.17</v>
+        <v>120.71</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.58</v>
+        <v>0.35</v>
       </c>
       <c r="AN5" t="n">
-        <v>54.17</v>
+        <v>56.29</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="AP5" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.58</v>
+        <v>12.71</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.33</v>
+        <v>11.06</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.42</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>53.25</v>
+        <v>54.65</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>14.67</v>
+        <v>15.35</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.67</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>5.65</v>
       </c>
       <c r="BD5" t="n">
-        <v>20.5</v>
+        <v>20.94</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.880000000000001</v>
+        <v>10.27</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.88</v>
+        <v>1.03</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.16</v>
+        <v>4.3</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.88</v>
+        <v>4.76</v>
       </c>
       <c r="BR5" t="n">
-        <v>96</v>
+        <v>96.97</v>
       </c>
       <c r="BS5" t="n">
-        <v>92</v>
+        <v>93.94</v>
       </c>
       <c r="BT5" t="n">
-        <v>64</v>
+        <v>72.73</v>
       </c>
       <c r="BU5" t="n">
-        <v>36</v>
+        <v>42.42</v>
       </c>
       <c r="BV5" t="n">
-        <v>24</v>
+        <v>27.27</v>
       </c>
       <c r="BW5" t="n">
-        <v>12</v>
+        <v>12.12</v>
       </c>
       <c r="BX5" t="n">
-        <v>68</v>
+        <v>66.67</v>
       </c>
       <c r="BY5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BZ5" t="n">
         <v>1.53</v>
       </c>
-      <c r="BZ5" t="n">
-        <v>1.54</v>
-      </c>
       <c r="CA5" t="n">
-        <v>4.24</v>
+        <v>4.29</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
       <c r="CC5" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="CD5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="CE5" t="n">
         <v>1.28</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="CL5" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="CO5" t="n">
         <v>1.18</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="CR5" t="n">
         <v>1.35</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="CT5" t="n">
         <v>3.27</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CV5" t="n">
         <v>2.2</v>
@@ -2891,97 +2879,97 @@
         <v>1.55</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="DH5" t="n">
-        <v>124.04</v>
+        <v>120.76</v>
       </c>
       <c r="DI5" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.68</v>
+        <v>5.76</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="DM5" t="n">
-        <v>62.84</v>
+        <v>62.06</v>
       </c>
       <c r="DN5" t="n">
         <v>0.52</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.2</v>
+        <v>12.03</v>
       </c>
       <c r="DQ5" t="n">
-        <v>9.92</v>
+        <v>10.03</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.32</v>
+        <v>6.61</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.92</v>
+        <v>55.06</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="DX5" t="n">
-        <v>17.16</v>
+        <v>17.58</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.64</v>
+        <v>11.7</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.52</v>
+        <v>5.88</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.68</v>
+        <v>20.88</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="6">
@@ -2991,298 +2979,298 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="F6" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="G6" t="n">
-        <v>3.92</v>
+        <v>3.62</v>
       </c>
       <c r="H6" t="n">
-        <v>106.62</v>
+        <v>104.81</v>
       </c>
       <c r="I6" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="J6" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="K6" t="n">
-        <v>6.38</v>
+        <v>6.19</v>
       </c>
       <c r="L6" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>54.46</v>
+        <v>52.56</v>
       </c>
       <c r="N6" t="n">
         <v>0.62</v>
       </c>
       <c r="O6" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="P6" t="n">
-        <v>12.15</v>
+        <v>13.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.85</v>
+        <v>14.69</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="S6" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="U6" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="V6" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>57.08</v>
+        <v>57.5</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.38</v>
+        <v>15.19</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.77</v>
+        <v>8.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.62</v>
+        <v>6.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.31</v>
+        <v>19.56</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="AI6" t="n">
-        <v>100.75</v>
+        <v>97.31</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.42</v>
+        <v>4.75</v>
       </c>
       <c r="AM6" t="n">
         <v>0.5</v>
       </c>
       <c r="AN6" t="n">
-        <v>43</v>
+        <v>42.94</v>
       </c>
       <c r="AO6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AT6" t="n">
         <v>0.75</v>
       </c>
-      <c r="AP6" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>12.08</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>11.08</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0.83</v>
-      </c>
       <c r="AU6" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>52</v>
+        <v>50.19</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.67</v>
+        <v>13.44</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.25</v>
+        <v>8.56</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.42</v>
+        <v>4.88</v>
       </c>
       <c r="BD6" t="n">
-        <v>21.08</v>
+        <v>21.25</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="BG6" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="CG6" t="n">
         <v>3.52</v>
       </c>
-      <c r="BH6" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>92</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>84</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>60</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>48</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>28</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="CG6" t="n">
-        <v>3.58</v>
-      </c>
       <c r="CH6" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.55</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.21</v>
+        <v>3.29</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CV6" t="n">
         <v>2.52</v>
@@ -3291,100 +3279,100 @@
         <v>1.57</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="DH6" t="n">
-        <v>103.8</v>
+        <v>101.06</v>
       </c>
       <c r="DI6" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.44</v>
+        <v>5.47</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DM6" t="n">
-        <v>48.96</v>
+        <v>47.75</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.12</v>
+        <v>12.81</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.04</v>
+        <v>13.25</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.92</v>
+        <v>6.88</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54.64</v>
+        <v>53.84</v>
       </c>
       <c r="DW6" t="n">
         <v>0.16</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.56</v>
+        <v>14.32</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.52</v>
+        <v>8.66</v>
       </c>
       <c r="DZ6" t="n">
-        <v>6.04</v>
+        <v>5.66</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.16</v>
+        <v>20.4</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="7">
@@ -3394,112 +3382,112 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="F7" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="G7" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="H7" t="n">
-        <v>108.85</v>
+        <v>111.94</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="K7" t="n">
-        <v>5.77</v>
+        <v>6.06</v>
       </c>
       <c r="L7" t="n">
-        <v>0.85</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>58.92</v>
+        <v>61.12</v>
       </c>
       <c r="N7" t="n">
         <v>0.62</v>
       </c>
       <c r="O7" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="P7" t="n">
-        <v>9.92</v>
+        <v>10.56</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.380000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="R7" t="n">
-        <v>6.38</v>
+        <v>6.75</v>
       </c>
       <c r="S7" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="V7" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>59.38</v>
+        <v>60.38</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.38</v>
+        <v>15.31</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.92</v>
+        <v>8.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.46</v>
+        <v>6.81</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.15</v>
+        <v>15.44</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AE7" t="n">
         <v>1.69</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AI7" t="n">
-        <v>103.69</v>
+        <v>102.56</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="AL7" t="n">
         <v>3.62</v>
@@ -3508,157 +3496,157 @@
         <v>0.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>44.08</v>
+        <v>44.44</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11.23</v>
+        <v>11.56</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.77</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.62</v>
+        <v>8</v>
       </c>
       <c r="AT7" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>53.23</v>
+        <v>54.06</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.23</v>
+        <v>11.62</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.92</v>
+        <v>7.12</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.31</v>
+        <v>4.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.85</v>
+        <v>17.44</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.23</v>
+        <v>3.03</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.039999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.23</v>
+        <v>3.03</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.92</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.04</v>
+        <v>4.12</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4</v>
+        <v>4.19</v>
       </c>
       <c r="BR7" t="n">
-        <v>100</v>
+        <v>96.88</v>
       </c>
       <c r="BS7" t="n">
-        <v>76.92</v>
+        <v>75</v>
       </c>
       <c r="BT7" t="n">
-        <v>65.38</v>
+        <v>59.38</v>
       </c>
       <c r="BU7" t="n">
-        <v>34.62</v>
+        <v>31.25</v>
       </c>
       <c r="BV7" t="n">
-        <v>30.77</v>
+        <v>28.12</v>
       </c>
       <c r="BW7" t="n">
-        <v>15.38</v>
+        <v>12.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>53.12</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.06</v>
+        <v>4.02</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="CK7" t="n">
         <v>1.53</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CM7" t="n">
         <v>2.35</v>
@@ -3667,25 +3655,25 @@
         <v>1.84</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="CR7" t="n">
         <v>1.35</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CT7" t="n">
         <v>3.34</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CV7" t="n">
         <v>2.58</v>
@@ -3694,100 +3682,100 @@
         <v>1.54</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.36</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="DE7" t="n">
         <v>0.19</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.96</v>
+        <v>2.09</v>
       </c>
       <c r="DH7" t="n">
-        <v>106.27</v>
+        <v>107.25</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.69</v>
+        <v>4.84</v>
       </c>
       <c r="DL7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>52.78</v>
+      </c>
+      <c r="DN7" t="n">
         <v>0.62</v>
       </c>
-      <c r="DM7" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>0.58</v>
-      </c>
       <c r="DO7" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.58</v>
+        <v>11.06</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.58</v>
+        <v>10.4</v>
       </c>
       <c r="DR7" t="n">
-        <v>7</v>
+        <v>7.38</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>56.3</v>
+        <v>57.22</v>
       </c>
       <c r="DW7" t="n">
         <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.8</v>
+        <v>13.46</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.42</v>
+        <v>7.81</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.38</v>
+        <v>5.65</v>
       </c>
       <c r="EA7" t="n">
-        <v>17</v>
+        <v>16.44</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="8">
@@ -3797,124 +3785,124 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="F8" t="n">
-        <v>0.92</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>107.77</v>
+        <v>110.62</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="K8" t="n">
-        <v>5.77</v>
+        <v>6.06</v>
       </c>
       <c r="L8" t="n">
-        <v>0.62</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>52.54</v>
+        <v>56.69</v>
       </c>
       <c r="N8" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="P8" t="n">
-        <v>11.23</v>
+        <v>11.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.23</v>
+        <v>10.56</v>
       </c>
       <c r="R8" t="n">
-        <v>5.69</v>
+        <v>5.94</v>
       </c>
       <c r="S8" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="T8" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U8" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="V8" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>51.15</v>
+        <v>52.94</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.54</v>
+        <v>12.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.54</v>
+        <v>5.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>18.46</v>
+        <v>19.06</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.33</v>
+        <v>2.56</v>
       </c>
       <c r="AI8" t="n">
-        <v>86.75</v>
+        <v>86.19</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.75</v>
+        <v>4.81</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>47.67</v>
+        <v>46.19</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AP8" t="n">
         <v>1.75</v>
@@ -3923,172 +3911,172 @@
         <v>11.25</v>
       </c>
       <c r="AR8" t="n">
-        <v>9.33</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.83</v>
+        <v>7.62</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>49.33</v>
+        <v>49.88</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.08</v>
+        <v>11.44</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.25</v>
+        <v>7.44</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
-        <v>19.25</v>
+        <v>18.19</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.52</v>
+        <v>3.47</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.24</v>
+        <v>10.47</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.52</v>
+        <v>3.47</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="BK8" t="n">
         <v>0.88</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="BN8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO8" t="n">
         <v>1.72</v>
       </c>
-      <c r="BO8" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BP8" t="n">
-        <v>4.64</v>
+        <v>4.75</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.84</v>
+        <v>5.12</v>
       </c>
       <c r="BR8" t="n">
-        <v>96</v>
+        <v>96.88</v>
       </c>
       <c r="BS8" t="n">
-        <v>88</v>
+        <v>87.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>72</v>
+        <v>71.88</v>
       </c>
       <c r="BU8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BV8" t="n">
-        <v>32</v>
+        <v>28.12</v>
       </c>
       <c r="BW8" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>80</v>
+        <v>78.12</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.68</v>
+        <v>2.51</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.74</v>
+        <v>2.57</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CB8" t="n">
         <v>3.98</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.91</v>
+        <v>3.73</v>
       </c>
       <c r="CE8" t="n">
         <v>1.27</v>
       </c>
       <c r="CF8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CI8" t="n">
         <v>2.35</v>
       </c>
-      <c r="CG8" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CI8" t="n">
-        <v>2.33</v>
-      </c>
       <c r="CJ8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="CR8" t="n">
         <v>1.34</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CV8" t="n">
         <v>2.48</v>
@@ -4100,97 +4088,97 @@
         <v>1.52</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="DH8" t="n">
-        <v>97.68000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="DI8" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.28</v>
+        <v>5.44</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="DM8" t="n">
-        <v>50.2</v>
+        <v>51.44</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.24</v>
+        <v>11.34</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.32</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.24</v>
+        <v>6.78</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.28</v>
+        <v>51.41</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.84</v>
+        <v>12.16</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.12</v>
+        <v>7.35</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.72</v>
+        <v>4.81</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.84</v>
+        <v>18.62</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9">
@@ -4200,259 +4188,259 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="H9" t="n">
-        <v>100.67</v>
+        <v>105.94</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="K9" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="L9" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="M9" t="n">
-        <v>47.83</v>
+        <v>52.88</v>
       </c>
       <c r="N9" t="n">
-        <v>0.92</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="P9" t="n">
-        <v>10.25</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>10.62</v>
       </c>
       <c r="R9" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="S9" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T9" t="n">
-        <v>0.92</v>
+        <v>1.06</v>
       </c>
       <c r="U9" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="V9" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>49</v>
+        <v>49.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.58</v>
+        <v>12.81</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.92</v>
+        <v>8.19</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.67</v>
+        <v>4.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>16.75</v>
+        <v>17.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.85</v>
+        <v>3.06</v>
       </c>
       <c r="AI9" t="n">
-        <v>91.84999999999999</v>
+        <v>88.62</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.15</v>
+        <v>5.31</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.54</v>
+        <v>0.44</v>
       </c>
       <c r="AN9" t="n">
-        <v>46.31</v>
+        <v>44.94</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.08</v>
+        <v>12.12</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.85</v>
+        <v>10.69</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.92</v>
+        <v>7.69</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>47.85</v>
+        <v>47.81</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>12</v>
+        <v>12.06</v>
       </c>
       <c r="BB9" t="n">
-        <v>8</v>
+        <v>7.88</v>
       </c>
       <c r="BC9" t="n">
-        <v>4</v>
+        <v>4.19</v>
       </c>
       <c r="BD9" t="n">
-        <v>18.85</v>
+        <v>18.75</v>
       </c>
       <c r="BE9" t="n">
         <v>1.38</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.68</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.36</v>
+        <v>0.59</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.16</v>
+        <v>5.34</v>
       </c>
       <c r="BR9" t="n">
-        <v>84</v>
+        <v>87.5</v>
       </c>
       <c r="BS9" t="n">
-        <v>68</v>
+        <v>71.88</v>
       </c>
       <c r="BT9" t="n">
-        <v>48</v>
+        <v>53.12</v>
       </c>
       <c r="BU9" t="n">
-        <v>12</v>
+        <v>21.88</v>
       </c>
       <c r="BV9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>4</v>
+        <v>3.12</v>
       </c>
       <c r="BX9" t="n">
-        <v>44</v>
+        <v>46.88</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.3</v>
+        <v>3.37</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CF9" t="n">
         <v>2.45</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CI9" t="n">
         <v>2.23</v>
@@ -4461,16 +4449,16 @@
         <v>1.61</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CO9" t="n">
         <v>1.2</v>
@@ -4479,10 +4467,10 @@
         <v>1.7</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CS9" t="n">
         <v>2.55</v>
@@ -4503,13 +4491,13 @@
         <v>1.51</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="DB9" t="n">
         <v>1.22</v>
@@ -4518,49 +4506,49 @@
         <v>1.73</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.96</v>
+        <v>3.06</v>
       </c>
       <c r="DH9" t="n">
-        <v>96.08</v>
+        <v>97.28</v>
       </c>
       <c r="DI9" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.24</v>
+        <v>5.34</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="DM9" t="n">
-        <v>47.04</v>
+        <v>48.91</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="DO9" t="n">
         <v>2.28</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.72</v>
+        <v>11</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.44</v>
+        <v>10.66</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.48</v>
+        <v>7.6</v>
       </c>
       <c r="DS9" t="n">
         <v>0.12</v>
@@ -4572,28 +4560,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.4</v>
+        <v>48.44</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.28</v>
+        <v>12.44</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.96</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.32</v>
+        <v>4.4</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.84</v>
+        <v>18.06</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="10">
@@ -4603,298 +4591,298 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="H10" t="n">
-        <v>97.58</v>
+        <v>90.88</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="J10" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="K10" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>48.08</v>
+        <v>45.06</v>
       </c>
       <c r="N10" t="n">
         <v>0.25</v>
       </c>
       <c r="O10" t="n">
-        <v>2.67</v>
+        <v>2.44</v>
       </c>
       <c r="P10" t="n">
-        <v>7.17</v>
+        <v>7.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.08</v>
+        <v>10.94</v>
       </c>
       <c r="R10" t="n">
-        <v>9.67</v>
+        <v>9.44</v>
       </c>
       <c r="S10" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="T10" t="n">
-        <v>0.92</v>
+        <v>1.12</v>
       </c>
       <c r="U10" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="V10" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>52.83</v>
+        <v>51.38</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.42</v>
+        <v>12.44</v>
       </c>
       <c r="AA10" t="n">
-        <v>8</v>
+        <v>7.56</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.42</v>
+        <v>4.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>16.92</v>
+        <v>17.19</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AI10" t="n">
-        <v>84.69</v>
+        <v>82.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.46</v>
+        <v>3.62</v>
       </c>
       <c r="AM10" t="n">
         <v>0.38</v>
       </c>
       <c r="AN10" t="n">
-        <v>33.77</v>
+        <v>32.19</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.23</v>
+        <v>7.12</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.38</v>
+        <v>10.62</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.460000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>47.69</v>
+        <v>46.25</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.46</v>
+        <v>10.44</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.38</v>
+        <v>6.19</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.08</v>
+        <v>4.25</v>
       </c>
       <c r="BD10" t="n">
-        <v>14.77</v>
+        <v>15.19</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.04</v>
+        <v>9.69</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.76</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="BO10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>96.88</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>90.62</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>65.62</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CL10" t="n">
         <v>1.88</v>
       </c>
-      <c r="BP10" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>96</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>88</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>60</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>24</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>16</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>52</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="CB10" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="CC10" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="CE10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CF10" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="CG10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="CJ10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>1.91</v>
-      </c>
       <c r="CM10" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="CR10" t="n">
         <v>1.34</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CV10" t="n">
         <v>2.52</v>
@@ -4906,97 +4894,97 @@
         <v>1.53</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="DB10" t="n">
         <v>1.19</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="DE10" t="n">
         <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="DH10" t="n">
-        <v>90.88</v>
+        <v>86.69</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="DM10" t="n">
-        <v>40.64</v>
+        <v>38.62</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DP10" t="n">
-        <v>7.2</v>
+        <v>7.12</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.24</v>
+        <v>10.78</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.039999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.16</v>
+        <v>48.82</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.4</v>
+        <v>11.44</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.16</v>
+        <v>6.88</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.24</v>
+        <v>4.56</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.8</v>
+        <v>16.19</v>
       </c>
       <c r="EB10" t="n">
         <v>1.32</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="11">
@@ -5006,61 +4994,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
         <v>0.25</v>
       </c>
       <c r="F11" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="G11" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>85.08</v>
+        <v>82.44</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="K11" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="L11" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="M11" t="n">
-        <v>46.42</v>
+        <v>45.06</v>
       </c>
       <c r="N11" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="O11" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>10.25</v>
+        <v>10.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.75</v>
+        <v>10.56</v>
       </c>
       <c r="R11" t="n">
-        <v>8.58</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="U11" t="n">
         <v>0.25</v>
@@ -5072,232 +5060,232 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>44.33</v>
+        <v>44</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.08</v>
+        <v>12.81</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.92</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.17</v>
+        <v>4.19</v>
       </c>
       <c r="AC11" t="n">
         <v>18.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AI11" t="n">
-        <v>90.84999999999999</v>
+        <v>86.88</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AK11" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="AN11" t="n">
-        <v>43.15</v>
+        <v>40.94</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11.77</v>
+        <v>12</v>
       </c>
       <c r="AR11" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="AS11" t="n">
         <v>10</v>
       </c>
-      <c r="AS11" t="n">
-        <v>9</v>
-      </c>
       <c r="AT11" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>45.15</v>
+        <v>43.88</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.15</v>
+        <v>11.31</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>7.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.15</v>
+        <v>4.06</v>
       </c>
       <c r="BD11" t="n">
-        <v>18.92</v>
+        <v>18.31</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.2</v>
+        <v>10.16</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL11" t="n">
         <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.2</v>
+        <v>5.06</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5</v>
+        <v>5.03</v>
       </c>
       <c r="BR11" t="n">
-        <v>92</v>
+        <v>93.75</v>
       </c>
       <c r="BS11" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT11" t="n">
-        <v>52</v>
+        <v>56.25</v>
       </c>
       <c r="BU11" t="n">
-        <v>28</v>
+        <v>28.12</v>
       </c>
       <c r="BV11" t="n">
-        <v>16</v>
+        <v>18.75</v>
       </c>
       <c r="BW11" t="n">
-        <v>4</v>
+        <v>6.25</v>
       </c>
       <c r="BX11" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.14</v>
+        <v>3.27</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.81</v>
+        <v>3.86</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.96</v>
+        <v>4.05</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.08</v>
+        <v>4.27</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.22</v>
+        <v>4.54</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CL11" t="n">
         <v>1.87</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CO11" t="n">
         <v>1.18</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="CR11" t="n">
         <v>1.34</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="CT11" t="n">
         <v>3.34</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CV11" t="n">
         <v>2.45</v>
@@ -5306,67 +5294,67 @@
         <v>1.59</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="DE11" t="n">
         <v>0.16</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="DH11" t="n">
-        <v>88.08</v>
+        <v>84.66</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.12</v>
+        <v>4.03</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.72</v>
+        <v>43</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.52</v>
+        <v>0.46</v>
       </c>
       <c r="DO11" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.04</v>
+        <v>11.47</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.880000000000001</v>
+        <v>10.34</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="DS11" t="n">
         <v>0.16</v>
@@ -5378,28 +5366,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.76</v>
+        <v>43.94</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.6</v>
+        <v>12.06</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.44</v>
+        <v>7.94</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.16</v>
+        <v>4.12</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.84</v>
+        <v>18.53</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="12">
@@ -5409,298 +5397,298 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="F12" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="G12" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="H12" t="n">
-        <v>98.77</v>
+        <v>96.81</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>4.15</v>
+        <v>3.88</v>
       </c>
       <c r="L12" t="n">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="M12" t="n">
-        <v>65.08</v>
+        <v>58.75</v>
       </c>
       <c r="N12" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="P12" t="n">
-        <v>13.77</v>
+        <v>13.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>9</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>7.08</v>
+        <v>7.5</v>
       </c>
       <c r="S12" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="T12" t="n">
         <v>1.38</v>
       </c>
       <c r="U12" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="V12" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>46.23</v>
+        <v>46.38</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="Z12" t="n">
-        <v>11.38</v>
+        <v>11.88</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.31</v>
+        <v>7.62</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.08</v>
+        <v>4.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>23.15</v>
+        <v>21.69</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AI12" t="n">
-        <v>92.42</v>
+        <v>89.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.08</v>
+        <v>4.25</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AN12" t="n">
-        <v>43.75</v>
+        <v>42.12</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12.25</v>
+        <v>11.75</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.67</v>
+        <v>9</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.33</v>
+        <v>9</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>40.92</v>
+        <v>42.88</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.75</v>
+        <v>10.31</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.25</v>
+        <v>7.06</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.42</v>
+        <v>17.69</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="BF12" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.279999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL12" t="n">
         <v>0.84</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.6</v>
+        <v>4.84</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.68</v>
+        <v>4.72</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>96</v>
+        <v>90.62</v>
       </c>
       <c r="BT12" t="n">
-        <v>56</v>
+        <v>56.25</v>
       </c>
       <c r="BU12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BV12" t="n">
-        <v>16</v>
+        <v>15.62</v>
       </c>
       <c r="BW12" t="n">
-        <v>12</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BX12" t="n">
-        <v>68</v>
+        <v>62.5</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.94</v>
+        <v>3.99</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.06</v>
+        <v>4.14</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.91</v>
+        <v>5.16</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.53</v>
+        <v>5.69</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="CT12" t="n">
         <v>3.31</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CV12" t="n">
         <v>2.28</v>
@@ -5712,22 +5700,22 @@
         <v>1.5</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="DE12" t="n">
         <v>0.12</v>
@@ -5736,40 +5724,40 @@
         <v>1.28</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="DH12" t="n">
-        <v>95.72</v>
+        <v>93.16</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.12</v>
+        <v>4.06</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="DM12" t="n">
-        <v>54.84</v>
+        <v>50.44</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="DQ12" t="n">
-        <v>8.84</v>
+        <v>9.19</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.68</v>
+        <v>8.25</v>
       </c>
       <c r="DS12" t="n">
         <v>0.12</v>
@@ -5781,28 +5769,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.68</v>
+        <v>44.63</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.08</v>
+        <v>11.1</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.28</v>
+        <v>7.34</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.88</v>
+        <v>19.69</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="13">
@@ -5812,181 +5800,181 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E13" t="n">
         <v>0.38</v>
       </c>
       <c r="F13" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="H13" t="n">
-        <v>88.92</v>
+        <v>95.81</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="J13" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="K13" t="n">
-        <v>4.46</v>
+        <v>4.75</v>
       </c>
       <c r="L13" t="n">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="M13" t="n">
-        <v>42</v>
+        <v>46.94</v>
       </c>
       <c r="N13" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="O13" t="n">
-        <v>1.46</v>
+        <v>1.88</v>
       </c>
       <c r="P13" t="n">
-        <v>10.77</v>
+        <v>9.94</v>
       </c>
       <c r="Q13" t="n">
         <v>12.69</v>
       </c>
       <c r="R13" t="n">
-        <v>7.92</v>
+        <v>8</v>
       </c>
       <c r="S13" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="U13" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="V13" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>47.92</v>
+        <v>48.5</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>11.38</v>
+        <v>11.94</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.23</v>
+        <v>7.62</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.15</v>
+        <v>4.31</v>
       </c>
       <c r="AC13" t="n">
-        <v>20.31</v>
+        <v>19.94</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AI13" t="n">
-        <v>104.17</v>
+        <v>98.69</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.08</v>
+        <v>4.44</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.92</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AN13" t="n">
-        <v>51</v>
+        <v>47.12</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.92</v>
+        <v>12.31</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.42</v>
+        <v>12.44</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>8.81</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>48.83</v>
+        <v>46.62</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>13.92</v>
+        <v>14.31</v>
       </c>
       <c r="BB13" t="n">
         <v>9.25</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.67</v>
+        <v>5.06</v>
       </c>
       <c r="BD13" t="n">
-        <v>16.83</v>
+        <v>17.19</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="BG13" t="n">
         <v>3.12</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.92</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BI13" t="n">
         <v>3.12</v>
@@ -5998,10 +5986,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="BN13" t="n">
         <v>1.56</v>
@@ -6010,202 +5998,202 @@
         <v>1.56</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.16</v>
+        <v>3.94</v>
       </c>
       <c r="BR13" t="n">
-        <v>96</v>
+        <v>96.88</v>
       </c>
       <c r="BS13" t="n">
-        <v>76</v>
+        <v>71.88</v>
       </c>
       <c r="BT13" t="n">
-        <v>64</v>
+        <v>59.38</v>
       </c>
       <c r="BU13" t="n">
-        <v>32</v>
+        <v>31.25</v>
       </c>
       <c r="BV13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW13" t="n">
-        <v>12</v>
+        <v>15.62</v>
       </c>
       <c r="BX13" t="n">
-        <v>64</v>
+        <v>59.38</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.65</v>
+        <v>3.69</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.85</v>
+        <v>3.89</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.27</v>
+        <v>3.35</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CO13" t="n">
         <v>1.18</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="CT13" t="n">
         <v>3.31</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CW13" t="n">
         <v>1.61</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="DG13" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DH13" t="n">
-        <v>96.23999999999999</v>
+        <v>97.25</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.76</v>
+        <v>4.6</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="DM13" t="n">
-        <v>46.32</v>
+        <v>47.03</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.32</v>
+        <v>11.12</v>
       </c>
       <c r="DQ13" t="n">
         <v>12.56</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.96</v>
+        <v>8.41</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.36</v>
+        <v>47.56</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.6</v>
+        <v>13.12</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.4</v>
+        <v>4.68</v>
       </c>
       <c r="EA13" t="n">
-        <v>18.64</v>
+        <v>18.57</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
     </row>
   </sheetData>
